--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/catalogoPecas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC8AC66C-9162-4423-9B3C-059320002222}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E773DA3B-55AF-49D2-93F9-A3811158B3A4}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4155" yWindow="4155" windowWidth="15900" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="430">
   <si>
     <t>ABRAÇADEIRA PARALAMA VOLVO</t>
   </si>
@@ -1116,30 +1116,6 @@
     <t>VALVULA TRANSFERÊNCIA</t>
   </si>
   <si>
-    <t>CINTA</t>
-  </si>
-  <si>
-    <t>CORDA (METROS)</t>
-  </si>
-  <si>
-    <t>DESINGRIPANTE</t>
-  </si>
-  <si>
-    <t>ESPUMA EXPANSIVA</t>
-  </si>
-  <si>
-    <t>GANCHO DE LONA (LIGA)</t>
-  </si>
-  <si>
-    <t>LONA EMBORRACHADA GRANELEIRO</t>
-  </si>
-  <si>
-    <t>LONA PROT COB PVC AZ - (LONA FÁCIL)</t>
-  </si>
-  <si>
-    <t>REDE CONTENÇÃO PLUMA</t>
-  </si>
-  <si>
     <t>ABRAÇADEIRA</t>
   </si>
   <si>
@@ -1330,318 +1306,6 @@
   </si>
   <si>
     <t>LANTERNA DO ABS (LANTERNA VERDE)</t>
-  </si>
-  <si>
-    <t>ALONGADOR (EXTENSOR DE BICO)</t>
-  </si>
-  <si>
-    <t>BICO PNEU DIANTEIRA (RODA CAVALO)</t>
-  </si>
-  <si>
-    <t>BICO PNEU (RODA FERRO CARRETA)</t>
-  </si>
-  <si>
-    <t>CALIBRADOR PR C/HAST INDIC;FIX ANG;7188F</t>
-  </si>
-  <si>
-    <t>INFLADOR DE ENCHER PNEU</t>
-  </si>
-  <si>
-    <t>ESCOVA ROTATIVA 7P (P/LIXADEIRA)</t>
-  </si>
-  <si>
-    <t>NÚCLEO CURTO VÁLV. PNEU</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE RODA CARRETA RANDON</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE RODA CARRETA LIBRELATTO</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE RODA DIANTEIRA SCANIA</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE RODA TRAÇÃO SCANIA</t>
-  </si>
-  <si>
-    <t>PARAFUSO DE RODA DIANTEIRA VOLVO</t>
-  </si>
-  <si>
-    <t>PARAFUSO DA TRAÇÃO VOLVO</t>
-  </si>
-  <si>
-    <t>PNEU VULCANIZADO</t>
-  </si>
-  <si>
-    <t>PNEU LISO NOVO</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO NOVO</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO BONIN (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO BONIN (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO FOX  (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO FOX (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO VIPAL (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU LISO VIPAL BANDA NOVA (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO VIPAL (RECAPADO)</t>
-  </si>
-  <si>
-    <t>PNEU BORRACHUDO VIPAL (RECAPADO) VT100</t>
-  </si>
-  <si>
-    <t>RODA 22,5X8,25 295 10 FUROS</t>
-  </si>
-  <si>
-    <t>SACA VÁLVULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VASELINA VEGETAL 3KG </t>
-  </si>
-  <si>
-    <t>AVENTAL DE RASPA</t>
-  </si>
-  <si>
-    <t>BOTINA 35 (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>BOTINA 36  (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>BOTINA 37  (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>BOTINA 38  (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>BOTINA 39  (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>BOTINA 40  (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>BOTINA 41  (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>BOTINA 42  (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>BOTINA 43  (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>BOTINA 44  (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>BOTINA 45  (CANO ALTO)</t>
-  </si>
-  <si>
-    <t>CALÇA GG (OFICINA)</t>
-  </si>
-  <si>
-    <t>CALÇA G (OFICINA)</t>
-  </si>
-  <si>
-    <t>CALÇA M (OFICINA)</t>
-  </si>
-  <si>
-    <t>CALÇA P (OFICINA)</t>
-  </si>
-  <si>
-    <t>CAMISA GG (OFICINA)</t>
-  </si>
-  <si>
-    <t>CAMISA G (OFICINA)</t>
-  </si>
-  <si>
-    <t>CAMISA M (OFICINA)</t>
-  </si>
-  <si>
-    <t>CAMISA P (OFICINA)</t>
-  </si>
-  <si>
-    <t>CINTA ERGONÔMICA G</t>
-  </si>
-  <si>
-    <t>CINTA ERGONÔMICA M</t>
-  </si>
-  <si>
-    <t>CINTA ERGONÔMICA P</t>
-  </si>
-  <si>
-    <t>CINTA ERGONÔMICA XG</t>
-  </si>
-  <si>
-    <t>CINTO SEG ALTISEG 1180192</t>
-  </si>
-  <si>
-    <t>COLETE SINALIZAÇÃO EM X</t>
-  </si>
-  <si>
-    <t>TALABARTE Y PES PARA ALTURA</t>
-  </si>
-  <si>
-    <t>CAPUZ SEG UNIC HERCULES (TOUCA ARABE)</t>
-  </si>
-  <si>
-    <t>LUVA LATEX AMARELA G</t>
-  </si>
-  <si>
-    <t>LUVA LATEX AMARELA XG</t>
-  </si>
-  <si>
-    <t>LUVA MULTITATO P</t>
-  </si>
-  <si>
-    <t>LUVA MULTITATO M</t>
-  </si>
-  <si>
-    <t>LUVA MULTITATO G</t>
-  </si>
-  <si>
-    <t>LUVA MALHA TRICOTADA</t>
-  </si>
-  <si>
-    <t>LUVA MISTA P (LAVADOR)</t>
-  </si>
-  <si>
-    <t>LUVA RASPA</t>
-  </si>
-  <si>
-    <t>LUVA VAQUETA (OFICINA)</t>
-  </si>
-  <si>
-    <t>LUVA SEG VERDE (CARLOS E ROSANGELA)</t>
-  </si>
-  <si>
-    <t>LUVEX CREME</t>
-  </si>
-  <si>
-    <t>CLIP LUVA</t>
-  </si>
-  <si>
-    <t>MASCARA DE SOLDA</t>
-  </si>
-  <si>
-    <t>MÁSCARA PFF2</t>
-  </si>
-  <si>
-    <t>MACACAO LAVADOR P</t>
-  </si>
-  <si>
-    <t>MACACAO LAVADOR M</t>
-  </si>
-  <si>
-    <t>MACACAO LAVADOR G</t>
-  </si>
-  <si>
-    <t>MACACAO LAVADOR GG</t>
-  </si>
-  <si>
-    <t>MACACAO LAVADOR XXG</t>
-  </si>
-  <si>
-    <t>ÓCULOS ESCURO</t>
-  </si>
-  <si>
-    <t>ÓCULOS INCOLOR</t>
-  </si>
-  <si>
-    <t>ÓCULOS INCOLOR MODELO NOVO</t>
-  </si>
-  <si>
-    <t>ÓCULOS  (LAVADOR)</t>
-  </si>
-  <si>
-    <t>ÓCULOS SOBREPOR</t>
-  </si>
-  <si>
-    <t>PROTETOR FACIAL TRANSPARENTE</t>
-  </si>
-  <si>
-    <t>PROT AUDITIVO ABAFADOR CONCHA</t>
-  </si>
-  <si>
-    <t>PROT AUDITIVO SILICONE PLUG</t>
-  </si>
-  <si>
-    <t>PROTETOR SOLAR 60FPS</t>
-  </si>
-  <si>
-    <t>KIT HIGIENE ABAFADOR</t>
-  </si>
-  <si>
-    <t>DISCO CORTE 7 POLEGADAS DEWALT</t>
-  </si>
-  <si>
-    <t>DISCO CORTE 4 POLEGADAS DEWALT</t>
-  </si>
-  <si>
-    <t>DISCO FLAP 7 POLEGADAS</t>
-  </si>
-  <si>
-    <t>DISCO FLAP 4 POLEGADAS</t>
-  </si>
-  <si>
-    <t>DISCO DESBASTE 7P</t>
-  </si>
-  <si>
-    <t>DISCO ROQUITE 80</t>
-  </si>
-  <si>
-    <t>ESTOPA (LANÇAR POR UND)</t>
-  </si>
-  <si>
-    <t>ESCOVA  AÇO CABO PLAST</t>
-  </si>
-  <si>
-    <t>FAIXA REFLET LE 3M HB004037097</t>
-  </si>
-  <si>
-    <t>FAIXA REFLETIVA PARACHOQUE</t>
-  </si>
-  <si>
-    <t>LIXA OURO 120</t>
-  </si>
-  <si>
-    <t>LIXA OURO 220</t>
-  </si>
-  <si>
-    <t>LIXA FERRO N120 225X275MM</t>
-  </si>
-  <si>
-    <t>PINCEL</t>
-  </si>
-  <si>
-    <t>THINNER</t>
-  </si>
-  <si>
-    <t>TINTA BRANCO PU</t>
-  </si>
-  <si>
-    <t>TINTA PU PRETO CADILAC</t>
-  </si>
-  <si>
-    <t>TINTA SPRAY BRANCO 250ML</t>
-  </si>
-  <si>
-    <t>TINTA SPRAY PRETO BRILHANTE</t>
-  </si>
-  <si>
-    <t>TINTA SPRAY AZU 250GR</t>
   </si>
   <si>
     <t>CONECTOR MACHO 16X16MM</t>
@@ -2167,10 +1831,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>541</v>
+        <v>429</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>540</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -2762,7 +2426,7 @@
         <v>341430</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>539</v>
+        <v>427</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5076,8 +4740,8 @@
       </c>
     </row>
     <row r="365" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A365" s="17">
-        <v>1010062826</v>
+      <c r="A365" s="4">
+        <v>1010008578</v>
       </c>
       <c r="B365" s="4" t="s">
         <v>363</v>
@@ -5085,15 +4749,15 @@
     </row>
     <row r="366" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" s="4">
-        <v>1010002592</v>
+        <v>1010031694</v>
       </c>
       <c r="B366" s="4" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="367" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A367" s="5">
-        <v>1010001155</v>
+      <c r="A367" s="4">
+        <v>1010051997</v>
       </c>
       <c r="B367" s="4" t="s">
         <v>365</v>
@@ -5101,7 +4765,7 @@
     </row>
     <row r="368" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" s="4">
-        <v>159668</v>
+        <v>1010022601</v>
       </c>
       <c r="B368" s="4" t="s">
         <v>366</v>
@@ -5109,15 +4773,15 @@
     </row>
     <row r="369" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" s="4">
-        <v>382290</v>
+        <v>1010054278</v>
       </c>
       <c r="B369" s="4" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="370" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A370" s="5">
-        <v>1010044502</v>
+      <c r="A370" s="4">
+        <v>1010083462</v>
       </c>
       <c r="B370" s="4" t="s">
         <v>368</v>
@@ -5125,7 +4789,7 @@
     </row>
     <row r="371" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" s="4">
-        <v>1010053692</v>
+        <v>1010027772</v>
       </c>
       <c r="B371" s="4" t="s">
         <v>369</v>
@@ -5133,39 +4797,39 @@
     </row>
     <row r="372" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" s="4">
-        <v>390742</v>
+        <v>300186</v>
       </c>
       <c r="B372" s="4" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="373" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A373" s="4">
-        <v>1010008578</v>
-      </c>
-      <c r="B373" s="4" t="s">
+      <c r="A373" s="6">
+        <v>214055</v>
+      </c>
+      <c r="B373" s="14" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="374" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A374" s="4">
-        <v>1010031694</v>
-      </c>
-      <c r="B374" s="4" t="s">
+      <c r="A374" s="11">
+        <v>1010021956</v>
+      </c>
+      <c r="B374" s="14" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="375" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A375" s="4">
-        <v>1010051997</v>
-      </c>
-      <c r="B375" s="4" t="s">
+      <c r="A375" s="11">
+        <v>1010026464</v>
+      </c>
+      <c r="B375" s="14" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="376" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A376" s="4">
-        <v>1010022601</v>
+      <c r="A376" s="3">
+        <v>1010021957</v>
       </c>
       <c r="B376" s="4" t="s">
         <v>374</v>
@@ -5173,7 +4837,7 @@
     </row>
     <row r="377" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" s="4">
-        <v>1010054278</v>
+        <v>1010026462</v>
       </c>
       <c r="B377" s="4" t="s">
         <v>375</v>
@@ -5181,7 +4845,7 @@
     </row>
     <row r="378" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" s="4">
-        <v>1010083462</v>
+        <v>1010026551</v>
       </c>
       <c r="B378" s="4" t="s">
         <v>376</v>
@@ -5189,7 +4853,7 @@
     </row>
     <row r="379" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" s="4">
-        <v>1010027772</v>
+        <v>1010042554</v>
       </c>
       <c r="B379" s="4" t="s">
         <v>377</v>
@@ -5197,39 +4861,39 @@
     </row>
     <row r="380" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" s="4">
-        <v>300186</v>
+        <v>1010039904</v>
       </c>
       <c r="B380" s="4" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="381" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A381" s="6">
-        <v>214055</v>
-      </c>
-      <c r="B381" s="14" t="s">
+      <c r="A381" s="4">
+        <v>1010060205</v>
+      </c>
+      <c r="B381" s="4" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="382" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A382" s="11">
-        <v>1010021956</v>
-      </c>
-      <c r="B382" s="14" t="s">
+      <c r="A382" s="4">
+        <v>1010060206</v>
+      </c>
+      <c r="B382" s="4" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="383" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A383" s="11">
-        <v>1010026464</v>
-      </c>
-      <c r="B383" s="14" t="s">
+      <c r="A383" s="4">
+        <v>1010077431</v>
+      </c>
+      <c r="B383" s="4" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="384" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A384" s="3">
-        <v>1010021957</v>
+      <c r="A384" s="4">
+        <v>1010077503</v>
       </c>
       <c r="B384" s="4" t="s">
         <v>382</v>
@@ -5237,7 +4901,7 @@
     </row>
     <row r="385" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" s="4">
-        <v>1010026462</v>
+        <v>386009</v>
       </c>
       <c r="B385" s="4" t="s">
         <v>383</v>
@@ -5245,7 +4909,7 @@
     </row>
     <row r="386" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" s="4">
-        <v>1010026551</v>
+        <v>1010080958</v>
       </c>
       <c r="B386" s="4" t="s">
         <v>384</v>
@@ -5253,7 +4917,7 @@
     </row>
     <row r="387" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" s="4">
-        <v>1010042554</v>
+        <v>20191</v>
       </c>
       <c r="B387" s="4" t="s">
         <v>385</v>
@@ -5261,7 +4925,7 @@
     </row>
     <row r="388" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" s="4">
-        <v>1010039904</v>
+        <v>431445</v>
       </c>
       <c r="B388" s="4" t="s">
         <v>386</v>
@@ -5269,7 +4933,7 @@
     </row>
     <row r="389" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" s="4">
-        <v>1010060205</v>
+        <v>431463</v>
       </c>
       <c r="B389" s="4" t="s">
         <v>387</v>
@@ -5277,7 +4941,7 @@
     </row>
     <row r="390" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" s="4">
-        <v>1010060206</v>
+        <v>431464</v>
       </c>
       <c r="B390" s="4" t="s">
         <v>388</v>
@@ -5285,23 +4949,23 @@
     </row>
     <row r="391" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" s="4">
-        <v>1010077431</v>
-      </c>
-      <c r="B391" s="4" t="s">
+        <v>1010024158</v>
+      </c>
+      <c r="B391" s="6" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="392" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" s="4">
-        <v>1010077503</v>
-      </c>
-      <c r="B392" s="4" t="s">
+        <v>1010024131</v>
+      </c>
+      <c r="B392" s="6" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="393" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" s="4">
-        <v>386009</v>
+        <v>1010007160</v>
       </c>
       <c r="B393" s="4" t="s">
         <v>391</v>
@@ -5309,7 +4973,7 @@
     </row>
     <row r="394" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" s="4">
-        <v>1010080958</v>
+        <v>1010023642</v>
       </c>
       <c r="B394" s="4" t="s">
         <v>392</v>
@@ -5317,15 +4981,15 @@
     </row>
     <row r="395" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" s="4">
-        <v>20191</v>
-      </c>
-      <c r="B395" s="4" t="s">
+        <v>1010007193</v>
+      </c>
+      <c r="B395" s="5" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="396" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" s="4">
-        <v>431445</v>
+        <v>1010042637</v>
       </c>
       <c r="B396" s="4" t="s">
         <v>394</v>
@@ -5333,7 +4997,7 @@
     </row>
     <row r="397" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" s="4">
-        <v>431463</v>
+        <v>1040075323</v>
       </c>
       <c r="B397" s="4" t="s">
         <v>395</v>
@@ -5341,55 +5005,55 @@
     </row>
     <row r="398" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" s="4">
-        <v>431464</v>
-      </c>
-      <c r="B398" s="4" t="s">
+        <v>1040075324</v>
+      </c>
+      <c r="B398" s="6" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="399" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A399" s="4">
-        <v>1010024158</v>
+      <c r="A399" s="18">
+        <v>1040083312</v>
       </c>
       <c r="B399" s="6" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="400" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A400" s="4">
-        <v>1010024131</v>
+      <c r="A400" s="18">
+        <v>1040077661</v>
       </c>
       <c r="B400" s="6" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="401" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A401" s="4">
-        <v>1010007160</v>
-      </c>
-      <c r="B401" s="4" t="s">
+      <c r="A401" s="18">
+        <v>409638</v>
+      </c>
+      <c r="B401" s="19" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="402" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A402" s="4">
-        <v>1010023642</v>
-      </c>
-      <c r="B402" s="4" t="s">
+      <c r="A402" s="3">
+        <v>1040017489</v>
+      </c>
+      <c r="B402" s="3" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="403" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A403" s="4">
-        <v>1010007193</v>
-      </c>
-      <c r="B403" s="5" t="s">
+      <c r="A403" s="3">
+        <v>400174</v>
+      </c>
+      <c r="B403" s="4" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="404" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" s="4">
-        <v>1010042637</v>
+        <v>400175</v>
       </c>
       <c r="B404" s="4" t="s">
         <v>402</v>
@@ -5397,7 +5061,7 @@
     </row>
     <row r="405" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" s="4">
-        <v>1040075323</v>
+        <v>1040017505</v>
       </c>
       <c r="B405" s="4" t="s">
         <v>403</v>
@@ -5405,47 +5069,47 @@
     </row>
     <row r="406" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" s="4">
-        <v>1040075324</v>
-      </c>
-      <c r="B406" s="6" t="s">
+        <v>1040017503</v>
+      </c>
+      <c r="B406" s="4" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="407" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A407" s="18">
-        <v>1040083312</v>
-      </c>
-      <c r="B407" s="6" t="s">
+      <c r="A407" s="4">
+        <v>1010046445</v>
+      </c>
+      <c r="B407" s="4" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="408" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A408" s="18">
-        <v>1040077661</v>
-      </c>
-      <c r="B408" s="6" t="s">
+      <c r="A408" s="4">
+        <v>1010021033</v>
+      </c>
+      <c r="B408" s="4" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="409" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A409" s="18">
-        <v>409638</v>
-      </c>
-      <c r="B409" s="19" t="s">
+      <c r="A409" s="4">
+        <v>24950</v>
+      </c>
+      <c r="B409" s="4" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="410" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A410" s="3">
-        <v>1040017489</v>
-      </c>
-      <c r="B410" s="3" t="s">
+      <c r="A410" s="4">
+        <v>1010016356</v>
+      </c>
+      <c r="B410" s="4" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="411" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A411" s="3">
-        <v>400174</v>
+      <c r="A411" s="4">
+        <v>400228</v>
       </c>
       <c r="B411" s="4" t="s">
         <v>409</v>
@@ -5453,7 +5117,7 @@
     </row>
     <row r="412" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" s="4">
-        <v>400175</v>
+        <v>1010052021</v>
       </c>
       <c r="B412" s="4" t="s">
         <v>410</v>
@@ -5461,7 +5125,7 @@
     </row>
     <row r="413" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" s="4">
-        <v>1040017505</v>
+        <v>1040091721</v>
       </c>
       <c r="B413" s="4" t="s">
         <v>411</v>
@@ -5469,7 +5133,7 @@
     </row>
     <row r="414" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" s="4">
-        <v>1040017503</v>
+        <v>1010062022</v>
       </c>
       <c r="B414" s="4" t="s">
         <v>412</v>
@@ -5477,7 +5141,7 @@
     </row>
     <row r="415" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" s="4">
-        <v>1010046445</v>
+        <v>18336</v>
       </c>
       <c r="B415" s="4" t="s">
         <v>413</v>
@@ -5485,7 +5149,7 @@
     </row>
     <row r="416" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" s="4">
-        <v>1010021033</v>
+        <v>229205</v>
       </c>
       <c r="B416" s="4" t="s">
         <v>414</v>
@@ -5493,7 +5157,7 @@
     </row>
     <row r="417" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" s="4">
-        <v>24950</v>
+        <v>60671</v>
       </c>
       <c r="B417" s="4" t="s">
         <v>415</v>
@@ -5501,7 +5165,7 @@
     </row>
     <row r="418" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" s="4">
-        <v>1010016356</v>
+        <v>1010059726</v>
       </c>
       <c r="B418" s="4" t="s">
         <v>416</v>
@@ -5509,7 +5173,7 @@
     </row>
     <row r="419" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" s="4">
-        <v>400228</v>
+        <v>1010008144</v>
       </c>
       <c r="B419" s="4" t="s">
         <v>417</v>
@@ -5517,7 +5181,7 @@
     </row>
     <row r="420" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" s="4">
-        <v>1010052021</v>
+        <v>1010007244</v>
       </c>
       <c r="B420" s="4" t="s">
         <v>418</v>
@@ -5525,7 +5189,7 @@
     </row>
     <row r="421" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" s="4">
-        <v>1040091721</v>
+        <v>1010006827</v>
       </c>
       <c r="B421" s="4" t="s">
         <v>419</v>
@@ -5533,7 +5197,7 @@
     </row>
     <row r="422" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" s="4">
-        <v>1010062022</v>
+        <v>1040075426</v>
       </c>
       <c r="B422" s="4" t="s">
         <v>420</v>
@@ -5541,7 +5205,7 @@
     </row>
     <row r="423" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" s="4">
-        <v>18336</v>
+        <v>1040075427</v>
       </c>
       <c r="B423" s="4" t="s">
         <v>421</v>
@@ -5549,7 +5213,7 @@
     </row>
     <row r="424" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" s="4">
-        <v>229205</v>
+        <v>401167</v>
       </c>
       <c r="B424" s="4" t="s">
         <v>422</v>
@@ -5557,7 +5221,7 @@
     </row>
     <row r="425" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" s="4">
-        <v>60671</v>
+        <v>403459</v>
       </c>
       <c r="B425" s="4" t="s">
         <v>423</v>
@@ -5565,7 +5229,7 @@
     </row>
     <row r="426" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" s="4">
-        <v>1010059726</v>
+        <v>300296</v>
       </c>
       <c r="B426" s="4" t="s">
         <v>424</v>
@@ -5573,7 +5237,7 @@
     </row>
     <row r="427" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" s="4">
-        <v>1010008144</v>
+        <v>1010026973</v>
       </c>
       <c r="B427" s="4" t="s">
         <v>425</v>
@@ -5581,907 +5245,459 @@
     </row>
     <row r="428" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" s="4">
-        <v>1010007244</v>
+        <v>1040017204</v>
       </c>
       <c r="B428" s="4" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="429" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A429" s="4">
-        <v>1010006827</v>
-      </c>
-      <c r="B429" s="4" t="s">
-        <v>427</v>
-      </c>
+      <c r="A429" s="4"/>
+      <c r="B429" s="4"/>
     </row>
     <row r="430" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A430" s="4">
-        <v>1040075426</v>
-      </c>
-      <c r="B430" s="4" t="s">
-        <v>428</v>
-      </c>
+      <c r="A430" s="4"/>
+      <c r="B430" s="4"/>
     </row>
     <row r="431" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A431" s="4">
-        <v>1040075427</v>
-      </c>
-      <c r="B431" s="4" t="s">
-        <v>429</v>
-      </c>
+      <c r="A431" s="4"/>
+      <c r="B431" s="4"/>
     </row>
     <row r="432" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A432" s="4">
-        <v>401167</v>
-      </c>
-      <c r="B432" s="4" t="s">
-        <v>430</v>
-      </c>
+      <c r="A432" s="4"/>
+      <c r="B432" s="4"/>
     </row>
     <row r="433" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A433" s="4">
-        <v>403459</v>
-      </c>
-      <c r="B433" s="4" t="s">
-        <v>431</v>
-      </c>
+      <c r="A433" s="4"/>
+      <c r="B433" s="4"/>
     </row>
     <row r="434" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A434" s="4">
-        <v>300296</v>
-      </c>
-      <c r="B434" s="4" t="s">
-        <v>432</v>
-      </c>
+      <c r="A434" s="4"/>
+      <c r="B434" s="4"/>
     </row>
     <row r="435" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A435" s="4">
-        <v>1010026973</v>
-      </c>
-      <c r="B435" s="4" t="s">
-        <v>433</v>
-      </c>
+      <c r="A435" s="4"/>
+      <c r="B435" s="4"/>
     </row>
     <row r="436" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A436" s="4">
-        <v>1040017204</v>
-      </c>
-      <c r="B436" s="4" t="s">
-        <v>434</v>
-      </c>
+      <c r="A436" s="4"/>
+      <c r="B436" s="4"/>
     </row>
     <row r="437" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A437" s="5">
-        <v>1010022119</v>
-      </c>
-      <c r="B437" s="5" t="s">
-        <v>435</v>
-      </c>
+      <c r="A437" s="5"/>
+      <c r="B437" s="5"/>
     </row>
     <row r="438" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A438" s="4">
-        <v>1010034964</v>
-      </c>
-      <c r="B438" s="4" t="s">
-        <v>436</v>
-      </c>
+      <c r="A438" s="4"/>
+      <c r="B438" s="4"/>
     </row>
     <row r="439" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A439" s="4">
-        <v>1010058709</v>
-      </c>
-      <c r="B439" s="4" t="s">
-        <v>437</v>
-      </c>
+      <c r="A439" s="4"/>
+      <c r="B439" s="4"/>
     </row>
     <row r="440" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A440" s="4">
-        <v>1010025711</v>
-      </c>
-      <c r="B440" s="4" t="s">
-        <v>438</v>
-      </c>
+      <c r="A440" s="4"/>
+      <c r="B440" s="4"/>
     </row>
     <row r="441" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A441" s="4">
-        <v>1010059684</v>
-      </c>
-      <c r="B441" s="4" t="s">
-        <v>439</v>
-      </c>
+      <c r="A441" s="4"/>
+      <c r="B441" s="4"/>
     </row>
     <row r="442" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A442" s="4">
-        <v>427341</v>
-      </c>
-      <c r="B442" s="4" t="s">
-        <v>440</v>
-      </c>
+      <c r="A442" s="4"/>
+      <c r="B442" s="4"/>
     </row>
     <row r="443" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A443" s="4">
-        <v>32344</v>
-      </c>
-      <c r="B443" s="4" t="s">
-        <v>441</v>
-      </c>
+      <c r="A443" s="4"/>
+      <c r="B443" s="4"/>
     </row>
     <row r="444" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A444" s="6">
-        <v>1010022588</v>
-      </c>
-      <c r="B444" s="4" t="s">
-        <v>442</v>
-      </c>
+      <c r="A444" s="6"/>
+      <c r="B444" s="4"/>
     </row>
     <row r="445" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A445" s="4">
-        <v>1010026864</v>
-      </c>
-      <c r="B445" s="14" t="s">
-        <v>443</v>
-      </c>
+      <c r="A445" s="4"/>
+      <c r="B445" s="14"/>
     </row>
     <row r="446" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A446" s="3">
-        <v>1010030946</v>
-      </c>
-      <c r="B446" s="14" t="s">
-        <v>444</v>
-      </c>
+      <c r="A446" s="3"/>
+      <c r="B446" s="14"/>
     </row>
     <row r="447" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A447" s="3">
-        <v>1010022589</v>
-      </c>
-      <c r="B447" s="4" t="s">
-        <v>445</v>
-      </c>
+      <c r="A447" s="3"/>
+      <c r="B447" s="4"/>
     </row>
     <row r="448" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A448" s="4">
-        <v>1040090143</v>
-      </c>
-      <c r="B448" s="4" t="s">
-        <v>446</v>
-      </c>
+      <c r="A448" s="4"/>
+      <c r="B448" s="4"/>
     </row>
     <row r="449" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A449" s="4">
-        <v>1040090138</v>
-      </c>
-      <c r="B449" s="4" t="s">
-        <v>447</v>
-      </c>
+      <c r="A449" s="4"/>
+      <c r="B449" s="4"/>
     </row>
     <row r="450" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A450" s="4">
-        <v>1030001314</v>
-      </c>
-      <c r="B450" s="4" t="s">
-        <v>448</v>
-      </c>
+      <c r="A450" s="4"/>
+      <c r="B450" s="4"/>
     </row>
     <row r="451" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A451" s="4">
-        <v>1010052319</v>
-      </c>
-      <c r="B451" s="4" t="s">
-        <v>449</v>
-      </c>
+      <c r="A451" s="4"/>
+      <c r="B451" s="4"/>
     </row>
     <row r="452" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A452" s="4">
-        <v>1010052320</v>
-      </c>
-      <c r="B452" s="4" t="s">
-        <v>450</v>
-      </c>
+      <c r="A452" s="4"/>
+      <c r="B452" s="4"/>
     </row>
     <row r="453" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A453" s="4">
-        <v>1030000370</v>
-      </c>
-      <c r="B453" s="4" t="s">
-        <v>451</v>
-      </c>
+      <c r="A453" s="4"/>
+      <c r="B453" s="4"/>
     </row>
     <row r="454" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="4">
-        <v>1030000366</v>
-      </c>
-      <c r="B454" s="4" t="s">
-        <v>452</v>
-      </c>
+      <c r="A454" s="4"/>
+      <c r="B454" s="4"/>
     </row>
     <row r="455" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A455" s="4">
-        <v>1030000368</v>
-      </c>
-      <c r="B455" s="4" t="s">
-        <v>453</v>
-      </c>
+      <c r="A455" s="4"/>
+      <c r="B455" s="4"/>
     </row>
     <row r="456" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A456" s="4">
-        <v>1030000369</v>
-      </c>
-      <c r="B456" s="4" t="s">
-        <v>454</v>
-      </c>
+      <c r="A456" s="4"/>
+      <c r="B456" s="4"/>
     </row>
     <row r="457" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A457" s="4">
-        <v>1030000489</v>
-      </c>
-      <c r="B457" s="4" t="s">
-        <v>455</v>
-      </c>
+      <c r="A457" s="4"/>
+      <c r="B457" s="4"/>
     </row>
     <row r="458" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A458" s="4">
-        <v>1030000490</v>
-      </c>
-      <c r="B458" s="4" t="s">
-        <v>456</v>
-      </c>
+      <c r="A458" s="4"/>
+      <c r="B458" s="4"/>
     </row>
     <row r="459" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A459" s="4">
-        <v>1030000821</v>
-      </c>
-      <c r="B459" s="4" t="s">
-        <v>457</v>
-      </c>
+      <c r="A459" s="4"/>
+      <c r="B459" s="4"/>
     </row>
     <row r="460" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A460" s="4">
-        <v>1030000511</v>
-      </c>
-      <c r="B460" s="6" t="s">
-        <v>458</v>
-      </c>
+      <c r="A460" s="4"/>
+      <c r="B460" s="6"/>
     </row>
     <row r="461" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A461" s="7">
-        <v>433720</v>
-      </c>
-      <c r="B461" s="6" t="s">
-        <v>459</v>
-      </c>
+      <c r="A461" s="7"/>
+      <c r="B461" s="6"/>
     </row>
     <row r="462" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A462" s="7">
-        <v>1010004281</v>
-      </c>
-      <c r="B462" s="4" t="s">
-        <v>460</v>
-      </c>
+      <c r="A462" s="7"/>
+      <c r="B462" s="4"/>
     </row>
     <row r="463" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A463" s="4">
-        <v>1010022118</v>
-      </c>
-      <c r="B463" s="3" t="s">
-        <v>461</v>
-      </c>
+      <c r="A463" s="4"/>
+      <c r="B463" s="3"/>
     </row>
     <row r="464" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A464" s="4">
-        <v>1020000874</v>
-      </c>
-      <c r="B464" s="4" t="s">
-        <v>462</v>
-      </c>
+      <c r="A464" s="4"/>
+      <c r="B464" s="4"/>
     </row>
     <row r="465" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A465" s="4">
-        <v>1020001568</v>
-      </c>
-      <c r="B465" s="4" t="s">
-        <v>463</v>
-      </c>
+      <c r="A465" s="4"/>
+      <c r="B465" s="4"/>
     </row>
     <row r="466" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A466" s="4">
-        <v>1020001569</v>
-      </c>
-      <c r="B466" s="4" t="s">
-        <v>464</v>
-      </c>
+      <c r="A466" s="4"/>
+      <c r="B466" s="4"/>
     </row>
     <row r="467" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A467" s="4">
-        <v>1020000317</v>
-      </c>
-      <c r="B467" s="4" t="s">
-        <v>465</v>
-      </c>
+      <c r="A467" s="4"/>
+      <c r="B467" s="4"/>
     </row>
     <row r="468" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A468" s="4">
-        <v>1020001570</v>
-      </c>
-      <c r="B468" s="4" t="s">
-        <v>466</v>
-      </c>
+      <c r="A468" s="4"/>
+      <c r="B468" s="4"/>
     </row>
     <row r="469" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A469" s="4">
-        <v>1020001711</v>
-      </c>
-      <c r="B469" s="4" t="s">
-        <v>467</v>
-      </c>
+      <c r="A469" s="4"/>
+      <c r="B469" s="4"/>
     </row>
     <row r="470" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A470" s="4">
-        <v>1020001712</v>
-      </c>
-      <c r="B470" s="4" t="s">
-        <v>468</v>
-      </c>
+      <c r="A470" s="4"/>
+      <c r="B470" s="4"/>
     </row>
     <row r="471" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A471" s="4">
-        <v>1020001612</v>
-      </c>
-      <c r="B471" s="4" t="s">
-        <v>469</v>
-      </c>
+      <c r="A471" s="4"/>
+      <c r="B471" s="4"/>
     </row>
     <row r="472" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A472" s="4">
-        <v>1020001713</v>
-      </c>
-      <c r="B472" s="4" t="s">
-        <v>470</v>
-      </c>
+      <c r="A472" s="4"/>
+      <c r="B472" s="4"/>
     </row>
     <row r="473" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A473" s="4">
-        <v>1020001613</v>
-      </c>
-      <c r="B473" s="4" t="s">
-        <v>471</v>
-      </c>
+      <c r="A473" s="4"/>
+      <c r="B473" s="4"/>
     </row>
     <row r="474" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A474" s="4">
-        <v>1020001714</v>
-      </c>
-      <c r="B474" s="4" t="s">
-        <v>472</v>
-      </c>
+      <c r="A474" s="4"/>
+      <c r="B474" s="4"/>
     </row>
     <row r="475" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A475" s="4">
-        <v>1020001715</v>
-      </c>
-      <c r="B475" s="4" t="s">
-        <v>473</v>
-      </c>
+      <c r="A475" s="4"/>
+      <c r="B475" s="4"/>
     </row>
     <row r="476" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A476" s="4">
-        <v>306792</v>
-      </c>
-      <c r="B476" s="4" t="s">
-        <v>474</v>
-      </c>
+      <c r="A476" s="4"/>
+      <c r="B476" s="4"/>
     </row>
     <row r="477" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A477" s="4">
-        <v>306791</v>
-      </c>
-      <c r="B477" s="4" t="s">
-        <v>475</v>
-      </c>
+      <c r="A477" s="4"/>
+      <c r="B477" s="4"/>
     </row>
     <row r="478" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="4">
-        <v>306790</v>
-      </c>
-      <c r="B478" s="4" t="s">
-        <v>476</v>
-      </c>
+      <c r="A478" s="4"/>
+      <c r="B478" s="4"/>
     </row>
     <row r="479" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A479" s="4">
-        <v>306788</v>
-      </c>
-      <c r="B479" s="4" t="s">
-        <v>477</v>
-      </c>
+      <c r="A479" s="4"/>
+      <c r="B479" s="4"/>
     </row>
     <row r="480" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="4">
-        <v>41673</v>
-      </c>
-      <c r="B480" s="4" t="s">
-        <v>478</v>
-      </c>
+      <c r="A480" s="4"/>
+      <c r="B480" s="4"/>
     </row>
     <row r="481" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A481" s="4">
-        <v>138818</v>
-      </c>
-      <c r="B481" s="4" t="s">
-        <v>479</v>
-      </c>
+      <c r="A481" s="4"/>
+      <c r="B481" s="4"/>
     </row>
     <row r="482" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A482" s="4">
-        <v>138817</v>
-      </c>
-      <c r="B482" s="4" t="s">
-        <v>480</v>
-      </c>
+      <c r="A482" s="4"/>
+      <c r="B482" s="4"/>
     </row>
     <row r="483" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="4">
-        <v>267476</v>
-      </c>
-      <c r="B483" s="4" t="s">
-        <v>481</v>
-      </c>
+      <c r="A483" s="4"/>
+      <c r="B483" s="4"/>
     </row>
     <row r="484" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="4">
-        <v>1020001263</v>
-      </c>
-      <c r="B484" s="4" t="s">
-        <v>482</v>
-      </c>
+      <c r="A484" s="4"/>
+      <c r="B484" s="4"/>
     </row>
     <row r="485" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A485" s="4">
-        <v>1020001266</v>
-      </c>
-      <c r="B485" s="4" t="s">
-        <v>483</v>
-      </c>
+      <c r="A485" s="4"/>
+      <c r="B485" s="4"/>
     </row>
     <row r="486" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A486" s="4">
-        <v>1020001042</v>
-      </c>
-      <c r="B486" s="4" t="s">
-        <v>484</v>
-      </c>
+      <c r="A486" s="4"/>
+      <c r="B486" s="4"/>
     </row>
     <row r="487" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A487" s="4">
-        <v>1020001265</v>
-      </c>
-      <c r="B487" s="4" t="s">
-        <v>485</v>
-      </c>
+      <c r="A487" s="4"/>
+      <c r="B487" s="4"/>
     </row>
     <row r="488" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A488" s="4">
-        <v>1020001271</v>
-      </c>
-      <c r="B488" s="4" t="s">
-        <v>486</v>
-      </c>
+      <c r="A488" s="4"/>
+      <c r="B488" s="4"/>
     </row>
     <row r="489" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A489" s="4">
-        <v>1020001137</v>
-      </c>
-      <c r="B489" s="4" t="s">
-        <v>487</v>
-      </c>
+      <c r="A489" s="4"/>
+      <c r="B489" s="4"/>
     </row>
     <row r="490" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A490" s="4">
-        <v>1020001071</v>
-      </c>
-      <c r="B490" s="4" t="s">
-        <v>488</v>
-      </c>
+      <c r="A490" s="4"/>
+      <c r="B490" s="4"/>
     </row>
     <row r="491" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A491" s="4">
-        <v>1020001259</v>
-      </c>
-      <c r="B491" s="4" t="s">
-        <v>489</v>
-      </c>
+      <c r="A491" s="4"/>
+      <c r="B491" s="4"/>
     </row>
     <row r="492" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A492" s="4">
-        <v>77390</v>
-      </c>
-      <c r="B492" s="4" t="s">
-        <v>490</v>
-      </c>
+      <c r="A492" s="4"/>
+      <c r="B492" s="4"/>
     </row>
     <row r="493" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A493" s="4">
-        <v>77391</v>
-      </c>
-      <c r="B493" s="4" t="s">
-        <v>491</v>
-      </c>
+      <c r="A493" s="4"/>
+      <c r="B493" s="4"/>
     </row>
     <row r="494" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A494" s="4">
-        <v>1020000379</v>
-      </c>
-      <c r="B494" s="4" t="s">
-        <v>492</v>
-      </c>
+      <c r="A494" s="4"/>
+      <c r="B494" s="4"/>
     </row>
     <row r="495" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A495" s="4">
-        <v>1020000380</v>
-      </c>
-      <c r="B495" s="4" t="s">
-        <v>493</v>
-      </c>
+      <c r="A495" s="4"/>
+      <c r="B495" s="4"/>
     </row>
     <row r="496" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A496" s="4">
-        <v>1020000382</v>
-      </c>
-      <c r="B496" s="4" t="s">
-        <v>494</v>
-      </c>
+      <c r="A496" s="4"/>
+      <c r="B496" s="4"/>
     </row>
     <row r="497" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A497" s="4">
-        <v>26479</v>
-      </c>
-      <c r="B497" s="4" t="s">
-        <v>495</v>
-      </c>
+      <c r="A497" s="4"/>
+      <c r="B497" s="4"/>
     </row>
     <row r="498" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A498" s="4">
-        <v>167151</v>
-      </c>
-      <c r="B498" s="20" t="s">
-        <v>496</v>
-      </c>
+      <c r="A498" s="4"/>
+      <c r="B498" s="20"/>
     </row>
     <row r="499" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A499" s="4">
-        <v>1020001294</v>
-      </c>
-      <c r="B499" s="20" t="s">
-        <v>497</v>
-      </c>
+      <c r="A499" s="4"/>
+      <c r="B499" s="20"/>
     </row>
     <row r="500" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A500" s="4">
-        <v>1020001304</v>
-      </c>
-      <c r="B500" s="20" t="s">
-        <v>498</v>
-      </c>
+      <c r="A500" s="4"/>
+      <c r="B500" s="20"/>
     </row>
     <row r="501" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A501" s="4">
-        <v>1020001237</v>
-      </c>
-      <c r="B501" s="20" t="s">
-        <v>499</v>
-      </c>
+      <c r="A501" s="4"/>
+      <c r="B501" s="20"/>
     </row>
     <row r="502" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A502" s="4">
-        <v>1020001277</v>
-      </c>
-      <c r="B502" s="4" t="s">
-        <v>500</v>
-      </c>
+      <c r="A502" s="4"/>
+      <c r="B502" s="4"/>
     </row>
     <row r="503" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A503" s="4">
-        <v>1020001273</v>
-      </c>
-      <c r="B503" s="4" t="s">
-        <v>501</v>
-      </c>
+      <c r="A503" s="4"/>
+      <c r="B503" s="4"/>
     </row>
     <row r="504" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A504" s="4">
-        <v>1020001316</v>
-      </c>
-      <c r="B504" s="4" t="s">
-        <v>502</v>
-      </c>
+      <c r="A504" s="4"/>
+      <c r="B504" s="4"/>
     </row>
     <row r="505" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A505" s="4">
-        <v>1020001332</v>
-      </c>
-      <c r="B505" s="4" t="s">
-        <v>503</v>
-      </c>
+      <c r="A505" s="4"/>
+      <c r="B505" s="4"/>
     </row>
     <row r="506" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A506" s="4">
-        <v>74648</v>
-      </c>
-      <c r="B506" s="4" t="s">
-        <v>504</v>
-      </c>
+      <c r="A506" s="4"/>
+      <c r="B506" s="4"/>
     </row>
     <row r="507" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A507" s="4">
-        <v>1020001306</v>
-      </c>
-      <c r="B507" s="4" t="s">
-        <v>505</v>
-      </c>
+      <c r="A507" s="4"/>
+      <c r="B507" s="4"/>
     </row>
     <row r="508" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A508" s="4">
-        <v>1020001471</v>
-      </c>
-      <c r="B508" s="4" t="s">
-        <v>506</v>
-      </c>
+      <c r="A508" s="4"/>
+      <c r="B508" s="4"/>
     </row>
     <row r="509" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A509" s="4">
-        <v>1020001308</v>
-      </c>
-      <c r="B509" s="4" t="s">
-        <v>507</v>
-      </c>
+      <c r="A509" s="4"/>
+      <c r="B509" s="4"/>
     </row>
     <row r="510" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A510" s="4">
-        <v>297007</v>
-      </c>
-      <c r="B510" s="4" t="s">
-        <v>508</v>
-      </c>
+      <c r="A510" s="4"/>
+      <c r="B510" s="4"/>
     </row>
     <row r="511" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A511" s="4">
-        <v>1020001102</v>
-      </c>
-      <c r="B511" s="4" t="s">
-        <v>509</v>
-      </c>
+      <c r="A511" s="4"/>
+      <c r="B511" s="4"/>
     </row>
     <row r="512" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A512" s="4">
-        <v>1020001240</v>
-      </c>
-      <c r="B512" s="4" t="s">
-        <v>510</v>
-      </c>
+      <c r="A512" s="4"/>
+      <c r="B512" s="4"/>
     </row>
     <row r="513" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A513" s="4">
-        <v>1020001319</v>
-      </c>
-      <c r="B513" s="4" t="s">
-        <v>511</v>
-      </c>
+      <c r="A513" s="4"/>
+      <c r="B513" s="4"/>
     </row>
     <row r="514" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A514" s="4">
-        <v>1020001365</v>
-      </c>
-      <c r="B514" s="4" t="s">
-        <v>512</v>
-      </c>
+      <c r="A514" s="4"/>
+      <c r="B514" s="4"/>
     </row>
     <row r="515" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A515" s="4">
-        <v>1020001124</v>
-      </c>
-      <c r="B515" s="4" t="s">
-        <v>513</v>
-      </c>
+      <c r="A515" s="4"/>
+      <c r="B515" s="4"/>
     </row>
     <row r="516" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A516" s="4">
-        <v>1020001122</v>
-      </c>
-      <c r="B516" s="4" t="s">
-        <v>514</v>
-      </c>
+      <c r="A516" s="4"/>
+      <c r="B516" s="4"/>
     </row>
     <row r="517" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A517" s="4">
-        <v>1020001323</v>
-      </c>
-      <c r="B517" s="4" t="s">
-        <v>515</v>
-      </c>
+      <c r="A517" s="4"/>
+      <c r="B517" s="4"/>
     </row>
     <row r="518" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A518" s="4">
-        <v>1020001325</v>
-      </c>
-      <c r="B518" s="4" t="s">
-        <v>516</v>
-      </c>
+      <c r="A518" s="4"/>
+      <c r="B518" s="4"/>
     </row>
     <row r="519" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A519" s="4">
-        <v>1020001127</v>
-      </c>
-      <c r="B519" s="4" t="s">
-        <v>517</v>
-      </c>
+      <c r="A519" s="4"/>
+      <c r="B519" s="4"/>
     </row>
     <row r="520" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A520" s="4">
-        <v>1020001229</v>
-      </c>
-      <c r="B520" s="4" t="s">
-        <v>518</v>
-      </c>
+      <c r="A520" s="4"/>
+      <c r="B520" s="4"/>
     </row>
     <row r="521" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A521" s="4">
-        <v>1010028657</v>
-      </c>
-      <c r="B521" s="4" t="s">
-        <v>519</v>
-      </c>
+      <c r="A521" s="4"/>
+      <c r="B521" s="4"/>
     </row>
     <row r="522" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A522" s="11">
-        <v>1010028655</v>
-      </c>
-      <c r="B522" s="4" t="s">
-        <v>520</v>
-      </c>
+      <c r="A522" s="11"/>
+      <c r="B522" s="4"/>
     </row>
     <row r="523" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A523" s="11">
-        <v>145165</v>
-      </c>
-      <c r="B523" s="4" t="s">
-        <v>521</v>
-      </c>
+      <c r="A523" s="11"/>
+      <c r="B523" s="4"/>
     </row>
     <row r="524" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A524" s="4">
-        <v>51666</v>
-      </c>
-      <c r="B524" s="4" t="s">
-        <v>522</v>
-      </c>
+      <c r="A524" s="4"/>
+      <c r="B524" s="4"/>
     </row>
     <row r="525" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A525" s="11">
-        <v>1010080930</v>
-      </c>
-      <c r="B525" s="4" t="s">
-        <v>523</v>
-      </c>
+      <c r="A525" s="11"/>
+      <c r="B525" s="4"/>
     </row>
     <row r="526" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A526" s="4">
-        <v>161055</v>
-      </c>
-      <c r="B526" s="4" t="s">
-        <v>524</v>
-      </c>
+      <c r="A526" s="4"/>
+      <c r="B526" s="4"/>
     </row>
     <row r="527" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A527" s="4">
-        <v>1010050517</v>
-      </c>
-      <c r="B527" s="4" t="s">
-        <v>525</v>
-      </c>
+      <c r="A527" s="4"/>
+      <c r="B527" s="4"/>
     </row>
     <row r="528" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A528" s="4">
-        <v>176190</v>
-      </c>
-      <c r="B528" s="4" t="s">
-        <v>526</v>
-      </c>
+      <c r="A528" s="4"/>
+      <c r="B528" s="4"/>
     </row>
     <row r="529" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A529" s="4">
-        <v>267271</v>
-      </c>
-      <c r="B529" s="4" t="s">
-        <v>527</v>
-      </c>
+      <c r="A529" s="4"/>
+      <c r="B529" s="4"/>
     </row>
     <row r="530" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A530" s="10">
-        <v>1010008416</v>
-      </c>
-      <c r="B530" s="4" t="s">
-        <v>528</v>
-      </c>
+      <c r="A530" s="10"/>
+      <c r="B530" s="4"/>
     </row>
     <row r="531" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A531" s="21">
-        <v>1010018372</v>
-      </c>
-      <c r="B531" s="4" t="s">
-        <v>529</v>
-      </c>
+      <c r="A531" s="21"/>
+      <c r="B531" s="4"/>
     </row>
     <row r="532" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A532" s="21">
-        <v>1010018361</v>
-      </c>
-      <c r="B532" s="6" t="s">
-        <v>530</v>
-      </c>
+      <c r="A532" s="21"/>
+      <c r="B532" s="6"/>
     </row>
     <row r="533" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A533" s="7">
-        <v>1010055398</v>
-      </c>
-      <c r="B533" s="11" t="s">
-        <v>531</v>
-      </c>
+      <c r="A533" s="7"/>
+      <c r="B533" s="11"/>
     </row>
     <row r="534" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A534" s="4">
-        <v>422131</v>
-      </c>
-      <c r="B534" s="4" t="s">
-        <v>532</v>
-      </c>
+      <c r="A534" s="4"/>
+      <c r="B534" s="4"/>
     </row>
     <row r="535" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A535" s="4">
-        <v>113863</v>
-      </c>
-      <c r="B535" s="4" t="s">
-        <v>533</v>
-      </c>
+      <c r="A535" s="4"/>
+      <c r="B535" s="4"/>
     </row>
     <row r="536" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A536" s="4">
-        <v>422759</v>
-      </c>
-      <c r="B536" s="4" t="s">
-        <v>534</v>
-      </c>
+      <c r="A536" s="4"/>
+      <c r="B536" s="4"/>
     </row>
     <row r="537" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A537" s="4">
-        <v>120955</v>
-      </c>
-      <c r="B537" s="4" t="s">
-        <v>535</v>
-      </c>
+      <c r="A537" s="4"/>
+      <c r="B537" s="4"/>
     </row>
     <row r="538" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A538" s="4">
-        <v>1010000896</v>
-      </c>
-      <c r="B538" s="4" t="s">
-        <v>536</v>
-      </c>
+      <c r="A538" s="4"/>
+      <c r="B538" s="4"/>
     </row>
     <row r="539" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A539" s="4">
-        <v>422793</v>
-      </c>
-      <c r="B539" s="4" t="s">
-        <v>537</v>
-      </c>
+      <c r="A539" s="4"/>
+      <c r="B539" s="4"/>
     </row>
     <row r="540" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A540" s="4">
-        <v>42607</v>
-      </c>
-      <c r="B540" s="4" t="s">
-        <v>538</v>
-      </c>
+      <c r="A540" s="4"/>
+      <c r="B540" s="4"/>
     </row>
     <row r="541" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" s="17"/>

--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="18" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E773DA3B-55AF-49D2-93F9-A3811158B3A4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4155" yWindow="4155" windowWidth="15900" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -1553,10 +1553,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/catalogoPecas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E773DA3B-55AF-49D2-93F9-A3811158B3A4}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F4B1027-81F3-421D-8E75-5DEFB80CE880}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4155" yWindow="4155" windowWidth="15900" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3900" yWindow="3900" windowWidth="12150" windowHeight="20745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -489,12 +489,6 @@
     <t>KIT TAPA PO RANDON (PAR DE ESPELHO)</t>
   </si>
   <si>
-    <t>KIT TAPA PO FACCHINI LE (PAR DE ESPELHO)</t>
-  </si>
-  <si>
-    <t>KIT TAPA PO FACCHINI LD (PAR DE ESPELHO)</t>
-  </si>
-  <si>
     <t>LOCTITTE (TRAVA PARAFUSO)</t>
   </si>
   <si>
@@ -1315,6 +1309,12 @@
   </si>
   <si>
     <t>material</t>
+  </si>
+  <si>
+    <t>KIT TAPA PO FACCHINI LE (ESPELHO)</t>
+  </si>
+  <si>
+    <t>KIT TAPA PO FACCHINI LD (ESPELHO)</t>
   </si>
 </sst>
 </file>
@@ -1553,6 +1553,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1827,10 +1831,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -2422,7 +2426,7 @@
         <v>341430</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3078,7 +3082,7 @@
         <v>1040097070</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>154</v>
+        <v>428</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3086,7 +3090,7 @@
         <v>1040097068</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>155</v>
+        <v>429</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3094,7 +3098,7 @@
         <v>22004</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3102,7 +3106,7 @@
         <v>1010058554</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3110,7 +3114,7 @@
         <v>1010027308</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3118,7 +3122,7 @@
         <v>1040077383</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3126,7 +3130,7 @@
         <v>1010025482</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3134,7 +3138,7 @@
         <v>1010025509</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3142,7 +3146,7 @@
         <v>1010027789</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3150,7 +3154,7 @@
         <v>1010027790</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3158,7 +3162,7 @@
         <v>1010018301</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3166,7 +3170,7 @@
         <v>1010031616</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3174,7 +3178,7 @@
         <v>1010053728</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3182,7 +3186,7 @@
         <v>1010020758</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3190,7 +3194,7 @@
         <v>1010020781</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3198,7 +3202,7 @@
         <v>1010058426</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3206,7 +3210,7 @@
         <v>1010059332</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3214,7 +3218,7 @@
         <v>1040077389</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3222,7 +3226,7 @@
         <v>1010021364</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3230,7 +3234,7 @@
         <v>1010021541</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3238,7 +3242,7 @@
         <v>1010021955</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3246,7 +3250,7 @@
         <v>1040077388</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3254,7 +3258,7 @@
         <v>1010058100</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3262,7 +3266,7 @@
         <v>1010020524</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3270,7 +3274,7 @@
         <v>1010021958</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3278,7 +3282,7 @@
         <v>1010019756</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3286,7 +3290,7 @@
         <v>1010019752</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3294,7 +3298,7 @@
         <v>409639</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3302,7 +3306,7 @@
         <v>1010047089</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3310,7 +3314,7 @@
         <v>1040084107</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3318,7 +3322,7 @@
         <v>405588</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3326,7 +3330,7 @@
         <v>424298</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3334,7 +3338,7 @@
         <v>421847</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3342,7 +3346,7 @@
         <v>431573</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3350,7 +3354,7 @@
         <v>1010021581</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3358,7 +3362,7 @@
         <v>412413</v>
       </c>
       <c r="B192" s="14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3366,7 +3370,7 @@
         <v>1010022606</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3374,7 +3378,7 @@
         <v>1010003527</v>
       </c>
       <c r="B194" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3382,7 +3386,7 @@
         <v>422027</v>
       </c>
       <c r="B195" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3390,7 +3394,7 @@
         <v>1010011313</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3398,7 +3402,7 @@
         <v>27051</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3406,7 +3410,7 @@
         <v>1010011304</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3414,7 +3418,7 @@
         <v>35659</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3422,7 +3426,7 @@
         <v>1040077390</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="201" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3430,7 +3434,7 @@
         <v>1010021542</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3438,7 +3442,7 @@
         <v>1010021733</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3446,7 +3450,7 @@
         <v>1010011379</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="204" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3454,7 +3458,7 @@
         <v>1010003279</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3462,7 +3466,7 @@
         <v>1010011380</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3470,7 +3474,7 @@
         <v>351197</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3478,7 +3482,7 @@
         <v>1010011286</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3486,7 +3490,7 @@
         <v>2479</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="209" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3494,7 +3498,7 @@
         <v>1010011382</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3502,7 +3506,7 @@
         <v>1010055703</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3510,7 +3514,7 @@
         <v>4165</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3518,7 +3522,7 @@
         <v>301626</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="213" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3526,7 +3530,7 @@
         <v>429495</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="214" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3534,7 +3538,7 @@
         <v>162998</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="215" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3542,7 +3546,7 @@
         <v>432657</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3550,7 +3554,7 @@
         <v>1010021929</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3558,7 +3562,7 @@
         <v>428065</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3566,7 +3570,7 @@
         <v>1010003404</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3574,7 +3578,7 @@
         <v>1010003322</v>
       </c>
       <c r="B219" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3582,7 +3586,7 @@
         <v>17738</v>
       </c>
       <c r="B220" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3590,7 +3594,7 @@
         <v>270373</v>
       </c>
       <c r="B221" s="14" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3598,7 +3602,7 @@
         <v>1040077391</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3606,7 +3610,7 @@
         <v>1010058624</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3614,7 +3618,7 @@
         <v>1010024661</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3622,7 +3626,7 @@
         <v>1040019315</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3630,7 +3634,7 @@
         <v>1010021089</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3638,7 +3642,7 @@
         <v>1040017264</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3646,7 +3650,7 @@
         <v>1010051765</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3654,7 +3658,7 @@
         <v>1010035272</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3662,7 +3666,7 @@
         <v>1040077392</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3670,7 +3674,7 @@
         <v>1040077393</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3678,7 +3682,7 @@
         <v>1040077395</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3686,7 +3690,7 @@
         <v>1040077401</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3694,7 +3698,7 @@
         <v>27572</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3702,7 +3706,7 @@
         <v>18745</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3710,7 +3714,7 @@
         <v>1040077396</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3718,7 +3722,7 @@
         <v>1010036546</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3726,7 +3730,7 @@
         <v>1010014049</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3734,7 +3738,7 @@
         <v>1010025148</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3742,7 +3746,7 @@
         <v>1040077394</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3750,7 +3754,7 @@
         <v>1040077400</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3758,7 +3762,7 @@
         <v>1040079329</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3766,7 +3770,7 @@
         <v>1040040957</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3774,7 +3778,7 @@
         <v>1040077398</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3782,7 +3786,7 @@
         <v>1010031545</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3790,7 +3794,7 @@
         <v>1010053128</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3798,7 +3802,7 @@
         <v>1010010599</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3806,7 +3810,7 @@
         <v>1010056064</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3814,7 +3818,7 @@
         <v>5389</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3822,7 +3826,7 @@
         <v>264250</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3830,7 +3834,7 @@
         <v>1010055970</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3838,7 +3842,7 @@
         <v>181395</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3846,7 +3850,7 @@
         <v>1010055962</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3854,7 +3858,7 @@
         <v>1010003578</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3862,7 +3866,7 @@
         <v>332891</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3870,7 +3874,7 @@
         <v>17727</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3878,7 +3882,7 @@
         <v>17918</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3886,7 +3890,7 @@
         <v>1010020554</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="259" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3894,7 +3898,7 @@
         <v>1040085949</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="260" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3902,7 +3906,7 @@
         <v>1010062938</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="261" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3910,7 +3914,7 @@
         <v>1010062086</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="262" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3918,7 +3922,7 @@
         <v>1010062087</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="263" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3926,7 +3930,7 @@
         <v>1040077373</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3934,7 +3938,7 @@
         <v>1040077372</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3942,7 +3946,7 @@
         <v>1040097154</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="266" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3950,7 +3954,7 @@
         <v>1010042579</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3958,7 +3962,7 @@
         <v>1010029427</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3966,7 +3970,7 @@
         <v>133108</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3974,7 +3978,7 @@
         <v>269427</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="270" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3982,7 +3986,7 @@
         <v>298227</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3990,7 +3994,7 @@
         <v>1010062285</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="272" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -3998,7 +4002,7 @@
         <v>1010058052</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="273" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4006,7 +4010,7 @@
         <v>1010050033</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4014,7 +4018,7 @@
         <v>1040098869</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="275" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4022,7 +4026,7 @@
         <v>1010056523</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="276" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4030,7 +4034,7 @@
         <v>1010062045</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="277" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4038,7 +4042,7 @@
         <v>1040097575</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="278" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4046,7 +4050,7 @@
         <v>1040098437</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="279" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4054,7 +4058,7 @@
         <v>1010040346</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="280" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4062,7 +4066,7 @@
         <v>1010021543</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="281" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4070,7 +4074,7 @@
         <v>1040077397</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="282" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4078,7 +4082,7 @@
         <v>1040094213</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="283" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4086,7 +4090,7 @@
         <v>406060</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="284" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4094,7 +4098,7 @@
         <v>1010042564</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="285" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4102,7 +4106,7 @@
         <v>1010042688</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="286" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4110,7 +4114,7 @@
         <v>1010040133</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="287" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4118,7 +4122,7 @@
         <v>1010039879</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="288" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4126,7 +4130,7 @@
         <v>62608</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="289" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4134,7 +4138,7 @@
         <v>1040098603</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="290" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4142,7 +4146,7 @@
         <v>1040017266</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="291" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4150,7 +4154,7 @@
         <v>1010063326</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="292" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4158,7 +4162,7 @@
         <v>1010050574</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="293" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4166,7 +4170,7 @@
         <v>1040087856</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="294" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4174,7 +4178,7 @@
         <v>1040019838</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="295" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4182,7 +4186,7 @@
         <v>1010042882</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="296" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4190,7 +4194,7 @@
         <v>1010042873</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="297" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4198,7 +4202,7 @@
         <v>1010059549</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="298" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4206,7 +4210,7 @@
         <v>1010020552</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="299" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4214,7 +4218,7 @@
         <v>1040078895</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="300" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4222,7 +4226,7 @@
         <v>1040024309</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="301" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4230,7 +4234,7 @@
         <v>1040024323</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="302" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4238,7 +4242,7 @@
         <v>1040024322</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="303" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4246,7 +4250,7 @@
         <v>417694</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="304" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4254,7 +4258,7 @@
         <v>1010059685</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="305" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4262,7 +4266,7 @@
         <v>1010059687</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="306" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4270,7 +4274,7 @@
         <v>1010077469</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="307" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4278,15 +4282,15 @@
         <v>1010077470</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="308" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B308" s="14" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="309" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4294,7 +4298,7 @@
         <v>1010084108</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="310" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4302,7 +4306,7 @@
         <v>1040043537</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="311" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4310,7 +4314,7 @@
         <v>1010046401</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="312" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4318,7 +4322,7 @@
         <v>1010062007</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="313" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4326,7 +4330,7 @@
         <v>1010051284</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="314" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4334,7 +4338,7 @@
         <v>1010027788</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="315" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4342,7 +4346,7 @@
         <v>1010027786</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="316" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4350,7 +4354,7 @@
         <v>1010026889</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="317" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4358,7 +4362,7 @@
         <v>1010042358</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="318" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4366,7 +4370,7 @@
         <v>1040023848</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="319" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4374,7 +4378,7 @@
         <v>1010042341</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="320" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4382,7 +4386,7 @@
         <v>1040023858</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="321" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4390,7 +4394,7 @@
         <v>1040023843</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="322" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4398,7 +4402,7 @@
         <v>1040077411</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="323" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4406,7 +4410,7 @@
         <v>1040077410</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="324" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4414,7 +4418,7 @@
         <v>1010062008</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="325" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4422,7 +4426,7 @@
         <v>1040040960</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="326" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4430,7 +4434,7 @@
         <v>409578</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="327" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4438,7 +4442,7 @@
         <v>1040077360</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="328" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4446,7 +4450,7 @@
         <v>1010064470</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="329" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4454,7 +4458,7 @@
         <v>1010021991</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="330" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4462,7 +4466,7 @@
         <v>1010021960</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="331" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4470,7 +4474,7 @@
         <v>1010031545</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="332" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4478,7 +4482,7 @@
         <v>1010022590</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="333" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4486,13 +4490,13 @@
         <v>1040098643</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="334" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" s="4"/>
       <c r="B334" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="335" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4500,7 +4504,7 @@
         <v>1010046550</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="336" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4508,7 +4512,7 @@
         <v>1010046402</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="337" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4516,7 +4520,7 @@
         <v>1010060291</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="338" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4524,7 +4528,7 @@
         <v>1010050920</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="339" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4532,7 +4536,7 @@
         <v>1040077412</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="340" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4540,7 +4544,7 @@
         <v>1010042609</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="341" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4548,7 +4552,7 @@
         <v>417701</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="342" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4556,7 +4560,7 @@
         <v>399384</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="343" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4564,7 +4568,7 @@
         <v>1040077345</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="344" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4572,7 +4576,7 @@
         <v>297290</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="345" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4580,7 +4584,7 @@
         <v>399253</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="346" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4588,7 +4592,7 @@
         <v>377363</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="347" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4596,7 +4600,7 @@
         <v>405556</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="348" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4604,7 +4608,7 @@
         <v>405590</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="349" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4612,7 +4616,7 @@
         <v>405591</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="350" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4620,7 +4624,7 @@
         <v>1010003966</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="351" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4628,7 +4632,7 @@
         <v>1010003967</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="352" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4636,7 +4640,7 @@
         <v>65219</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="353" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4644,7 +4648,7 @@
         <v>10168</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="354" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4652,7 +4656,7 @@
         <v>180778</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="355" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4660,7 +4664,7 @@
         <v>1040077414</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="356" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4668,7 +4672,7 @@
         <v>1010018482</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="357" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4676,7 +4680,7 @@
         <v>409903</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="358" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4684,7 +4688,7 @@
         <v>418427</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="359" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4692,7 +4696,7 @@
         <v>1010027285</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="360" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4700,7 +4704,7 @@
         <v>1040077413</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="361" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4708,7 +4712,7 @@
         <v>416554</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="362" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4716,7 +4720,7 @@
         <v>1010022819</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="363" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4724,7 +4728,7 @@
         <v>1010052853</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="364" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4732,7 +4736,7 @@
         <v>433362</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="365" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4740,7 +4744,7 @@
         <v>1010008578</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="366" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4748,7 +4752,7 @@
         <v>1010031694</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="367" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4756,7 +4760,7 @@
         <v>1010051997</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="368" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4764,7 +4768,7 @@
         <v>1010022601</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
     </row>
     <row r="369" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4772,7 +4776,7 @@
         <v>1010054278</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="370" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4780,7 +4784,7 @@
         <v>1010083462</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="371" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4788,7 +4792,7 @@
         <v>1010027772</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="372" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4796,7 +4800,7 @@
         <v>300186</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="373" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4804,7 +4808,7 @@
         <v>214055</v>
       </c>
       <c r="B373" s="14" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="374" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4812,7 +4816,7 @@
         <v>1010021956</v>
       </c>
       <c r="B374" s="14" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="375" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4820,7 +4824,7 @@
         <v>1010026464</v>
       </c>
       <c r="B375" s="14" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="376" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4828,7 +4832,7 @@
         <v>1010021957</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="377" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4836,7 +4840,7 @@
         <v>1010026462</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="378" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4844,7 +4848,7 @@
         <v>1010026551</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="379" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4852,7 +4856,7 @@
         <v>1010042554</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="380" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4860,7 +4864,7 @@
         <v>1010039904</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="381" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4868,7 +4872,7 @@
         <v>1010060205</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="382" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4876,7 +4880,7 @@
         <v>1010060206</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="383" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4884,7 +4888,7 @@
         <v>1010077431</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="384" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4892,7 +4896,7 @@
         <v>1010077503</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="385" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4900,7 +4904,7 @@
         <v>386009</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="386" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4908,7 +4912,7 @@
         <v>1010080958</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="387" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4916,7 +4920,7 @@
         <v>20191</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="388" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4924,7 +4928,7 @@
         <v>431445</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="389" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4932,7 +4936,7 @@
         <v>431463</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="390" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4940,7 +4944,7 @@
         <v>431464</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="391" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4948,7 +4952,7 @@
         <v>1010024158</v>
       </c>
       <c r="B391" s="6" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="392" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4956,7 +4960,7 @@
         <v>1010024131</v>
       </c>
       <c r="B392" s="6" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="393" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4964,7 +4968,7 @@
         <v>1010007160</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="394" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4972,7 +4976,7 @@
         <v>1010023642</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="395" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4980,7 +4984,7 @@
         <v>1010007193</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="396" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4988,7 +4992,7 @@
         <v>1010042637</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="397" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -4996,7 +5000,7 @@
         <v>1040075323</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="398" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5004,7 +5008,7 @@
         <v>1040075324</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="399" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5012,7 +5016,7 @@
         <v>1040083312</v>
       </c>
       <c r="B399" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="400" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5020,7 +5024,7 @@
         <v>1040077661</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="401" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5028,7 +5032,7 @@
         <v>409638</v>
       </c>
       <c r="B401" s="19" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="402" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5036,7 +5040,7 @@
         <v>1040017489</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="403" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5044,7 +5048,7 @@
         <v>400174</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="404" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5052,7 +5056,7 @@
         <v>400175</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="405" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5060,7 +5064,7 @@
         <v>1040017505</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="406" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5068,7 +5072,7 @@
         <v>1040017503</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="407" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5076,7 +5080,7 @@
         <v>1010046445</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="408" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5084,7 +5088,7 @@
         <v>1010021033</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="409" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5092,7 +5096,7 @@
         <v>24950</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="410" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5100,7 +5104,7 @@
         <v>1010016356</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="411" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5108,7 +5112,7 @@
         <v>400228</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="412" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5116,7 +5120,7 @@
         <v>1010052021</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="413" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5124,7 +5128,7 @@
         <v>1040091721</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="414" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5132,7 +5136,7 @@
         <v>1010062022</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="415" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5140,7 +5144,7 @@
         <v>18336</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="416" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5148,7 +5152,7 @@
         <v>229205</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="417" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5156,7 +5160,7 @@
         <v>60671</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="418" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5164,7 +5168,7 @@
         <v>1010059726</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="419" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5172,7 +5176,7 @@
         <v>1010008144</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="420" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5180,7 +5184,7 @@
         <v>1010007244</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="421" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5188,7 +5192,7 @@
         <v>1010006827</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="422" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5196,7 +5200,7 @@
         <v>1040075426</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="423" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5204,7 +5208,7 @@
         <v>1040075427</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="424" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5212,7 +5216,7 @@
         <v>401167</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="425" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5220,7 +5224,7 @@
         <v>403459</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="426" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5228,7 +5232,7 @@
         <v>300296</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="427" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5236,7 +5240,7 @@
         <v>1010026973</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="428" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
@@ -5244,7 +5248,7 @@
         <v>1040017204</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="429" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">

--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/catalogoPecas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F4B1027-81F3-421D-8E75-5DEFB80CE880}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6DB7206-54D6-4822-8E52-88F873D306AE}"/>
   <bookViews>
-    <workbookView xWindow="3900" yWindow="3900" windowWidth="12150" windowHeight="20745" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="431">
   <si>
     <t>ABRAÇADEIRA PARALAMA VOLVO</t>
   </si>
@@ -1315,6 +1315,9 @@
   </si>
   <si>
     <t>KIT TAPA PO FACCHINI LD (ESPELHO)</t>
+  </si>
+  <si>
+    <t>TRAVA ELASTICA</t>
   </si>
 </sst>
 </file>
@@ -1345,12 +1348,14 @@
     <font>
       <sz val="12"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF242424"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1475,7 +1480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1526,17 +1531,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1822,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1659"/>
+  <dimension ref="A1:B1195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -1999,7 +2022,7 @@
     </row>
     <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>214743</v>
+        <v>1010084124</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>20</v>
@@ -2287,7 +2310,7 @@
     </row>
     <row r="58" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>417668</v>
+        <v>1010085124</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>56</v>
@@ -2447,7 +2470,7 @@
     </row>
     <row r="78" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" s="4">
-        <v>403089</v>
+        <v>1010084162</v>
       </c>
       <c r="B78" s="4" t="s">
         <v>75</v>
@@ -2455,7 +2478,7 @@
     </row>
     <row r="79" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
-        <v>403559</v>
+        <v>1010084157</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>76</v>
@@ -2463,7 +2486,7 @@
     </row>
     <row r="80" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="4">
-        <v>403560</v>
+        <v>1010084158</v>
       </c>
       <c r="B80" s="4" t="s">
         <v>77</v>
@@ -2471,7 +2494,7 @@
     </row>
     <row r="81" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="4">
-        <v>427015</v>
+        <v>1010084159</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>78</v>
@@ -2479,7 +2502,7 @@
     </row>
     <row r="82" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="4">
-        <v>403558</v>
+        <v>1010084160</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>79</v>
@@ -2487,7 +2510,7 @@
     </row>
     <row r="83" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" s="4">
-        <v>403090</v>
+        <v>1010084161</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>80</v>
@@ -2719,7 +2742,7 @@
     </row>
     <row r="112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="4">
-        <v>405589</v>
+        <v>1010084930</v>
       </c>
       <c r="B112" s="4" t="s">
         <v>109</v>
@@ -2847,7 +2870,7 @@
     </row>
     <row r="128" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
-        <v>70166</v>
+        <v>1010085344</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>125</v>
@@ -2855,7 +2878,7 @@
     </row>
     <row r="129" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
-        <v>431441</v>
+        <v>1010085383</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>126</v>
@@ -2863,7 +2886,7 @@
     </row>
     <row r="130" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="4">
-        <v>301757</v>
+        <v>1010001389</v>
       </c>
       <c r="B130" s="4" t="s">
         <v>127</v>
@@ -3319,7 +3342,7 @@
     </row>
     <row r="187" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" s="4">
-        <v>405588</v>
+        <v>1010085203</v>
       </c>
       <c r="B187" s="4" t="s">
         <v>182</v>
@@ -3591,7 +3614,7 @@
     </row>
     <row r="221" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" s="4">
-        <v>270373</v>
+        <v>1010085360</v>
       </c>
       <c r="B221" s="14" t="s">
         <v>216</v>
@@ -3823,7 +3846,7 @@
     </row>
     <row r="250" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" s="4">
-        <v>264250</v>
+        <v>1010055969</v>
       </c>
       <c r="B250" s="4" t="s">
         <v>245</v>
@@ -4087,7 +4110,7 @@
     </row>
     <row r="283" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" s="4">
-        <v>406060</v>
+        <v>1010085326</v>
       </c>
       <c r="B283" s="4" t="s">
         <v>278</v>
@@ -4247,7 +4270,7 @@
     </row>
     <row r="303" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" s="4">
-        <v>417694</v>
+        <v>1040024314</v>
       </c>
       <c r="B303" s="4" t="s">
         <v>298</v>
@@ -4564,1140 +4587,1144 @@
       </c>
     </row>
     <row r="343" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A343" s="4">
-        <v>1040077345</v>
-      </c>
-      <c r="B343" s="4" t="s">
-        <v>339</v>
+      <c r="A343" s="19">
+        <v>1010024086</v>
+      </c>
+      <c r="B343" s="19" t="s">
+        <v>430</v>
       </c>
     </row>
     <row r="344" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" s="4">
-        <v>297290</v>
+        <v>1040077345</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="345" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" s="4">
-        <v>399253</v>
+        <v>1010084315</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="346" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" s="4">
-        <v>377363</v>
+        <v>399253</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="347" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" s="4">
-        <v>405556</v>
+        <v>1010084317</v>
       </c>
       <c r="B347" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A348" s="18">
+        <v>1010085369</v>
+      </c>
+      <c r="B348" s="4" t="s">
         <v>343</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A348" s="4">
-        <v>405590</v>
-      </c>
-      <c r="B348" s="4" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="349" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" s="4">
-        <v>405591</v>
+        <v>1010085370</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="350" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" s="4">
-        <v>1010003966</v>
+        <v>1010085204</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="351" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" s="4">
-        <v>1010003967</v>
+        <v>1010003966</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="352" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" s="4">
-        <v>65219</v>
+        <v>1010003967</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="353" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" s="4">
-        <v>10168</v>
+        <v>65219</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="354" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" s="4">
-        <v>180778</v>
+        <v>10168</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="355" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" s="4">
-        <v>1040077414</v>
+        <v>1010083792</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="356" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" s="4">
-        <v>1010018482</v>
+        <v>1040077414</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="357" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" s="4">
-        <v>409903</v>
+        <v>1010018482</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="358" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" s="4">
-        <v>418427</v>
+        <v>1010084320</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="359" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" s="4">
-        <v>1010027285</v>
+        <v>1010084532</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="360" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" s="4">
-        <v>1040077413</v>
+        <v>1010027285</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="361" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" s="4">
-        <v>416554</v>
+        <v>1040077413</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="362" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" s="4">
-        <v>1010022819</v>
+        <v>1010085376</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="363" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" s="4">
-        <v>1010052853</v>
+        <v>1010022819</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="364" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" s="4">
-        <v>433362</v>
+        <v>1010052853</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="365" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" s="4">
+        <v>1010084377</v>
+      </c>
+      <c r="B365" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A366" s="20">
         <v>1010008578</v>
       </c>
-      <c r="B365" s="4" t="s">
+      <c r="B366" s="20" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="366" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A366" s="4">
+    <row r="367" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A367" s="20">
         <v>1010031694</v>
       </c>
-      <c r="B366" s="4" t="s">
+      <c r="B367" s="20" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="367" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A367" s="4">
+    <row r="368" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A368" s="20">
         <v>1010051997</v>
       </c>
-      <c r="B367" s="4" t="s">
+      <c r="B368" s="20" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="368" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A368" s="4">
+    <row r="369" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A369" s="20">
         <v>1010022601</v>
       </c>
-      <c r="B368" s="4" t="s">
+      <c r="B369" s="20" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="369" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A369" s="4">
+    <row r="370" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A370" s="20">
         <v>1010054278</v>
       </c>
-      <c r="B369" s="4" t="s">
+      <c r="B370" s="20" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="370" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A370" s="4">
+    <row r="371" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A371" s="20">
         <v>1010083462</v>
       </c>
-      <c r="B370" s="4" t="s">
+      <c r="B371" s="20" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="371" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A371" s="4">
+    <row r="372" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A372" s="20">
         <v>1010027772</v>
       </c>
-      <c r="B371" s="4" t="s">
+      <c r="B372" s="20" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="372" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A372" s="4">
-        <v>300186</v>
-      </c>
-      <c r="B372" s="4" t="s">
+    <row r="373" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A373" s="20">
+        <v>1010084144</v>
+      </c>
+      <c r="B373" s="20" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="373" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A373" s="6">
+    <row r="374" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A374" s="21">
         <v>214055</v>
       </c>
-      <c r="B373" s="14" t="s">
+      <c r="B374" s="22" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="374" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A374" s="11">
+    <row r="375" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A375" s="23">
         <v>1010021956</v>
       </c>
-      <c r="B374" s="14" t="s">
+      <c r="B375" s="22" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="375" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A375" s="11">
+    <row r="376" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A376" s="23">
         <v>1010026464</v>
       </c>
-      <c r="B375" s="14" t="s">
+      <c r="B376" s="22" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="376" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A376" s="3">
+    <row r="377" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A377" s="24">
         <v>1010021957</v>
       </c>
-      <c r="B376" s="4" t="s">
+      <c r="B377" s="20" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="377" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A377" s="4">
+    <row r="378" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A378" s="20">
         <v>1010026462</v>
       </c>
-      <c r="B377" s="4" t="s">
+      <c r="B378" s="20" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="378" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A378" s="4">
+    <row r="379" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A379" s="20">
         <v>1010026551</v>
       </c>
-      <c r="B378" s="4" t="s">
+      <c r="B379" s="20" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="379" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A379" s="4">
+    <row r="380" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A380" s="20">
         <v>1010042554</v>
       </c>
-      <c r="B379" s="4" t="s">
+      <c r="B380" s="20" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="380" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A380" s="4">
+    <row r="381" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A381" s="20">
         <v>1010039904</v>
       </c>
-      <c r="B380" s="4" t="s">
+      <c r="B381" s="20" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="381" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A381" s="4">
+    <row r="382" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A382" s="20">
         <v>1010060205</v>
       </c>
-      <c r="B381" s="4" t="s">
+      <c r="B382" s="20" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="382" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A382" s="4">
+    <row r="383" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A383" s="20">
         <v>1010060206</v>
       </c>
-      <c r="B382" s="4" t="s">
+      <c r="B383" s="20" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="383" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A383" s="4">
+    <row r="384" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A384" s="20">
         <v>1010077431</v>
       </c>
-      <c r="B383" s="4" t="s">
+      <c r="B384" s="20" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="384" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A384" s="4">
+    <row r="385" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A385" s="20">
         <v>1010077503</v>
       </c>
-      <c r="B384" s="4" t="s">
+      <c r="B385" s="20" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="385" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A385" s="4">
-        <v>386009</v>
-      </c>
-      <c r="B385" s="4" t="s">
+    <row r="386" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A386" s="20">
+        <v>1010084187</v>
+      </c>
+      <c r="B386" s="20" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="386" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A386" s="4">
+    <row r="387" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A387" s="20">
         <v>1010080958</v>
       </c>
-      <c r="B386" s="4" t="s">
+      <c r="B387" s="20" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="387" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A387" s="4">
-        <v>20191</v>
-      </c>
-      <c r="B387" s="4" t="s">
+    <row r="388" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A388" s="20">
+        <v>1010026032</v>
+      </c>
+      <c r="B388" s="20" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="388" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A388" s="4">
-        <v>431445</v>
-      </c>
-      <c r="B388" s="4" t="s">
+    <row r="389" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A389" s="20">
+        <v>1010085384</v>
+      </c>
+      <c r="B389" s="20" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="389" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A389" s="4">
-        <v>431463</v>
-      </c>
-      <c r="B389" s="4" t="s">
+    <row r="390" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A390" s="20">
+        <v>1010006347</v>
+      </c>
+      <c r="B390" s="20" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="390" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A390" s="4">
-        <v>431464</v>
-      </c>
-      <c r="B390" s="4" t="s">
+    <row r="391" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A391" s="20">
+        <v>1010085179</v>
+      </c>
+      <c r="B391" s="20" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="391" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A391" s="4">
+    <row r="392" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A392" s="20">
         <v>1010024158</v>
       </c>
-      <c r="B391" s="6" t="s">
+      <c r="B392" s="21" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="392" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A392" s="4">
+    <row r="393" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A393" s="20">
         <v>1010024131</v>
       </c>
-      <c r="B392" s="6" t="s">
+      <c r="B393" s="21" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="393" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A393" s="4">
+    <row r="394" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A394" s="20">
         <v>1010007160</v>
       </c>
-      <c r="B393" s="4" t="s">
+      <c r="B394" s="20" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="394" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A394" s="4">
+    <row r="395" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A395" s="20">
         <v>1010023642</v>
       </c>
-      <c r="B394" s="4" t="s">
+      <c r="B395" s="20" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="395" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A395" s="4">
+    <row r="396" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A396" s="20">
         <v>1010007193</v>
       </c>
-      <c r="B395" s="5" t="s">
+      <c r="B396" s="25" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="396" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A396" s="4">
+    <row r="397" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A397" s="20">
         <v>1010042637</v>
       </c>
-      <c r="B396" s="4" t="s">
+      <c r="B397" s="20" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="397" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A397" s="4">
+    <row r="398" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A398" s="20">
         <v>1040075323</v>
       </c>
-      <c r="B397" s="4" t="s">
+      <c r="B398" s="20" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="398" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A398" s="4">
+    <row r="399" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A399" s="20">
         <v>1040075324</v>
       </c>
-      <c r="B398" s="6" t="s">
+      <c r="B399" s="21" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="399" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A399" s="18">
+    <row r="400" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A400" s="26">
         <v>1040083312</v>
       </c>
-      <c r="B399" s="6" t="s">
+      <c r="B400" s="21" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="400" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A400" s="18">
+    <row r="401" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A401" s="26">
         <v>1040077661</v>
       </c>
-      <c r="B400" s="6" t="s">
+      <c r="B401" s="21" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="401" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A401" s="18">
-        <v>409638</v>
-      </c>
-      <c r="B401" s="19" t="s">
+    <row r="402" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A402" s="26">
+        <v>1010085180</v>
+      </c>
+      <c r="B402" s="27" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="402" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A402" s="3">
+    <row r="403" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A403" s="24">
         <v>1040017489</v>
       </c>
-      <c r="B402" s="3" t="s">
+      <c r="B403" s="24" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="403" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A403" s="3">
-        <v>400174</v>
-      </c>
-      <c r="B403" s="4" t="s">
+    <row r="404" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A404" s="24">
+        <v>1010085181</v>
+      </c>
+      <c r="B404" s="20" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="404" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A404" s="4">
+    <row r="405" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A405" s="20">
         <v>400175</v>
       </c>
-      <c r="B404" s="4" t="s">
+      <c r="B405" s="20" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="405" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A405" s="4">
+    <row r="406" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A406" s="20">
         <v>1040017505</v>
       </c>
-      <c r="B405" s="4" t="s">
+      <c r="B406" s="20" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="406" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A406" s="4">
+    <row r="407" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A407" s="20">
         <v>1040017503</v>
       </c>
-      <c r="B406" s="4" t="s">
+      <c r="B407" s="20" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="407" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A407" s="4">
+    <row r="408" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A408" s="20">
         <v>1010046445</v>
       </c>
-      <c r="B407" s="4" t="s">
+      <c r="B408" s="20" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="408" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A408" s="4">
+    <row r="409" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A409" s="20">
         <v>1010021033</v>
       </c>
-      <c r="B408" s="4" t="s">
+      <c r="B409" s="20" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="409" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A409" s="4">
-        <v>24950</v>
-      </c>
-      <c r="B409" s="4" t="s">
+    <row r="410" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A410" s="20">
+        <v>1010057142</v>
+      </c>
+      <c r="B410" s="20" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="410" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A410" s="4">
+    <row r="411" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A411" s="20">
         <v>1010016356</v>
       </c>
-      <c r="B410" s="4" t="s">
+      <c r="B411" s="20" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="411" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A411" s="4">
-        <v>400228</v>
-      </c>
-      <c r="B411" s="4" t="s">
+    <row r="412" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A412" s="20">
+        <v>1010084363</v>
+      </c>
+      <c r="B412" s="20" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="412" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A412" s="4">
+    <row r="413" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A413" s="20">
         <v>1010052021</v>
       </c>
-      <c r="B412" s="4" t="s">
+      <c r="B413" s="20" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="413" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A413" s="4">
+    <row r="414" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A414" s="20">
         <v>1040091721</v>
       </c>
-      <c r="B413" s="4" t="s">
+      <c r="B414" s="20" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="414" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A414" s="4">
+    <row r="415" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A415" s="20">
         <v>1010062022</v>
       </c>
-      <c r="B414" s="4" t="s">
+      <c r="B415" s="20" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="415" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A415" s="4">
+    <row r="416" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A416" s="20">
         <v>18336</v>
       </c>
-      <c r="B415" s="4" t="s">
+      <c r="B416" s="20" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="416" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A416" s="4">
+    <row r="417" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A417" s="20">
         <v>229205</v>
       </c>
-      <c r="B416" s="4" t="s">
+      <c r="B417" s="20" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="417" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A417" s="4">
+    <row r="418" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A418" s="20">
         <v>60671</v>
       </c>
-      <c r="B417" s="4" t="s">
+      <c r="B418" s="20" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="418" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A418" s="4">
+    <row r="419" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A419" s="20">
         <v>1010059726</v>
       </c>
-      <c r="B418" s="4" t="s">
+      <c r="B419" s="20" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="419" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A419" s="4">
+    <row r="420" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A420" s="20">
         <v>1010008144</v>
       </c>
-      <c r="B419" s="4" t="s">
+      <c r="B420" s="20" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="420" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A420" s="4">
+    <row r="421" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A421" s="20">
         <v>1010007244</v>
       </c>
-      <c r="B420" s="4" t="s">
+      <c r="B421" s="20" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="421" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A421" s="4">
+    <row r="422" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A422" s="20">
         <v>1010006827</v>
       </c>
-      <c r="B421" s="4" t="s">
+      <c r="B422" s="20" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="422" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A422" s="4">
+    <row r="423" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A423" s="20">
         <v>1040075426</v>
       </c>
-      <c r="B422" s="4" t="s">
+      <c r="B423" s="20" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="423" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A423" s="4">
+    <row r="424" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A424" s="20">
         <v>1040075427</v>
       </c>
-      <c r="B423" s="4" t="s">
+      <c r="B424" s="20" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="424" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A424" s="4">
-        <v>401167</v>
-      </c>
-      <c r="B424" s="4" t="s">
+    <row r="425" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A425" s="20">
+        <v>1010084313</v>
+      </c>
+      <c r="B425" s="20" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="425" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A425" s="4">
+    <row r="426" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A426" s="20">
         <v>403459</v>
       </c>
-      <c r="B425" s="4" t="s">
+      <c r="B426" s="20" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="426" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A426" s="4">
-        <v>300296</v>
-      </c>
-      <c r="B426" s="4" t="s">
+    <row r="427" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A427" s="20">
+        <v>1010044828</v>
+      </c>
+      <c r="B427" s="20" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="427" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A427" s="4">
+    <row r="428" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A428" s="20">
         <v>1010026973</v>
       </c>
-      <c r="B427" s="4" t="s">
+      <c r="B428" s="20" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="428" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A428" s="4">
+    <row r="429" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A429" s="20">
         <v>1040017204</v>
       </c>
-      <c r="B428" s="4" t="s">
+      <c r="B429" s="20" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="429" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A429" s="4"/>
-      <c r="B429" s="4"/>
-    </row>
     <row r="430" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A430" s="4"/>
-      <c r="B430" s="4"/>
+      <c r="A430" s="17"/>
+      <c r="B430" s="17"/>
     </row>
     <row r="431" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A431" s="4"/>
-      <c r="B431" s="4"/>
+      <c r="A431" s="17"/>
+      <c r="B431" s="17"/>
     </row>
     <row r="432" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A432" s="4"/>
-      <c r="B432" s="4"/>
+      <c r="A432" s="17"/>
+      <c r="B432" s="17"/>
     </row>
     <row r="433" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A433" s="4"/>
-      <c r="B433" s="4"/>
+      <c r="A433" s="17"/>
+      <c r="B433" s="17"/>
     </row>
     <row r="434" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A434" s="4"/>
-      <c r="B434" s="4"/>
+      <c r="A434" s="17"/>
+      <c r="B434" s="17"/>
     </row>
     <row r="435" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A435" s="4"/>
-      <c r="B435" s="4"/>
+      <c r="A435" s="17"/>
+      <c r="B435" s="17"/>
     </row>
     <row r="436" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A436" s="4"/>
-      <c r="B436" s="4"/>
+      <c r="A436" s="17"/>
+      <c r="B436" s="17"/>
     </row>
     <row r="437" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A437" s="5"/>
-      <c r="B437" s="5"/>
+      <c r="A437" s="17"/>
+      <c r="B437" s="17"/>
     </row>
     <row r="438" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A438" s="4"/>
-      <c r="B438" s="4"/>
+      <c r="A438" s="17"/>
+      <c r="B438" s="17"/>
     </row>
     <row r="439" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A439" s="4"/>
-      <c r="B439" s="4"/>
+      <c r="A439" s="17"/>
+      <c r="B439" s="17"/>
     </row>
     <row r="440" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A440" s="4"/>
-      <c r="B440" s="4"/>
+      <c r="A440" s="17"/>
+      <c r="B440" s="17"/>
     </row>
     <row r="441" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A441" s="4"/>
-      <c r="B441" s="4"/>
+      <c r="A441" s="17"/>
+      <c r="B441" s="17"/>
     </row>
     <row r="442" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A442" s="4"/>
-      <c r="B442" s="4"/>
+      <c r="A442" s="17"/>
+      <c r="B442" s="17"/>
     </row>
     <row r="443" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A443" s="4"/>
-      <c r="B443" s="4"/>
+      <c r="A443" s="17"/>
+      <c r="B443" s="17"/>
     </row>
     <row r="444" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A444" s="6"/>
-      <c r="B444" s="4"/>
+      <c r="A444" s="17"/>
+      <c r="B444" s="17"/>
     </row>
     <row r="445" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A445" s="4"/>
-      <c r="B445" s="14"/>
+      <c r="A445" s="17"/>
+      <c r="B445" s="17"/>
     </row>
     <row r="446" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A446" s="3"/>
-      <c r="B446" s="14"/>
+      <c r="A446" s="17"/>
+      <c r="B446" s="17"/>
     </row>
     <row r="447" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A447" s="3"/>
-      <c r="B447" s="4"/>
+      <c r="A447" s="17"/>
+      <c r="B447" s="17"/>
     </row>
     <row r="448" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A448" s="4"/>
-      <c r="B448" s="4"/>
+      <c r="A448" s="17"/>
+      <c r="B448" s="17"/>
     </row>
     <row r="449" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A449" s="4"/>
-      <c r="B449" s="4"/>
+      <c r="A449" s="17"/>
+      <c r="B449" s="17"/>
     </row>
     <row r="450" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A450" s="4"/>
-      <c r="B450" s="4"/>
+      <c r="A450" s="17"/>
+      <c r="B450" s="17"/>
     </row>
     <row r="451" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A451" s="4"/>
-      <c r="B451" s="4"/>
+      <c r="A451" s="17"/>
+      <c r="B451" s="17"/>
     </row>
     <row r="452" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A452" s="4"/>
-      <c r="B452" s="4"/>
+      <c r="A452" s="17"/>
+      <c r="B452" s="17"/>
     </row>
     <row r="453" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A453" s="4"/>
-      <c r="B453" s="4"/>
+      <c r="A453" s="17"/>
+      <c r="B453" s="17"/>
     </row>
     <row r="454" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="4"/>
-      <c r="B454" s="4"/>
+      <c r="A454" s="17"/>
+      <c r="B454" s="17"/>
     </row>
     <row r="455" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A455" s="4"/>
-      <c r="B455" s="4"/>
+      <c r="A455" s="17"/>
+      <c r="B455" s="17"/>
     </row>
     <row r="456" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A456" s="4"/>
-      <c r="B456" s="4"/>
+      <c r="A456" s="17"/>
+      <c r="B456" s="17"/>
     </row>
     <row r="457" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A457" s="4"/>
-      <c r="B457" s="4"/>
+      <c r="A457" s="17"/>
+      <c r="B457" s="17"/>
     </row>
     <row r="458" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A458" s="4"/>
-      <c r="B458" s="4"/>
+      <c r="A458" s="17"/>
+      <c r="B458" s="17"/>
     </row>
     <row r="459" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A459" s="4"/>
-      <c r="B459" s="4"/>
+      <c r="A459" s="17"/>
+      <c r="B459" s="17"/>
     </row>
     <row r="460" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A460" s="4"/>
-      <c r="B460" s="6"/>
+      <c r="A460" s="17"/>
+      <c r="B460" s="17"/>
     </row>
     <row r="461" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A461" s="7"/>
-      <c r="B461" s="6"/>
+      <c r="A461" s="17"/>
+      <c r="B461" s="17"/>
     </row>
     <row r="462" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A462" s="7"/>
-      <c r="B462" s="4"/>
+      <c r="A462" s="17"/>
+      <c r="B462" s="17"/>
     </row>
     <row r="463" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A463" s="4"/>
-      <c r="B463" s="3"/>
+      <c r="A463" s="17"/>
+      <c r="B463" s="17"/>
     </row>
     <row r="464" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A464" s="4"/>
-      <c r="B464" s="4"/>
+      <c r="A464" s="17"/>
+      <c r="B464" s="17"/>
     </row>
     <row r="465" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A465" s="4"/>
-      <c r="B465" s="4"/>
+      <c r="A465" s="17"/>
+      <c r="B465" s="17"/>
     </row>
     <row r="466" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A466" s="4"/>
-      <c r="B466" s="4"/>
+      <c r="A466" s="17"/>
+      <c r="B466" s="17"/>
     </row>
     <row r="467" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A467" s="4"/>
-      <c r="B467" s="4"/>
+      <c r="A467" s="17"/>
+      <c r="B467" s="17"/>
     </row>
     <row r="468" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A468" s="4"/>
-      <c r="B468" s="4"/>
+      <c r="A468" s="17"/>
+      <c r="B468" s="17"/>
     </row>
     <row r="469" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A469" s="4"/>
-      <c r="B469" s="4"/>
+      <c r="A469" s="17"/>
+      <c r="B469" s="17"/>
     </row>
     <row r="470" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A470" s="4"/>
-      <c r="B470" s="4"/>
+      <c r="A470" s="17"/>
+      <c r="B470" s="17"/>
     </row>
     <row r="471" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A471" s="4"/>
-      <c r="B471" s="4"/>
+      <c r="A471" s="17"/>
+      <c r="B471" s="17"/>
     </row>
     <row r="472" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A472" s="4"/>
-      <c r="B472" s="4"/>
+      <c r="A472" s="17"/>
+      <c r="B472" s="17"/>
     </row>
     <row r="473" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A473" s="4"/>
-      <c r="B473" s="4"/>
+      <c r="A473" s="17"/>
+      <c r="B473" s="17"/>
     </row>
     <row r="474" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A474" s="4"/>
-      <c r="B474" s="4"/>
+      <c r="A474" s="17"/>
+      <c r="B474" s="17"/>
     </row>
     <row r="475" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A475" s="4"/>
-      <c r="B475" s="4"/>
+      <c r="A475" s="17"/>
+      <c r="B475" s="17"/>
     </row>
     <row r="476" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A476" s="4"/>
-      <c r="B476" s="4"/>
+      <c r="A476" s="17"/>
+      <c r="B476" s="17"/>
     </row>
     <row r="477" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A477" s="4"/>
-      <c r="B477" s="4"/>
+      <c r="A477" s="17"/>
+      <c r="B477" s="17"/>
     </row>
     <row r="478" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="4"/>
-      <c r="B478" s="4"/>
+      <c r="A478" s="17"/>
+      <c r="B478" s="17"/>
     </row>
     <row r="479" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A479" s="4"/>
-      <c r="B479" s="4"/>
+      <c r="A479" s="17"/>
+      <c r="B479" s="17"/>
     </row>
     <row r="480" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="4"/>
-      <c r="B480" s="4"/>
+      <c r="A480" s="17"/>
+      <c r="B480" s="17"/>
     </row>
     <row r="481" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A481" s="4"/>
-      <c r="B481" s="4"/>
+      <c r="A481" s="17"/>
+      <c r="B481" s="17"/>
     </row>
     <row r="482" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A482" s="4"/>
-      <c r="B482" s="4"/>
+      <c r="A482" s="17"/>
+      <c r="B482" s="17"/>
     </row>
     <row r="483" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="4"/>
-      <c r="B483" s="4"/>
+      <c r="A483" s="17"/>
+      <c r="B483" s="17"/>
     </row>
     <row r="484" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="4"/>
-      <c r="B484" s="4"/>
+      <c r="A484" s="17"/>
+      <c r="B484" s="17"/>
     </row>
     <row r="485" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A485" s="4"/>
-      <c r="B485" s="4"/>
+      <c r="A485" s="17"/>
+      <c r="B485" s="17"/>
     </row>
     <row r="486" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A486" s="4"/>
-      <c r="B486" s="4"/>
+      <c r="A486" s="17"/>
+      <c r="B486" s="17"/>
     </row>
     <row r="487" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A487" s="4"/>
-      <c r="B487" s="4"/>
+      <c r="A487" s="17"/>
+      <c r="B487" s="17"/>
     </row>
     <row r="488" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A488" s="4"/>
-      <c r="B488" s="4"/>
+      <c r="A488" s="17"/>
+      <c r="B488" s="17"/>
     </row>
     <row r="489" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A489" s="4"/>
-      <c r="B489" s="4"/>
+      <c r="A489" s="17"/>
+      <c r="B489" s="17"/>
     </row>
     <row r="490" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A490" s="4"/>
-      <c r="B490" s="4"/>
+      <c r="A490" s="17"/>
+      <c r="B490" s="17"/>
     </row>
     <row r="491" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A491" s="4"/>
-      <c r="B491" s="4"/>
+      <c r="A491" s="17"/>
+      <c r="B491" s="17"/>
     </row>
     <row r="492" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A492" s="4"/>
-      <c r="B492" s="4"/>
+      <c r="A492" s="17"/>
+      <c r="B492" s="17"/>
     </row>
     <row r="493" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A493" s="4"/>
-      <c r="B493" s="4"/>
+      <c r="A493" s="17"/>
+      <c r="B493" s="17"/>
     </row>
     <row r="494" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A494" s="4"/>
-      <c r="B494" s="4"/>
+      <c r="A494" s="17"/>
+      <c r="B494" s="17"/>
     </row>
     <row r="495" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A495" s="4"/>
-      <c r="B495" s="4"/>
+      <c r="A495" s="17"/>
+      <c r="B495" s="17"/>
     </row>
     <row r="496" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A496" s="4"/>
-      <c r="B496" s="4"/>
+      <c r="A496" s="17"/>
+      <c r="B496" s="17"/>
     </row>
     <row r="497" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A497" s="4"/>
-      <c r="B497" s="4"/>
+      <c r="A497" s="17"/>
+      <c r="B497" s="17"/>
     </row>
     <row r="498" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A498" s="4"/>
-      <c r="B498" s="20"/>
+      <c r="A498" s="17"/>
+      <c r="B498" s="17"/>
     </row>
     <row r="499" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A499" s="4"/>
-      <c r="B499" s="20"/>
+      <c r="A499" s="17"/>
+      <c r="B499" s="17"/>
     </row>
     <row r="500" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A500" s="4"/>
-      <c r="B500" s="20"/>
+      <c r="A500" s="17"/>
+      <c r="B500" s="17"/>
     </row>
     <row r="501" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A501" s="4"/>
-      <c r="B501" s="20"/>
+      <c r="A501" s="17"/>
+      <c r="B501" s="17"/>
     </row>
     <row r="502" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A502" s="4"/>
-      <c r="B502" s="4"/>
+      <c r="A502" s="17"/>
+      <c r="B502" s="17"/>
     </row>
     <row r="503" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A503" s="4"/>
-      <c r="B503" s="4"/>
+      <c r="A503" s="17"/>
+      <c r="B503" s="17"/>
     </row>
     <row r="504" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A504" s="4"/>
-      <c r="B504" s="4"/>
+      <c r="A504" s="17"/>
+      <c r="B504" s="17"/>
     </row>
     <row r="505" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A505" s="4"/>
-      <c r="B505" s="4"/>
+      <c r="A505" s="17"/>
+      <c r="B505" s="17"/>
     </row>
     <row r="506" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A506" s="4"/>
-      <c r="B506" s="4"/>
+      <c r="A506" s="17"/>
+      <c r="B506" s="17"/>
     </row>
     <row r="507" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A507" s="4"/>
-      <c r="B507" s="4"/>
+      <c r="A507" s="17"/>
+      <c r="B507" s="17"/>
     </row>
     <row r="508" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A508" s="4"/>
-      <c r="B508" s="4"/>
+      <c r="A508" s="17"/>
+      <c r="B508" s="17"/>
     </row>
     <row r="509" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A509" s="4"/>
-      <c r="B509" s="4"/>
+      <c r="A509" s="17"/>
+      <c r="B509" s="17"/>
     </row>
     <row r="510" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A510" s="4"/>
-      <c r="B510" s="4"/>
+      <c r="A510" s="17"/>
+      <c r="B510" s="17"/>
     </row>
     <row r="511" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A511" s="4"/>
-      <c r="B511" s="4"/>
+      <c r="A511" s="17"/>
+      <c r="B511" s="17"/>
     </row>
     <row r="512" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A512" s="4"/>
-      <c r="B512" s="4"/>
+      <c r="A512" s="17"/>
+      <c r="B512" s="17"/>
     </row>
     <row r="513" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A513" s="4"/>
-      <c r="B513" s="4"/>
+      <c r="A513" s="17"/>
+      <c r="B513" s="17"/>
     </row>
     <row r="514" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A514" s="4"/>
-      <c r="B514" s="4"/>
+      <c r="A514" s="17"/>
+      <c r="B514" s="17"/>
     </row>
     <row r="515" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A515" s="4"/>
-      <c r="B515" s="4"/>
+      <c r="A515" s="17"/>
+      <c r="B515" s="17"/>
     </row>
     <row r="516" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A516" s="4"/>
-      <c r="B516" s="4"/>
+      <c r="A516" s="17"/>
+      <c r="B516" s="17"/>
     </row>
     <row r="517" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A517" s="4"/>
-      <c r="B517" s="4"/>
+      <c r="A517" s="17"/>
+      <c r="B517" s="17"/>
     </row>
     <row r="518" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A518" s="4"/>
-      <c r="B518" s="4"/>
+      <c r="A518" s="17"/>
+      <c r="B518" s="17"/>
     </row>
     <row r="519" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A519" s="4"/>
-      <c r="B519" s="4"/>
+      <c r="A519" s="17"/>
+      <c r="B519" s="17"/>
     </row>
     <row r="520" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A520" s="4"/>
-      <c r="B520" s="4"/>
+      <c r="A520" s="17"/>
+      <c r="B520" s="17"/>
     </row>
     <row r="521" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A521" s="4"/>
-      <c r="B521" s="4"/>
+      <c r="A521" s="17"/>
+      <c r="B521" s="17"/>
     </row>
     <row r="522" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A522" s="11"/>
-      <c r="B522" s="4"/>
+      <c r="A522" s="17"/>
+      <c r="B522" s="17"/>
     </row>
     <row r="523" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A523" s="11"/>
-      <c r="B523" s="4"/>
+      <c r="A523" s="17"/>
+      <c r="B523" s="17"/>
     </row>
     <row r="524" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A524" s="4"/>
-      <c r="B524" s="4"/>
+      <c r="A524" s="17"/>
+      <c r="B524" s="17"/>
     </row>
     <row r="525" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A525" s="11"/>
-      <c r="B525" s="4"/>
+      <c r="A525" s="17"/>
+      <c r="B525" s="17"/>
     </row>
     <row r="526" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A526" s="4"/>
-      <c r="B526" s="4"/>
+      <c r="A526" s="17"/>
+      <c r="B526" s="17"/>
     </row>
     <row r="527" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A527" s="4"/>
-      <c r="B527" s="4"/>
+      <c r="A527" s="17"/>
+      <c r="B527" s="17"/>
     </row>
     <row r="528" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A528" s="4"/>
-      <c r="B528" s="4"/>
+      <c r="A528" s="17"/>
+      <c r="B528" s="17"/>
     </row>
     <row r="529" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A529" s="4"/>
-      <c r="B529" s="4"/>
+      <c r="A529" s="17"/>
+      <c r="B529" s="17"/>
     </row>
     <row r="530" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A530" s="10"/>
-      <c r="B530" s="4"/>
+      <c r="A530" s="17"/>
+      <c r="B530" s="17"/>
     </row>
     <row r="531" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A531" s="21"/>
-      <c r="B531" s="4"/>
+      <c r="A531" s="17"/>
+      <c r="B531" s="17"/>
     </row>
     <row r="532" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A532" s="21"/>
-      <c r="B532" s="6"/>
+      <c r="A532" s="17"/>
+      <c r="B532" s="17"/>
     </row>
     <row r="533" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A533" s="7"/>
-      <c r="B533" s="11"/>
+      <c r="A533" s="17"/>
+      <c r="B533" s="17"/>
     </row>
     <row r="534" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A534" s="4"/>
-      <c r="B534" s="4"/>
+      <c r="A534" s="17"/>
+      <c r="B534" s="17"/>
     </row>
     <row r="535" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A535" s="4"/>
-      <c r="B535" s="4"/>
+      <c r="A535" s="17"/>
+      <c r="B535" s="17"/>
     </row>
     <row r="536" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A536" s="4"/>
-      <c r="B536" s="4"/>
+      <c r="A536" s="17"/>
+      <c r="B536" s="17"/>
     </row>
     <row r="537" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A537" s="4"/>
-      <c r="B537" s="4"/>
+      <c r="A537" s="17"/>
+      <c r="B537" s="17"/>
     </row>
     <row r="538" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A538" s="4"/>
-      <c r="B538" s="4"/>
+      <c r="A538" s="17"/>
+      <c r="B538" s="17"/>
     </row>
     <row r="539" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A539" s="4"/>
-      <c r="B539" s="4"/>
+      <c r="A539" s="17"/>
+      <c r="B539" s="17"/>
     </row>
     <row r="540" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A540" s="4"/>
-      <c r="B540" s="4"/>
+      <c r="A540" s="17"/>
+      <c r="B540" s="17"/>
     </row>
     <row r="541" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" s="17"/>
@@ -5769,7 +5796,7 @@
     </row>
     <row r="558" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" s="17"/>
-      <c r="B558" s="8"/>
+      <c r="B558" s="17"/>
     </row>
     <row r="559" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" s="17"/>
@@ -7269,2911 +7296,1055 @@
     </row>
     <row r="933" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A933" s="17"/>
-      <c r="B933" s="17"/>
+      <c r="B933" s="8"/>
     </row>
     <row r="934" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A934" s="17"/>
-      <c r="B934" s="17"/>
+      <c r="B934" s="8"/>
     </row>
     <row r="935" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A935" s="17"/>
-      <c r="B935" s="17"/>
+      <c r="B935" s="8"/>
     </row>
     <row r="936" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A936" s="17"/>
-      <c r="B936" s="17"/>
+      <c r="B936" s="8"/>
     </row>
     <row r="937" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A937" s="17"/>
-      <c r="B937" s="17"/>
+      <c r="B937" s="8"/>
     </row>
     <row r="938" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A938" s="17"/>
-      <c r="B938" s="17"/>
+      <c r="B938" s="8"/>
     </row>
     <row r="939" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A939" s="17"/>
-      <c r="B939" s="17"/>
+      <c r="B939" s="8"/>
     </row>
     <row r="940" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A940" s="17"/>
-      <c r="B940" s="17"/>
+      <c r="B940" s="8"/>
     </row>
     <row r="941" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A941" s="17"/>
-      <c r="B941" s="17"/>
+      <c r="B941" s="8"/>
     </row>
     <row r="942" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A942" s="17"/>
-      <c r="B942" s="17"/>
+      <c r="B942" s="8"/>
     </row>
     <row r="943" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A943" s="17"/>
-      <c r="B943" s="17"/>
+      <c r="B943" s="8"/>
     </row>
     <row r="944" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A944" s="17"/>
-      <c r="B944" s="17"/>
+      <c r="B944" s="8"/>
     </row>
     <row r="945" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A945" s="17"/>
-      <c r="B945" s="17"/>
+      <c r="B945" s="8"/>
     </row>
     <row r="946" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A946" s="17"/>
-      <c r="B946" s="17"/>
+      <c r="B946" s="8"/>
     </row>
     <row r="947" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A947" s="17"/>
-      <c r="B947" s="17"/>
+      <c r="B947" s="8"/>
     </row>
     <row r="948" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A948" s="17"/>
-      <c r="B948" s="17"/>
+      <c r="B948" s="8"/>
     </row>
     <row r="949" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A949" s="17"/>
-      <c r="B949" s="17"/>
+      <c r="B949" s="8"/>
     </row>
     <row r="950" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A950" s="17"/>
-      <c r="B950" s="17"/>
+      <c r="B950" s="8"/>
     </row>
     <row r="951" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A951" s="17"/>
-      <c r="B951" s="17"/>
+      <c r="B951" s="8"/>
     </row>
     <row r="952" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A952" s="17"/>
-      <c r="B952" s="17"/>
+      <c r="B952" s="8"/>
     </row>
     <row r="953" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A953" s="17"/>
-      <c r="B953" s="17"/>
+      <c r="B953" s="8"/>
     </row>
     <row r="954" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A954" s="17"/>
-      <c r="B954" s="17"/>
+      <c r="B954" s="8"/>
     </row>
     <row r="955" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A955" s="17"/>
-      <c r="B955" s="17"/>
+      <c r="B955" s="8"/>
     </row>
     <row r="956" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A956" s="17"/>
-      <c r="B956" s="17"/>
+      <c r="B956" s="8"/>
     </row>
     <row r="957" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A957" s="17"/>
-      <c r="B957" s="17"/>
+      <c r="B957" s="8"/>
     </row>
     <row r="958" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A958" s="17"/>
-      <c r="B958" s="17"/>
+      <c r="B958" s="8"/>
     </row>
     <row r="959" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A959" s="17"/>
-      <c r="B959" s="17"/>
+      <c r="B959" s="8"/>
     </row>
     <row r="960" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A960" s="17"/>
-      <c r="B960" s="17"/>
+      <c r="B960" s="8"/>
     </row>
     <row r="961" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A961" s="17"/>
-      <c r="B961" s="17"/>
+      <c r="B961" s="8"/>
     </row>
     <row r="962" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A962" s="17"/>
-      <c r="B962" s="17"/>
+      <c r="B962" s="8"/>
     </row>
     <row r="963" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A963" s="17"/>
-      <c r="B963" s="17"/>
+      <c r="B963" s="8"/>
     </row>
     <row r="964" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A964" s="17"/>
-      <c r="B964" s="17"/>
+      <c r="B964" s="8"/>
     </row>
     <row r="965" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A965" s="17"/>
-      <c r="B965" s="17"/>
+      <c r="B965" s="8"/>
     </row>
     <row r="966" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A966" s="17"/>
-      <c r="B966" s="17"/>
+      <c r="B966" s="8"/>
     </row>
     <row r="967" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A967" s="17"/>
-      <c r="B967" s="17"/>
+      <c r="B967" s="8"/>
     </row>
     <row r="968" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A968" s="17"/>
-      <c r="B968" s="17"/>
+      <c r="B968" s="8"/>
     </row>
     <row r="969" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A969" s="17"/>
-      <c r="B969" s="17"/>
+      <c r="B969" s="8"/>
     </row>
     <row r="970" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A970" s="17"/>
-      <c r="B970" s="17"/>
+      <c r="B970" s="8"/>
     </row>
     <row r="971" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A971" s="17"/>
-      <c r="B971" s="17"/>
+      <c r="B971" s="8"/>
     </row>
     <row r="972" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A972" s="17"/>
-      <c r="B972" s="17"/>
+      <c r="B972" s="8"/>
     </row>
     <row r="973" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A973" s="17"/>
-      <c r="B973" s="17"/>
+      <c r="B973" s="8"/>
     </row>
     <row r="974" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A974" s="17"/>
-      <c r="B974" s="17"/>
+      <c r="B974" s="8"/>
     </row>
     <row r="975" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A975" s="17"/>
-      <c r="B975" s="17"/>
+      <c r="B975" s="8"/>
     </row>
     <row r="976" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A976" s="17"/>
-      <c r="B976" s="17"/>
+      <c r="B976" s="8"/>
     </row>
     <row r="977" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A977" s="17"/>
-      <c r="B977" s="17"/>
+      <c r="B977" s="8"/>
     </row>
     <row r="978" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A978" s="17"/>
-      <c r="B978" s="17"/>
+      <c r="B978" s="8"/>
     </row>
     <row r="979" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A979" s="17"/>
-      <c r="B979" s="17"/>
+      <c r="B979" s="8"/>
     </row>
     <row r="980" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A980" s="17"/>
-      <c r="B980" s="17"/>
+      <c r="B980" s="8"/>
     </row>
     <row r="981" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A981" s="17"/>
-      <c r="B981" s="17"/>
+      <c r="B981" s="8"/>
     </row>
     <row r="982" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A982" s="17"/>
-      <c r="B982" s="17"/>
+      <c r="B982" s="8"/>
     </row>
     <row r="983" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A983" s="17"/>
-      <c r="B983" s="17"/>
+      <c r="B983" s="8"/>
     </row>
     <row r="984" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A984" s="17"/>
-      <c r="B984" s="17"/>
+      <c r="B984" s="8"/>
     </row>
     <row r="985" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A985" s="17"/>
-      <c r="B985" s="17"/>
+      <c r="B985" s="8"/>
     </row>
     <row r="986" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A986" s="17"/>
-      <c r="B986" s="17"/>
+      <c r="B986" s="8"/>
     </row>
     <row r="987" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A987" s="17"/>
-      <c r="B987" s="17"/>
+      <c r="B987" s="8"/>
     </row>
     <row r="988" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A988" s="17"/>
-      <c r="B988" s="17"/>
+      <c r="B988" s="8"/>
     </row>
     <row r="989" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A989" s="17"/>
-      <c r="B989" s="17"/>
+      <c r="B989" s="8"/>
     </row>
     <row r="990" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A990" s="17"/>
-      <c r="B990" s="17"/>
+      <c r="B990" s="8"/>
     </row>
     <row r="991" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A991" s="17"/>
-      <c r="B991" s="17"/>
+      <c r="B991" s="8"/>
     </row>
     <row r="992" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A992" s="17"/>
-      <c r="B992" s="17"/>
+      <c r="B992" s="8"/>
     </row>
     <row r="993" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A993" s="17"/>
-      <c r="B993" s="17"/>
+      <c r="B993" s="8"/>
     </row>
     <row r="994" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A994" s="17"/>
-      <c r="B994" s="17"/>
+      <c r="B994" s="8"/>
     </row>
     <row r="995" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A995" s="17"/>
-      <c r="B995" s="17"/>
+      <c r="B995" s="8"/>
     </row>
     <row r="996" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A996" s="17"/>
-      <c r="B996" s="17"/>
+      <c r="B996" s="8"/>
     </row>
     <row r="997" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A997" s="17"/>
-      <c r="B997" s="17"/>
+      <c r="B997" s="8"/>
     </row>
     <row r="998" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A998" s="17"/>
-      <c r="B998" s="17"/>
+      <c r="B998" s="8"/>
     </row>
     <row r="999" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A999" s="17"/>
-      <c r="B999" s="17"/>
+      <c r="B999" s="8"/>
     </row>
     <row r="1000" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1000" s="17"/>
-      <c r="B1000" s="17"/>
+      <c r="B1000" s="8"/>
     </row>
     <row r="1001" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1001" s="17"/>
-      <c r="B1001" s="17"/>
+      <c r="A1001" s="8"/>
+      <c r="B1001" s="8"/>
     </row>
     <row r="1002" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1002" s="17"/>
-      <c r="B1002" s="17"/>
+      <c r="A1002" s="8"/>
+      <c r="B1002" s="8"/>
     </row>
     <row r="1003" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1003" s="17"/>
-      <c r="B1003" s="17"/>
+      <c r="A1003" s="8"/>
+      <c r="B1003" s="8"/>
     </row>
     <row r="1004" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1004" s="17"/>
-      <c r="B1004" s="17"/>
+      <c r="A1004" s="8"/>
+      <c r="B1004" s="8"/>
     </row>
     <row r="1005" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1005" s="17"/>
-      <c r="B1005" s="17"/>
+      <c r="A1005" s="8"/>
+      <c r="B1005" s="8"/>
     </row>
     <row r="1006" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1006" s="17"/>
-      <c r="B1006" s="17"/>
+      <c r="A1006" s="8"/>
+      <c r="B1006" s="8"/>
     </row>
     <row r="1007" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1007" s="17"/>
-      <c r="B1007" s="17"/>
+      <c r="A1007" s="8"/>
+      <c r="B1007" s="8"/>
     </row>
     <row r="1008" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1008" s="17"/>
-      <c r="B1008" s="17"/>
+      <c r="A1008" s="8"/>
+      <c r="B1008" s="8"/>
     </row>
     <row r="1009" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1009" s="17"/>
-      <c r="B1009" s="17"/>
+      <c r="A1009" s="8"/>
+      <c r="B1009" s="8"/>
     </row>
     <row r="1010" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1010" s="17"/>
-      <c r="B1010" s="17"/>
+      <c r="A1010" s="8"/>
+      <c r="B1010" s="8"/>
     </row>
     <row r="1011" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1011" s="17"/>
-      <c r="B1011" s="17"/>
+      <c r="A1011" s="8"/>
+      <c r="B1011" s="8"/>
     </row>
     <row r="1012" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1012" s="17"/>
-      <c r="B1012" s="17"/>
+      <c r="A1012" s="8"/>
+      <c r="B1012" s="8"/>
     </row>
     <row r="1013" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1013" s="17"/>
-      <c r="B1013" s="17"/>
+      <c r="A1013" s="8"/>
+      <c r="B1013" s="8"/>
     </row>
     <row r="1014" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1014" s="17"/>
-      <c r="B1014" s="17"/>
+      <c r="A1014" s="8"/>
+      <c r="B1014" s="8"/>
     </row>
     <row r="1015" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1015" s="17"/>
-      <c r="B1015" s="17"/>
+      <c r="A1015" s="8"/>
+      <c r="B1015" s="8"/>
     </row>
     <row r="1016" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1016" s="17"/>
-      <c r="B1016" s="17"/>
+      <c r="A1016" s="8"/>
+      <c r="B1016" s="8"/>
     </row>
     <row r="1017" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1017" s="17"/>
-      <c r="B1017" s="17"/>
+      <c r="A1017" s="8"/>
+      <c r="B1017" s="8"/>
     </row>
     <row r="1018" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1018" s="17"/>
-      <c r="B1018" s="17"/>
+      <c r="A1018" s="8"/>
+      <c r="B1018" s="8"/>
     </row>
     <row r="1019" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1019" s="17"/>
-      <c r="B1019" s="17"/>
+      <c r="A1019" s="8"/>
+      <c r="B1019" s="8"/>
     </row>
     <row r="1020" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1020" s="17"/>
-      <c r="B1020" s="17"/>
+      <c r="A1020" s="8"/>
+      <c r="B1020" s="8"/>
     </row>
     <row r="1021" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1021" s="17"/>
-      <c r="B1021" s="17"/>
+      <c r="A1021" s="8"/>
+      <c r="B1021" s="8"/>
     </row>
     <row r="1022" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1022" s="17"/>
-      <c r="B1022" s="17"/>
+      <c r="A1022" s="8"/>
+      <c r="B1022" s="8"/>
     </row>
     <row r="1023" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1023" s="17"/>
-      <c r="B1023" s="17"/>
+      <c r="A1023" s="8"/>
+      <c r="B1023" s="8"/>
     </row>
     <row r="1024" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1024" s="17"/>
-      <c r="B1024" s="17"/>
+      <c r="A1024" s="8"/>
+      <c r="B1024" s="8"/>
     </row>
     <row r="1025" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1025" s="17"/>
-      <c r="B1025" s="17"/>
+      <c r="A1025" s="8"/>
+      <c r="B1025" s="8"/>
     </row>
     <row r="1026" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1026" s="17"/>
-      <c r="B1026" s="17"/>
+      <c r="A1026" s="8"/>
+      <c r="B1026" s="8"/>
     </row>
     <row r="1027" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1027" s="17"/>
-      <c r="B1027" s="17"/>
+      <c r="A1027" s="8"/>
+      <c r="B1027" s="8"/>
     </row>
     <row r="1028" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1028" s="17"/>
-      <c r="B1028" s="17"/>
+      <c r="A1028" s="8"/>
+      <c r="B1028" s="8"/>
     </row>
     <row r="1029" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1029" s="17"/>
-      <c r="B1029" s="17"/>
+      <c r="A1029" s="8"/>
+      <c r="B1029" s="8"/>
     </row>
     <row r="1030" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1030" s="17"/>
-      <c r="B1030" s="17"/>
+      <c r="A1030" s="8"/>
+      <c r="B1030" s="8"/>
     </row>
     <row r="1031" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1031" s="17"/>
-      <c r="B1031" s="17"/>
+      <c r="A1031" s="8"/>
+      <c r="B1031" s="8"/>
     </row>
     <row r="1032" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1032" s="17"/>
-      <c r="B1032" s="17"/>
+      <c r="A1032" s="8"/>
+      <c r="B1032" s="8"/>
     </row>
     <row r="1033" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1033" s="17"/>
-      <c r="B1033" s="17"/>
+      <c r="A1033" s="8"/>
+      <c r="B1033" s="8"/>
     </row>
     <row r="1034" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1034" s="17"/>
-      <c r="B1034" s="17"/>
+      <c r="A1034" s="8"/>
+      <c r="B1034" s="8"/>
     </row>
     <row r="1035" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1035" s="17"/>
-      <c r="B1035" s="17"/>
+      <c r="A1035" s="8"/>
+      <c r="B1035" s="8"/>
     </row>
     <row r="1036" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1036" s="17"/>
-      <c r="B1036" s="17"/>
+      <c r="A1036" s="8"/>
+      <c r="B1036" s="8"/>
     </row>
     <row r="1037" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1037" s="17"/>
-      <c r="B1037" s="17"/>
+      <c r="A1037" s="8"/>
+      <c r="B1037" s="8"/>
     </row>
     <row r="1038" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1038" s="17"/>
-      <c r="B1038" s="17"/>
+      <c r="A1038" s="8"/>
+      <c r="B1038" s="8"/>
     </row>
     <row r="1039" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1039" s="17"/>
-      <c r="B1039" s="17"/>
+      <c r="A1039" s="8"/>
+      <c r="B1039" s="8"/>
     </row>
     <row r="1040" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1040" s="17"/>
-      <c r="B1040" s="17"/>
+      <c r="A1040" s="8"/>
+      <c r="B1040" s="8"/>
     </row>
     <row r="1041" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1041" s="17"/>
-      <c r="B1041" s="17"/>
+      <c r="A1041" s="8"/>
+      <c r="B1041" s="8"/>
     </row>
     <row r="1042" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1042" s="17"/>
-      <c r="B1042" s="17"/>
+      <c r="A1042" s="8"/>
+      <c r="B1042" s="8"/>
     </row>
     <row r="1043" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1043" s="17"/>
-      <c r="B1043" s="17"/>
+      <c r="A1043" s="8"/>
+      <c r="B1043" s="8"/>
     </row>
     <row r="1044" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1044" s="17"/>
-      <c r="B1044" s="17"/>
+      <c r="A1044" s="8"/>
+      <c r="B1044" s="8"/>
     </row>
     <row r="1045" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1045" s="17"/>
-      <c r="B1045" s="17"/>
+      <c r="A1045" s="8"/>
+      <c r="B1045" s="8"/>
     </row>
     <row r="1046" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1046" s="17"/>
-      <c r="B1046" s="17"/>
+      <c r="A1046" s="8"/>
+      <c r="B1046" s="8"/>
     </row>
     <row r="1047" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1047" s="17"/>
-      <c r="B1047" s="17"/>
+      <c r="A1047" s="8"/>
+      <c r="B1047" s="8"/>
     </row>
     <row r="1048" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1048" s="17"/>
-      <c r="B1048" s="17"/>
+      <c r="A1048" s="8"/>
+      <c r="B1048" s="8"/>
     </row>
     <row r="1049" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1049" s="17"/>
-      <c r="B1049" s="17"/>
+      <c r="A1049" s="8"/>
+      <c r="B1049" s="8"/>
     </row>
     <row r="1050" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1050" s="17"/>
-      <c r="B1050" s="17"/>
+      <c r="A1050" s="8"/>
+      <c r="B1050" s="8"/>
     </row>
     <row r="1051" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1051" s="17"/>
-      <c r="B1051" s="17"/>
+      <c r="A1051" s="8"/>
+      <c r="B1051" s="8"/>
     </row>
     <row r="1052" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1052" s="17"/>
-      <c r="B1052" s="17"/>
+      <c r="A1052" s="8"/>
+      <c r="B1052" s="8"/>
     </row>
     <row r="1053" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1053" s="17"/>
-      <c r="B1053" s="17"/>
+      <c r="A1053" s="8"/>
+      <c r="B1053" s="8"/>
     </row>
     <row r="1054" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1054" s="17"/>
-      <c r="B1054" s="17"/>
+      <c r="A1054" s="8"/>
+      <c r="B1054" s="8"/>
     </row>
     <row r="1055" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1055" s="17"/>
-      <c r="B1055" s="17"/>
+      <c r="A1055" s="8"/>
+      <c r="B1055" s="8"/>
     </row>
     <row r="1056" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1056" s="17"/>
-      <c r="B1056" s="17"/>
+      <c r="A1056" s="8"/>
+      <c r="B1056" s="8"/>
     </row>
     <row r="1057" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1057" s="17"/>
-      <c r="B1057" s="17"/>
+      <c r="A1057" s="8"/>
+      <c r="B1057" s="8"/>
     </row>
     <row r="1058" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1058" s="17"/>
-      <c r="B1058" s="17"/>
+      <c r="A1058" s="8"/>
+      <c r="B1058" s="8"/>
     </row>
     <row r="1059" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1059" s="17"/>
-      <c r="B1059" s="17"/>
+      <c r="A1059" s="8"/>
+      <c r="B1059" s="8"/>
     </row>
     <row r="1060" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1060" s="17"/>
-      <c r="B1060" s="17"/>
+      <c r="A1060" s="8"/>
+      <c r="B1060" s="8"/>
     </row>
     <row r="1061" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1061" s="17"/>
-      <c r="B1061" s="17"/>
+      <c r="A1061" s="8"/>
+      <c r="B1061" s="8"/>
     </row>
     <row r="1062" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1062" s="17"/>
-      <c r="B1062" s="17"/>
+      <c r="A1062" s="8"/>
+      <c r="B1062" s="8"/>
     </row>
     <row r="1063" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1063" s="17"/>
-      <c r="B1063" s="17"/>
+      <c r="A1063" s="8"/>
+      <c r="B1063" s="8"/>
     </row>
     <row r="1064" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1064" s="17"/>
-      <c r="B1064" s="17"/>
+      <c r="A1064" s="8"/>
+      <c r="B1064" s="8"/>
     </row>
     <row r="1065" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1065" s="17"/>
-      <c r="B1065" s="17"/>
+      <c r="A1065" s="8"/>
+      <c r="B1065" s="8"/>
     </row>
     <row r="1066" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1066" s="17"/>
-      <c r="B1066" s="17"/>
+      <c r="A1066" s="8"/>
+      <c r="B1066" s="8"/>
     </row>
     <row r="1067" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1067" s="17"/>
-      <c r="B1067" s="17"/>
+      <c r="A1067" s="8"/>
+      <c r="B1067" s="8"/>
     </row>
     <row r="1068" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1068" s="17"/>
-      <c r="B1068" s="17"/>
+      <c r="A1068" s="8"/>
+      <c r="B1068" s="8"/>
     </row>
     <row r="1069" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1069" s="17"/>
-      <c r="B1069" s="17"/>
+      <c r="A1069" s="8"/>
+      <c r="B1069" s="8"/>
     </row>
     <row r="1070" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1070" s="17"/>
-      <c r="B1070" s="17"/>
+      <c r="A1070" s="8"/>
+      <c r="B1070" s="8"/>
     </row>
     <row r="1071" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1071" s="17"/>
-      <c r="B1071" s="17"/>
+      <c r="A1071" s="8"/>
+      <c r="B1071" s="8"/>
     </row>
     <row r="1072" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1072" s="17"/>
-      <c r="B1072" s="17"/>
+      <c r="A1072" s="8"/>
+      <c r="B1072" s="8"/>
     </row>
     <row r="1073" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1073" s="17"/>
-      <c r="B1073" s="17"/>
+      <c r="A1073" s="8"/>
+      <c r="B1073" s="8"/>
     </row>
     <row r="1074" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1074" s="17"/>
-      <c r="B1074" s="17"/>
+      <c r="A1074" s="8"/>
+      <c r="B1074" s="8"/>
     </row>
     <row r="1075" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1075" s="17"/>
-      <c r="B1075" s="17"/>
+      <c r="A1075" s="8"/>
+      <c r="B1075" s="8"/>
     </row>
     <row r="1076" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1076" s="17"/>
-      <c r="B1076" s="17"/>
+      <c r="A1076" s="8"/>
+      <c r="B1076" s="8"/>
     </row>
     <row r="1077" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1077" s="17"/>
-      <c r="B1077" s="17"/>
+      <c r="A1077" s="8"/>
+      <c r="B1077" s="8"/>
     </row>
     <row r="1078" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1078" s="17"/>
-      <c r="B1078" s="17"/>
+      <c r="A1078" s="8"/>
+      <c r="B1078" s="8"/>
     </row>
     <row r="1079" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1079" s="17"/>
-      <c r="B1079" s="17"/>
+      <c r="A1079" s="8"/>
+      <c r="B1079" s="8"/>
     </row>
     <row r="1080" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1080" s="17"/>
-      <c r="B1080" s="17"/>
+      <c r="A1080" s="8"/>
+      <c r="B1080" s="8"/>
     </row>
     <row r="1081" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1081" s="17"/>
-      <c r="B1081" s="17"/>
+      <c r="A1081" s="8"/>
+      <c r="B1081" s="8"/>
     </row>
     <row r="1082" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1082" s="17"/>
-      <c r="B1082" s="17"/>
+      <c r="A1082" s="8"/>
+      <c r="B1082" s="8"/>
     </row>
     <row r="1083" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1083" s="17"/>
-      <c r="B1083" s="17"/>
+      <c r="A1083" s="8"/>
+      <c r="B1083" s="8"/>
     </row>
     <row r="1084" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1084" s="17"/>
-      <c r="B1084" s="17"/>
+      <c r="A1084" s="8"/>
+      <c r="B1084" s="8"/>
     </row>
     <row r="1085" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1085" s="17"/>
-      <c r="B1085" s="17"/>
+      <c r="A1085" s="8"/>
+      <c r="B1085" s="8"/>
     </row>
     <row r="1086" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1086" s="17"/>
-      <c r="B1086" s="17"/>
+      <c r="A1086" s="8"/>
+      <c r="B1086" s="8"/>
     </row>
     <row r="1087" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1087" s="17"/>
-      <c r="B1087" s="17"/>
+      <c r="A1087" s="8"/>
+      <c r="B1087" s="8"/>
     </row>
     <row r="1088" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1088" s="17"/>
-      <c r="B1088" s="17"/>
+      <c r="A1088" s="8"/>
+      <c r="B1088" s="8"/>
     </row>
     <row r="1089" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1089" s="17"/>
-      <c r="B1089" s="17"/>
+      <c r="A1089" s="8"/>
+      <c r="B1089" s="8"/>
     </row>
     <row r="1090" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1090" s="17"/>
-      <c r="B1090" s="17"/>
+      <c r="A1090" s="8"/>
+      <c r="B1090" s="8"/>
     </row>
     <row r="1091" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1091" s="17"/>
-      <c r="B1091" s="17"/>
+      <c r="A1091" s="8"/>
+      <c r="B1091" s="8"/>
     </row>
     <row r="1092" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1092" s="17"/>
-      <c r="B1092" s="17"/>
+      <c r="A1092" s="8"/>
+      <c r="B1092" s="8"/>
     </row>
     <row r="1093" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1093" s="17"/>
-      <c r="B1093" s="17"/>
+      <c r="A1093" s="8"/>
+      <c r="B1093" s="8"/>
     </row>
     <row r="1094" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1094" s="17"/>
-      <c r="B1094" s="17"/>
+      <c r="A1094" s="8"/>
+      <c r="B1094" s="8"/>
     </row>
     <row r="1095" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1095" s="17"/>
-      <c r="B1095" s="17"/>
+      <c r="A1095" s="8"/>
+      <c r="B1095" s="8"/>
     </row>
     <row r="1096" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1096" s="17"/>
-      <c r="B1096" s="17"/>
+      <c r="A1096" s="8"/>
+      <c r="B1096" s="8"/>
     </row>
     <row r="1097" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1097" s="17"/>
-      <c r="B1097" s="17"/>
+      <c r="A1097" s="8"/>
+      <c r="B1097" s="8"/>
     </row>
     <row r="1098" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1098" s="17"/>
-      <c r="B1098" s="17"/>
+      <c r="A1098" s="8"/>
+      <c r="B1098" s="8"/>
     </row>
     <row r="1099" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1099" s="17"/>
-      <c r="B1099" s="17"/>
+      <c r="A1099" s="8"/>
+      <c r="B1099" s="8"/>
     </row>
     <row r="1100" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1100" s="17"/>
-      <c r="B1100" s="17"/>
+      <c r="A1100" s="8"/>
+      <c r="B1100" s="8"/>
     </row>
     <row r="1101" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1101" s="17"/>
-      <c r="B1101" s="17"/>
+      <c r="A1101" s="8"/>
+      <c r="B1101" s="8"/>
     </row>
     <row r="1102" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1102" s="17"/>
-      <c r="B1102" s="17"/>
+      <c r="A1102" s="8"/>
+      <c r="B1102" s="8"/>
     </row>
     <row r="1103" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1103" s="17"/>
-      <c r="B1103" s="17"/>
+      <c r="A1103" s="8"/>
+      <c r="B1103" s="8"/>
     </row>
     <row r="1104" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1104" s="17"/>
-      <c r="B1104" s="17"/>
+      <c r="A1104" s="8"/>
+      <c r="B1104" s="8"/>
     </row>
     <row r="1105" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1105" s="17"/>
-      <c r="B1105" s="17"/>
+      <c r="A1105" s="8"/>
+      <c r="B1105" s="8"/>
     </row>
     <row r="1106" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1106" s="17"/>
-      <c r="B1106" s="17"/>
+      <c r="A1106" s="8"/>
+      <c r="B1106" s="8"/>
     </row>
     <row r="1107" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1107" s="17"/>
-      <c r="B1107" s="17"/>
+      <c r="A1107" s="8"/>
+      <c r="B1107" s="8"/>
     </row>
     <row r="1108" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1108" s="17"/>
-      <c r="B1108" s="17"/>
+      <c r="A1108" s="8"/>
+      <c r="B1108" s="8"/>
     </row>
     <row r="1109" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1109" s="17"/>
-      <c r="B1109" s="17"/>
+      <c r="A1109" s="8"/>
+      <c r="B1109" s="8"/>
     </row>
     <row r="1110" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1110" s="17"/>
-      <c r="B1110" s="17"/>
+      <c r="A1110" s="8"/>
+      <c r="B1110" s="8"/>
     </row>
     <row r="1111" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1111" s="17"/>
-      <c r="B1111" s="17"/>
+      <c r="A1111" s="8"/>
+      <c r="B1111" s="8"/>
     </row>
     <row r="1112" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1112" s="17"/>
-      <c r="B1112" s="17"/>
+      <c r="A1112" s="8"/>
+      <c r="B1112" s="8"/>
     </row>
     <row r="1113" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1113" s="17"/>
-      <c r="B1113" s="17"/>
+      <c r="A1113" s="8"/>
+      <c r="B1113" s="8"/>
     </row>
     <row r="1114" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1114" s="17"/>
-      <c r="B1114" s="17"/>
+      <c r="A1114" s="8"/>
+      <c r="B1114" s="8"/>
     </row>
     <row r="1115" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1115" s="17"/>
-      <c r="B1115" s="17"/>
+      <c r="A1115" s="8"/>
+      <c r="B1115" s="8"/>
     </row>
     <row r="1116" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1116" s="17"/>
-      <c r="B1116" s="17"/>
+      <c r="A1116" s="8"/>
+      <c r="B1116" s="8"/>
     </row>
     <row r="1117" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1117" s="17"/>
-      <c r="B1117" s="17"/>
+      <c r="A1117" s="8"/>
+      <c r="B1117" s="8"/>
     </row>
     <row r="1118" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1118" s="17"/>
-      <c r="B1118" s="17"/>
+      <c r="A1118" s="8"/>
+      <c r="B1118" s="8"/>
     </row>
     <row r="1119" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1119" s="17"/>
-      <c r="B1119" s="17"/>
+      <c r="A1119" s="8"/>
+      <c r="B1119" s="8"/>
     </row>
     <row r="1120" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1120" s="17"/>
-      <c r="B1120" s="17"/>
+      <c r="A1120" s="8"/>
+      <c r="B1120" s="8"/>
     </row>
     <row r="1121" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1121" s="17"/>
-      <c r="B1121" s="17"/>
+      <c r="A1121" s="8"/>
+      <c r="B1121" s="8"/>
     </row>
     <row r="1122" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1122" s="17"/>
-      <c r="B1122" s="17"/>
+      <c r="A1122" s="8"/>
+      <c r="B1122" s="8"/>
     </row>
     <row r="1123" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1123" s="17"/>
-      <c r="B1123" s="17"/>
+      <c r="A1123" s="8"/>
+      <c r="B1123" s="8"/>
     </row>
     <row r="1124" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1124" s="17"/>
-      <c r="B1124" s="17"/>
+      <c r="A1124" s="8"/>
+      <c r="B1124" s="8"/>
     </row>
     <row r="1125" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1125" s="17"/>
-      <c r="B1125" s="17"/>
+      <c r="A1125" s="8"/>
+      <c r="B1125" s="8"/>
     </row>
     <row r="1126" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1126" s="17"/>
-      <c r="B1126" s="17"/>
+      <c r="A1126" s="8"/>
+      <c r="B1126" s="8"/>
     </row>
     <row r="1127" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1127" s="17"/>
-      <c r="B1127" s="17"/>
+      <c r="A1127" s="8"/>
+      <c r="B1127" s="8"/>
     </row>
     <row r="1128" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1128" s="17"/>
-      <c r="B1128" s="17"/>
+      <c r="A1128" s="8"/>
+      <c r="B1128" s="8"/>
     </row>
     <row r="1129" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1129" s="17"/>
-      <c r="B1129" s="17"/>
+      <c r="A1129" s="8"/>
+      <c r="B1129" s="8"/>
     </row>
     <row r="1130" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1130" s="17"/>
-      <c r="B1130" s="17"/>
+      <c r="A1130" s="8"/>
+      <c r="B1130" s="8"/>
     </row>
     <row r="1131" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1131" s="17"/>
-      <c r="B1131" s="17"/>
+      <c r="A1131" s="8"/>
+      <c r="B1131" s="8"/>
     </row>
     <row r="1132" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1132" s="17"/>
-      <c r="B1132" s="17"/>
+      <c r="A1132" s="8"/>
+      <c r="B1132" s="8"/>
     </row>
     <row r="1133" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1133" s="17"/>
-      <c r="B1133" s="17"/>
+      <c r="A1133" s="8"/>
+      <c r="B1133" s="8"/>
     </row>
     <row r="1134" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1134" s="17"/>
-      <c r="B1134" s="17"/>
+      <c r="A1134" s="8"/>
+      <c r="B1134" s="8"/>
     </row>
     <row r="1135" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1135" s="17"/>
-      <c r="B1135" s="17"/>
+      <c r="A1135" s="8"/>
+      <c r="B1135" s="8"/>
     </row>
     <row r="1136" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1136" s="17"/>
-      <c r="B1136" s="17"/>
+      <c r="A1136" s="8"/>
+      <c r="B1136" s="8"/>
     </row>
     <row r="1137" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1137" s="17"/>
-      <c r="B1137" s="17"/>
+      <c r="A1137" s="8"/>
+      <c r="B1137" s="8"/>
     </row>
     <row r="1138" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1138" s="17"/>
-      <c r="B1138" s="17"/>
+      <c r="A1138" s="8"/>
+      <c r="B1138" s="8"/>
     </row>
     <row r="1139" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1139" s="17"/>
-      <c r="B1139" s="17"/>
+      <c r="A1139" s="8"/>
+      <c r="B1139" s="8"/>
     </row>
     <row r="1140" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1140" s="17"/>
-      <c r="B1140" s="17"/>
+      <c r="A1140" s="8"/>
+      <c r="B1140" s="8"/>
     </row>
     <row r="1141" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1141" s="17"/>
-      <c r="B1141" s="17"/>
+      <c r="A1141" s="8"/>
+      <c r="B1141" s="8"/>
     </row>
     <row r="1142" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1142" s="17"/>
-      <c r="B1142" s="17"/>
+      <c r="A1142" s="8"/>
+      <c r="B1142" s="8"/>
     </row>
     <row r="1143" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1143" s="17"/>
-      <c r="B1143" s="17"/>
+      <c r="A1143" s="8"/>
+      <c r="B1143" s="8"/>
     </row>
     <row r="1144" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1144" s="17"/>
-      <c r="B1144" s="17"/>
+      <c r="A1144" s="8"/>
+      <c r="B1144" s="8"/>
     </row>
     <row r="1145" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1145" s="17"/>
-      <c r="B1145" s="17"/>
+      <c r="A1145" s="8"/>
+      <c r="B1145" s="8"/>
     </row>
     <row r="1146" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1146" s="17"/>
-      <c r="B1146" s="17"/>
+      <c r="A1146" s="8"/>
+      <c r="B1146" s="8"/>
     </row>
     <row r="1147" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1147" s="17"/>
-      <c r="B1147" s="17"/>
+      <c r="A1147" s="8"/>
+      <c r="B1147" s="8"/>
     </row>
     <row r="1148" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1148" s="17"/>
-      <c r="B1148" s="17"/>
+      <c r="A1148" s="8"/>
+      <c r="B1148" s="8"/>
     </row>
     <row r="1149" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1149" s="17"/>
-      <c r="B1149" s="17"/>
+      <c r="A1149" s="8"/>
+      <c r="B1149" s="8"/>
     </row>
     <row r="1150" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1150" s="17"/>
-      <c r="B1150" s="17"/>
+      <c r="A1150" s="8"/>
+      <c r="B1150" s="8"/>
     </row>
     <row r="1151" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1151" s="17"/>
-      <c r="B1151" s="17"/>
+      <c r="A1151" s="8"/>
+      <c r="B1151" s="8"/>
     </row>
     <row r="1152" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1152" s="17"/>
-      <c r="B1152" s="17"/>
+      <c r="A1152" s="8"/>
+      <c r="B1152" s="8"/>
     </row>
     <row r="1153" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1153" s="17"/>
-      <c r="B1153" s="17"/>
+      <c r="A1153" s="8"/>
+      <c r="B1153" s="8"/>
     </row>
     <row r="1154" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1154" s="17"/>
-      <c r="B1154" s="17"/>
+      <c r="A1154" s="8"/>
+      <c r="B1154" s="8"/>
     </row>
     <row r="1155" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1155" s="17"/>
-      <c r="B1155" s="17"/>
+      <c r="A1155" s="8"/>
+      <c r="B1155" s="8"/>
     </row>
     <row r="1156" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1156" s="17"/>
-      <c r="B1156" s="17"/>
+      <c r="A1156" s="8"/>
+      <c r="B1156" s="8"/>
     </row>
     <row r="1157" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1157" s="17"/>
-      <c r="B1157" s="17"/>
+      <c r="A1157" s="8"/>
+      <c r="B1157" s="8"/>
     </row>
     <row r="1158" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1158" s="17"/>
-      <c r="B1158" s="17"/>
+      <c r="A1158" s="8"/>
+      <c r="B1158" s="8"/>
     </row>
     <row r="1159" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1159" s="17"/>
-      <c r="B1159" s="17"/>
+      <c r="A1159" s="8"/>
+      <c r="B1159" s="8"/>
     </row>
     <row r="1160" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1160" s="17"/>
-      <c r="B1160" s="17"/>
+      <c r="A1160" s="8"/>
+      <c r="B1160" s="8"/>
     </row>
     <row r="1161" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1161" s="17"/>
-      <c r="B1161" s="17"/>
+      <c r="A1161" s="8"/>
+      <c r="B1161" s="8"/>
     </row>
     <row r="1162" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1162" s="17"/>
-      <c r="B1162" s="17"/>
+      <c r="A1162" s="8"/>
+      <c r="B1162" s="8"/>
     </row>
     <row r="1163" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1163" s="17"/>
-      <c r="B1163" s="17"/>
+      <c r="A1163" s="8"/>
+      <c r="B1163" s="8"/>
     </row>
     <row r="1164" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1164" s="17"/>
-      <c r="B1164" s="17"/>
+      <c r="A1164" s="8"/>
+      <c r="B1164" s="8"/>
     </row>
     <row r="1165" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1165" s="17"/>
-      <c r="B1165" s="17"/>
+      <c r="A1165" s="8"/>
+      <c r="B1165" s="8"/>
     </row>
     <row r="1166" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1166" s="17"/>
-      <c r="B1166" s="17"/>
+      <c r="A1166" s="8"/>
+      <c r="B1166" s="8"/>
     </row>
     <row r="1167" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1167" s="17"/>
-      <c r="B1167" s="17"/>
+      <c r="A1167" s="8"/>
+      <c r="B1167" s="8"/>
     </row>
     <row r="1168" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1168" s="17"/>
-      <c r="B1168" s="17"/>
+      <c r="A1168" s="8"/>
+      <c r="B1168" s="8"/>
     </row>
     <row r="1169" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1169" s="17"/>
-      <c r="B1169" s="17"/>
+      <c r="A1169" s="8"/>
+      <c r="B1169" s="8"/>
     </row>
     <row r="1170" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1170" s="17"/>
-      <c r="B1170" s="17"/>
+      <c r="A1170" s="8"/>
+      <c r="B1170" s="8"/>
     </row>
     <row r="1171" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1171" s="17"/>
-      <c r="B1171" s="17"/>
+      <c r="A1171" s="8"/>
+      <c r="B1171" s="8"/>
     </row>
     <row r="1172" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1172" s="17"/>
-      <c r="B1172" s="17"/>
+      <c r="A1172" s="8"/>
+      <c r="B1172" s="8"/>
     </row>
     <row r="1173" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1173" s="17"/>
-      <c r="B1173" s="17"/>
+      <c r="A1173" s="8"/>
+      <c r="B1173" s="8"/>
     </row>
     <row r="1174" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1174" s="17"/>
-      <c r="B1174" s="17"/>
+      <c r="A1174" s="8"/>
+      <c r="B1174" s="8"/>
     </row>
     <row r="1175" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1175" s="17"/>
-      <c r="B1175" s="17"/>
+      <c r="A1175" s="8"/>
+      <c r="B1175" s="8"/>
     </row>
     <row r="1176" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1176" s="17"/>
-      <c r="B1176" s="17"/>
+      <c r="A1176" s="8"/>
+      <c r="B1176" s="8"/>
     </row>
     <row r="1177" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1177" s="17"/>
-      <c r="B1177" s="17"/>
+      <c r="A1177" s="8"/>
+      <c r="B1177" s="8"/>
     </row>
     <row r="1178" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1178" s="17"/>
-      <c r="B1178" s="17"/>
+      <c r="A1178" s="8"/>
+      <c r="B1178" s="8"/>
     </row>
     <row r="1179" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1179" s="17"/>
-      <c r="B1179" s="17"/>
+      <c r="A1179" s="8"/>
+      <c r="B1179" s="8"/>
     </row>
     <row r="1180" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1180" s="17"/>
-      <c r="B1180" s="17"/>
+      <c r="A1180" s="8"/>
+      <c r="B1180" s="8"/>
     </row>
     <row r="1181" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1181" s="17"/>
-      <c r="B1181" s="17"/>
+      <c r="A1181" s="8"/>
+      <c r="B1181" s="8"/>
     </row>
     <row r="1182" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1182" s="17"/>
-      <c r="B1182" s="17"/>
+      <c r="A1182" s="8"/>
+      <c r="B1182" s="8"/>
     </row>
     <row r="1183" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1183" s="17"/>
-      <c r="B1183" s="17"/>
+      <c r="A1183" s="8"/>
+      <c r="B1183" s="8"/>
     </row>
     <row r="1184" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1184" s="17"/>
-      <c r="B1184" s="17"/>
+      <c r="A1184" s="8"/>
+      <c r="B1184" s="8"/>
     </row>
     <row r="1185" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1185" s="17"/>
-      <c r="B1185" s="17"/>
+      <c r="A1185" s="8"/>
+      <c r="B1185" s="8"/>
     </row>
     <row r="1186" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1186" s="17"/>
-      <c r="B1186" s="17"/>
+      <c r="A1186" s="8"/>
+      <c r="B1186" s="8"/>
     </row>
     <row r="1187" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1187" s="17"/>
-      <c r="B1187" s="17"/>
+      <c r="A1187" s="8"/>
+      <c r="B1187" s="8"/>
     </row>
     <row r="1188" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1188" s="17"/>
-      <c r="B1188" s="17"/>
+      <c r="A1188" s="8"/>
+      <c r="B1188" s="8"/>
     </row>
     <row r="1189" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1189" s="17"/>
-      <c r="B1189" s="17"/>
+      <c r="A1189" s="8"/>
+      <c r="B1189" s="8"/>
     </row>
     <row r="1190" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1190" s="17"/>
-      <c r="B1190" s="17"/>
+      <c r="A1190" s="8"/>
+      <c r="B1190" s="8"/>
     </row>
     <row r="1191" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1191" s="17"/>
-      <c r="B1191" s="17"/>
+      <c r="A1191" s="8"/>
+      <c r="B1191" s="8"/>
     </row>
     <row r="1192" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1192" s="17"/>
-      <c r="B1192" s="17"/>
+      <c r="A1192" s="8"/>
+      <c r="B1192" s="8"/>
     </row>
     <row r="1193" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1193" s="17"/>
-      <c r="B1193" s="17"/>
+      <c r="A1193" s="8"/>
+      <c r="B1193" s="8"/>
     </row>
     <row r="1194" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1194" s="17"/>
-      <c r="B1194" s="17"/>
+      <c r="A1194" s="8"/>
+      <c r="B1194" s="8"/>
     </row>
     <row r="1195" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1195" s="17"/>
-      <c r="B1195" s="17"/>
-    </row>
-    <row r="1196" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1196" s="17"/>
-      <c r="B1196" s="17"/>
-    </row>
-    <row r="1197" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1197" s="17"/>
-      <c r="B1197" s="17"/>
-    </row>
-    <row r="1198" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1198" s="17"/>
-      <c r="B1198" s="17"/>
-    </row>
-    <row r="1199" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1199" s="17"/>
-      <c r="B1199" s="17"/>
-    </row>
-    <row r="1200" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1200" s="17"/>
-      <c r="B1200" s="17"/>
-    </row>
-    <row r="1201" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1201" s="17"/>
-      <c r="B1201" s="17"/>
-    </row>
-    <row r="1202" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1202" s="17"/>
-      <c r="B1202" s="17"/>
-    </row>
-    <row r="1203" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1203" s="17"/>
-      <c r="B1203" s="17"/>
-    </row>
-    <row r="1204" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1204" s="17"/>
-      <c r="B1204" s="17"/>
-    </row>
-    <row r="1205" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1205" s="17"/>
-      <c r="B1205" s="17"/>
-    </row>
-    <row r="1206" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1206" s="17"/>
-      <c r="B1206" s="17"/>
-    </row>
-    <row r="1207" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1207" s="17"/>
-      <c r="B1207" s="17"/>
-    </row>
-    <row r="1208" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1208" s="17"/>
-      <c r="B1208" s="17"/>
-    </row>
-    <row r="1209" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1209" s="17"/>
-      <c r="B1209" s="17"/>
-    </row>
-    <row r="1210" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1210" s="17"/>
-      <c r="B1210" s="17"/>
-    </row>
-    <row r="1211" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1211" s="17"/>
-      <c r="B1211" s="17"/>
-    </row>
-    <row r="1212" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1212" s="17"/>
-      <c r="B1212" s="17"/>
-    </row>
-    <row r="1213" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1213" s="17"/>
-      <c r="B1213" s="17"/>
-    </row>
-    <row r="1214" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1214" s="17"/>
-      <c r="B1214" s="17"/>
-    </row>
-    <row r="1215" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1215" s="17"/>
-      <c r="B1215" s="17"/>
-    </row>
-    <row r="1216" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1216" s="17"/>
-      <c r="B1216" s="17"/>
-    </row>
-    <row r="1217" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1217" s="17"/>
-      <c r="B1217" s="17"/>
-    </row>
-    <row r="1218" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1218" s="17"/>
-      <c r="B1218" s="17"/>
-    </row>
-    <row r="1219" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1219" s="17"/>
-      <c r="B1219" s="17"/>
-    </row>
-    <row r="1220" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1220" s="17"/>
-      <c r="B1220" s="17"/>
-    </row>
-    <row r="1221" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1221" s="17"/>
-      <c r="B1221" s="17"/>
-    </row>
-    <row r="1222" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1222" s="17"/>
-      <c r="B1222" s="17"/>
-    </row>
-    <row r="1223" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1223" s="17"/>
-      <c r="B1223" s="17"/>
-    </row>
-    <row r="1224" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1224" s="17"/>
-      <c r="B1224" s="17"/>
-    </row>
-    <row r="1225" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1225" s="17"/>
-      <c r="B1225" s="17"/>
-    </row>
-    <row r="1226" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1226" s="17"/>
-      <c r="B1226" s="17"/>
-    </row>
-    <row r="1227" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1227" s="17"/>
-      <c r="B1227" s="17"/>
-    </row>
-    <row r="1228" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1228" s="17"/>
-      <c r="B1228" s="17"/>
-    </row>
-    <row r="1229" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1229" s="17"/>
-      <c r="B1229" s="17"/>
-    </row>
-    <row r="1230" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1230" s="17"/>
-      <c r="B1230" s="17"/>
-    </row>
-    <row r="1231" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1231" s="17"/>
-      <c r="B1231" s="17"/>
-    </row>
-    <row r="1232" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1232" s="17"/>
-      <c r="B1232" s="17"/>
-    </row>
-    <row r="1233" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1233" s="17"/>
-      <c r="B1233" s="17"/>
-    </row>
-    <row r="1234" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1234" s="17"/>
-      <c r="B1234" s="17"/>
-    </row>
-    <row r="1235" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1235" s="17"/>
-      <c r="B1235" s="17"/>
-    </row>
-    <row r="1236" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1236" s="17"/>
-      <c r="B1236" s="17"/>
-    </row>
-    <row r="1237" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1237" s="17"/>
-      <c r="B1237" s="17"/>
-    </row>
-    <row r="1238" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1238" s="17"/>
-      <c r="B1238" s="17"/>
-    </row>
-    <row r="1239" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1239" s="17"/>
-      <c r="B1239" s="17"/>
-    </row>
-    <row r="1240" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1240" s="17"/>
-      <c r="B1240" s="17"/>
-    </row>
-    <row r="1241" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1241" s="17"/>
-      <c r="B1241" s="17"/>
-    </row>
-    <row r="1242" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1242" s="17"/>
-      <c r="B1242" s="17"/>
-    </row>
-    <row r="1243" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1243" s="17"/>
-      <c r="B1243" s="17"/>
-    </row>
-    <row r="1244" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1244" s="17"/>
-      <c r="B1244" s="17"/>
-    </row>
-    <row r="1245" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1245" s="17"/>
-      <c r="B1245" s="17"/>
-    </row>
-    <row r="1246" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1246" s="17"/>
-      <c r="B1246" s="17"/>
-    </row>
-    <row r="1247" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1247" s="17"/>
-      <c r="B1247" s="17"/>
-    </row>
-    <row r="1248" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1248" s="17"/>
-      <c r="B1248" s="17"/>
-    </row>
-    <row r="1249" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1249" s="17"/>
-      <c r="B1249" s="17"/>
-    </row>
-    <row r="1250" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1250" s="17"/>
-      <c r="B1250" s="17"/>
-    </row>
-    <row r="1251" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1251" s="17"/>
-      <c r="B1251" s="17"/>
-    </row>
-    <row r="1252" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1252" s="17"/>
-      <c r="B1252" s="17"/>
-    </row>
-    <row r="1253" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1253" s="17"/>
-      <c r="B1253" s="17"/>
-    </row>
-    <row r="1254" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1254" s="17"/>
-      <c r="B1254" s="17"/>
-    </row>
-    <row r="1255" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1255" s="17"/>
-      <c r="B1255" s="17"/>
-    </row>
-    <row r="1256" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1256" s="17"/>
-      <c r="B1256" s="17"/>
-    </row>
-    <row r="1257" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1257" s="17"/>
-      <c r="B1257" s="17"/>
-    </row>
-    <row r="1258" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1258" s="17"/>
-      <c r="B1258" s="17"/>
-    </row>
-    <row r="1259" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1259" s="17"/>
-      <c r="B1259" s="17"/>
-    </row>
-    <row r="1260" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1260" s="17"/>
-      <c r="B1260" s="17"/>
-    </row>
-    <row r="1261" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1261" s="17"/>
-      <c r="B1261" s="17"/>
-    </row>
-    <row r="1262" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1262" s="17"/>
-      <c r="B1262" s="17"/>
-    </row>
-    <row r="1263" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1263" s="17"/>
-      <c r="B1263" s="17"/>
-    </row>
-    <row r="1264" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1264" s="17"/>
-      <c r="B1264" s="17"/>
-    </row>
-    <row r="1265" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1265" s="17"/>
-      <c r="B1265" s="17"/>
-    </row>
-    <row r="1266" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1266" s="17"/>
-      <c r="B1266" s="17"/>
-    </row>
-    <row r="1267" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1267" s="17"/>
-      <c r="B1267" s="17"/>
-    </row>
-    <row r="1268" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1268" s="17"/>
-      <c r="B1268" s="17"/>
-    </row>
-    <row r="1269" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1269" s="17"/>
-      <c r="B1269" s="17"/>
-    </row>
-    <row r="1270" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1270" s="17"/>
-      <c r="B1270" s="17"/>
-    </row>
-    <row r="1271" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1271" s="17"/>
-      <c r="B1271" s="17"/>
-    </row>
-    <row r="1272" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1272" s="17"/>
-      <c r="B1272" s="17"/>
-    </row>
-    <row r="1273" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1273" s="17"/>
-      <c r="B1273" s="17"/>
-    </row>
-    <row r="1274" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1274" s="17"/>
-      <c r="B1274" s="17"/>
-    </row>
-    <row r="1275" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1275" s="17"/>
-      <c r="B1275" s="17"/>
-    </row>
-    <row r="1276" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1276" s="17"/>
-      <c r="B1276" s="17"/>
-    </row>
-    <row r="1277" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1277" s="17"/>
-      <c r="B1277" s="17"/>
-    </row>
-    <row r="1278" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1278" s="17"/>
-      <c r="B1278" s="17"/>
-    </row>
-    <row r="1279" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1279" s="17"/>
-      <c r="B1279" s="17"/>
-    </row>
-    <row r="1280" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1280" s="17"/>
-      <c r="B1280" s="17"/>
-    </row>
-    <row r="1281" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1281" s="17"/>
-      <c r="B1281" s="17"/>
-    </row>
-    <row r="1282" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1282" s="17"/>
-      <c r="B1282" s="17"/>
-    </row>
-    <row r="1283" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1283" s="17"/>
-      <c r="B1283" s="17"/>
-    </row>
-    <row r="1284" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1284" s="17"/>
-      <c r="B1284" s="17"/>
-    </row>
-    <row r="1285" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1285" s="17"/>
-      <c r="B1285" s="17"/>
-    </row>
-    <row r="1286" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1286" s="17"/>
-      <c r="B1286" s="17"/>
-    </row>
-    <row r="1287" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1287" s="17"/>
-      <c r="B1287" s="17"/>
-    </row>
-    <row r="1288" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1288" s="17"/>
-      <c r="B1288" s="17"/>
-    </row>
-    <row r="1289" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1289" s="17"/>
-      <c r="B1289" s="17"/>
-    </row>
-    <row r="1290" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1290" s="17"/>
-      <c r="B1290" s="17"/>
-    </row>
-    <row r="1291" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1291" s="17"/>
-      <c r="B1291" s="17"/>
-    </row>
-    <row r="1292" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1292" s="17"/>
-      <c r="B1292" s="17"/>
-    </row>
-    <row r="1293" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1293" s="17"/>
-      <c r="B1293" s="17"/>
-    </row>
-    <row r="1294" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1294" s="17"/>
-      <c r="B1294" s="17"/>
-    </row>
-    <row r="1295" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1295" s="17"/>
-      <c r="B1295" s="17"/>
-    </row>
-    <row r="1296" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1296" s="17"/>
-      <c r="B1296" s="17"/>
-    </row>
-    <row r="1297" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1297" s="17"/>
-      <c r="B1297" s="17"/>
-    </row>
-    <row r="1298" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1298" s="17"/>
-      <c r="B1298" s="17"/>
-    </row>
-    <row r="1299" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1299" s="17"/>
-      <c r="B1299" s="17"/>
-    </row>
-    <row r="1300" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1300" s="17"/>
-      <c r="B1300" s="17"/>
-    </row>
-    <row r="1301" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1301" s="17"/>
-      <c r="B1301" s="17"/>
-    </row>
-    <row r="1302" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1302" s="17"/>
-      <c r="B1302" s="17"/>
-    </row>
-    <row r="1303" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1303" s="17"/>
-      <c r="B1303" s="17"/>
-    </row>
-    <row r="1304" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1304" s="17"/>
-      <c r="B1304" s="17"/>
-    </row>
-    <row r="1305" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1305" s="17"/>
-      <c r="B1305" s="17"/>
-    </row>
-    <row r="1306" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1306" s="17"/>
-      <c r="B1306" s="17"/>
-    </row>
-    <row r="1307" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1307" s="17"/>
-      <c r="B1307" s="17"/>
-    </row>
-    <row r="1308" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1308" s="17"/>
-      <c r="B1308" s="17"/>
-    </row>
-    <row r="1309" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1309" s="17"/>
-      <c r="B1309" s="17"/>
-    </row>
-    <row r="1310" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1310" s="17"/>
-      <c r="B1310" s="17"/>
-    </row>
-    <row r="1311" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1311" s="17"/>
-      <c r="B1311" s="17"/>
-    </row>
-    <row r="1312" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1312" s="17"/>
-      <c r="B1312" s="17"/>
-    </row>
-    <row r="1313" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1313" s="17"/>
-      <c r="B1313" s="17"/>
-    </row>
-    <row r="1314" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1314" s="17"/>
-      <c r="B1314" s="17"/>
-    </row>
-    <row r="1315" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1315" s="17"/>
-      <c r="B1315" s="17"/>
-    </row>
-    <row r="1316" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1316" s="17"/>
-      <c r="B1316" s="17"/>
-    </row>
-    <row r="1317" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1317" s="17"/>
-      <c r="B1317" s="17"/>
-    </row>
-    <row r="1318" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1318" s="17"/>
-      <c r="B1318" s="17"/>
-    </row>
-    <row r="1319" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1319" s="17"/>
-      <c r="B1319" s="17"/>
-    </row>
-    <row r="1320" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1320" s="17"/>
-      <c r="B1320" s="17"/>
-    </row>
-    <row r="1321" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1321" s="17"/>
-      <c r="B1321" s="17"/>
-    </row>
-    <row r="1322" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1322" s="17"/>
-      <c r="B1322" s="17"/>
-    </row>
-    <row r="1323" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1323" s="17"/>
-      <c r="B1323" s="17"/>
-    </row>
-    <row r="1324" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1324" s="17"/>
-      <c r="B1324" s="17"/>
-    </row>
-    <row r="1325" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1325" s="17"/>
-      <c r="B1325" s="17"/>
-    </row>
-    <row r="1326" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1326" s="17"/>
-      <c r="B1326" s="17"/>
-    </row>
-    <row r="1327" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1327" s="17"/>
-      <c r="B1327" s="17"/>
-    </row>
-    <row r="1328" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1328" s="17"/>
-      <c r="B1328" s="17"/>
-    </row>
-    <row r="1329" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1329" s="17"/>
-      <c r="B1329" s="17"/>
-    </row>
-    <row r="1330" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1330" s="17"/>
-      <c r="B1330" s="17"/>
-    </row>
-    <row r="1331" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1331" s="17"/>
-      <c r="B1331" s="17"/>
-    </row>
-    <row r="1332" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1332" s="17"/>
-      <c r="B1332" s="17"/>
-    </row>
-    <row r="1333" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1333" s="17"/>
-      <c r="B1333" s="17"/>
-    </row>
-    <row r="1334" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1334" s="17"/>
-      <c r="B1334" s="17"/>
-    </row>
-    <row r="1335" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1335" s="17"/>
-      <c r="B1335" s="17"/>
-    </row>
-    <row r="1336" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1336" s="17"/>
-      <c r="B1336" s="17"/>
-    </row>
-    <row r="1337" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1337" s="17"/>
-      <c r="B1337" s="17"/>
-    </row>
-    <row r="1338" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1338" s="17"/>
-      <c r="B1338" s="17"/>
-    </row>
-    <row r="1339" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1339" s="17"/>
-      <c r="B1339" s="17"/>
-    </row>
-    <row r="1340" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1340" s="17"/>
-      <c r="B1340" s="17"/>
-    </row>
-    <row r="1341" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1341" s="17"/>
-      <c r="B1341" s="17"/>
-    </row>
-    <row r="1342" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1342" s="17"/>
-      <c r="B1342" s="17"/>
-    </row>
-    <row r="1343" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1343" s="17"/>
-      <c r="B1343" s="17"/>
-    </row>
-    <row r="1344" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1344" s="17"/>
-      <c r="B1344" s="17"/>
-    </row>
-    <row r="1345" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1345" s="17"/>
-      <c r="B1345" s="17"/>
-    </row>
-    <row r="1346" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1346" s="17"/>
-      <c r="B1346" s="17"/>
-    </row>
-    <row r="1347" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1347" s="17"/>
-      <c r="B1347" s="17"/>
-    </row>
-    <row r="1348" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1348" s="17"/>
-      <c r="B1348" s="17"/>
-    </row>
-    <row r="1349" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1349" s="17"/>
-      <c r="B1349" s="17"/>
-    </row>
-    <row r="1350" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1350" s="17"/>
-      <c r="B1350" s="17"/>
-    </row>
-    <row r="1351" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1351" s="17"/>
-      <c r="B1351" s="17"/>
-    </row>
-    <row r="1352" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1352" s="17"/>
-      <c r="B1352" s="17"/>
-    </row>
-    <row r="1353" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1353" s="17"/>
-      <c r="B1353" s="17"/>
-    </row>
-    <row r="1354" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1354" s="17"/>
-      <c r="B1354" s="17"/>
-    </row>
-    <row r="1355" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1355" s="17"/>
-      <c r="B1355" s="17"/>
-    </row>
-    <row r="1356" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1356" s="17"/>
-      <c r="B1356" s="17"/>
-    </row>
-    <row r="1357" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1357" s="17"/>
-      <c r="B1357" s="17"/>
-    </row>
-    <row r="1358" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1358" s="17"/>
-      <c r="B1358" s="17"/>
-    </row>
-    <row r="1359" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1359" s="17"/>
-      <c r="B1359" s="17"/>
-    </row>
-    <row r="1360" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1360" s="17"/>
-      <c r="B1360" s="17"/>
-    </row>
-    <row r="1361" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1361" s="17"/>
-      <c r="B1361" s="17"/>
-    </row>
-    <row r="1362" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1362" s="17"/>
-      <c r="B1362" s="17"/>
-    </row>
-    <row r="1363" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1363" s="17"/>
-      <c r="B1363" s="17"/>
-    </row>
-    <row r="1364" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1364" s="17"/>
-      <c r="B1364" s="17"/>
-    </row>
-    <row r="1365" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1365" s="17"/>
-      <c r="B1365" s="17"/>
-    </row>
-    <row r="1366" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1366" s="17"/>
-      <c r="B1366" s="17"/>
-    </row>
-    <row r="1367" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1367" s="17"/>
-      <c r="B1367" s="17"/>
-    </row>
-    <row r="1368" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1368" s="17"/>
-      <c r="B1368" s="17"/>
-    </row>
-    <row r="1369" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1369" s="17"/>
-      <c r="B1369" s="17"/>
-    </row>
-    <row r="1370" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1370" s="17"/>
-      <c r="B1370" s="17"/>
-    </row>
-    <row r="1371" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1371" s="17"/>
-      <c r="B1371" s="17"/>
-    </row>
-    <row r="1372" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1372" s="17"/>
-      <c r="B1372" s="17"/>
-    </row>
-    <row r="1373" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1373" s="17"/>
-      <c r="B1373" s="17"/>
-    </row>
-    <row r="1374" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1374" s="17"/>
-      <c r="B1374" s="17"/>
-    </row>
-    <row r="1375" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1375" s="17"/>
-      <c r="B1375" s="17"/>
-    </row>
-    <row r="1376" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1376" s="17"/>
-      <c r="B1376" s="17"/>
-    </row>
-    <row r="1377" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1377" s="17"/>
-      <c r="B1377" s="17"/>
-    </row>
-    <row r="1378" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1378" s="17"/>
-      <c r="B1378" s="17"/>
-    </row>
-    <row r="1379" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1379" s="17"/>
-      <c r="B1379" s="17"/>
-    </row>
-    <row r="1380" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1380" s="17"/>
-      <c r="B1380" s="17"/>
-    </row>
-    <row r="1381" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1381" s="17"/>
-      <c r="B1381" s="17"/>
-    </row>
-    <row r="1382" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1382" s="17"/>
-      <c r="B1382" s="17"/>
-    </row>
-    <row r="1383" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1383" s="17"/>
-      <c r="B1383" s="17"/>
-    </row>
-    <row r="1384" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1384" s="17"/>
-      <c r="B1384" s="17"/>
-    </row>
-    <row r="1385" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1385" s="17"/>
-      <c r="B1385" s="17"/>
-    </row>
-    <row r="1386" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1386" s="17"/>
-      <c r="B1386" s="17"/>
-    </row>
-    <row r="1387" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1387" s="17"/>
-      <c r="B1387" s="17"/>
-    </row>
-    <row r="1388" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1388" s="17"/>
-      <c r="B1388" s="17"/>
-    </row>
-    <row r="1389" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1389" s="17"/>
-      <c r="B1389" s="17"/>
-    </row>
-    <row r="1390" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1390" s="17"/>
-      <c r="B1390" s="17"/>
-    </row>
-    <row r="1391" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1391" s="17"/>
-      <c r="B1391" s="17"/>
-    </row>
-    <row r="1392" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1392" s="17"/>
-      <c r="B1392" s="17"/>
-    </row>
-    <row r="1393" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1393" s="17"/>
-      <c r="B1393" s="17"/>
-    </row>
-    <row r="1394" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1394" s="17"/>
-      <c r="B1394" s="17"/>
-    </row>
-    <row r="1395" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1395" s="17"/>
-      <c r="B1395" s="17"/>
-    </row>
-    <row r="1396" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1396" s="17"/>
-      <c r="B1396" s="17"/>
-    </row>
-    <row r="1397" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1397" s="17"/>
-      <c r="B1397" s="8"/>
-    </row>
-    <row r="1398" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1398" s="17"/>
-      <c r="B1398" s="8"/>
-    </row>
-    <row r="1399" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1399" s="17"/>
-      <c r="B1399" s="8"/>
-    </row>
-    <row r="1400" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1400" s="17"/>
-      <c r="B1400" s="8"/>
-    </row>
-    <row r="1401" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1401" s="17"/>
-      <c r="B1401" s="8"/>
-    </row>
-    <row r="1402" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1402" s="17"/>
-      <c r="B1402" s="8"/>
-    </row>
-    <row r="1403" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1403" s="17"/>
-      <c r="B1403" s="8"/>
-    </row>
-    <row r="1404" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1404" s="17"/>
-      <c r="B1404" s="8"/>
-    </row>
-    <row r="1405" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1405" s="17"/>
-      <c r="B1405" s="8"/>
-    </row>
-    <row r="1406" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1406" s="17"/>
-      <c r="B1406" s="8"/>
-    </row>
-    <row r="1407" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1407" s="17"/>
-      <c r="B1407" s="8"/>
-    </row>
-    <row r="1408" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1408" s="17"/>
-      <c r="B1408" s="8"/>
-    </row>
-    <row r="1409" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1409" s="17"/>
-      <c r="B1409" s="8"/>
-    </row>
-    <row r="1410" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1410" s="17"/>
-      <c r="B1410" s="8"/>
-    </row>
-    <row r="1411" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1411" s="17"/>
-      <c r="B1411" s="8"/>
-    </row>
-    <row r="1412" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1412" s="17"/>
-      <c r="B1412" s="8"/>
-    </row>
-    <row r="1413" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1413" s="17"/>
-      <c r="B1413" s="8"/>
-    </row>
-    <row r="1414" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1414" s="17"/>
-      <c r="B1414" s="8"/>
-    </row>
-    <row r="1415" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1415" s="17"/>
-      <c r="B1415" s="8"/>
-    </row>
-    <row r="1416" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1416" s="17"/>
-      <c r="B1416" s="8"/>
-    </row>
-    <row r="1417" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1417" s="17"/>
-      <c r="B1417" s="8"/>
-    </row>
-    <row r="1418" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1418" s="17"/>
-      <c r="B1418" s="8"/>
-    </row>
-    <row r="1419" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1419" s="17"/>
-      <c r="B1419" s="8"/>
-    </row>
-    <row r="1420" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1420" s="17"/>
-      <c r="B1420" s="8"/>
-    </row>
-    <row r="1421" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1421" s="17"/>
-      <c r="B1421" s="8"/>
-    </row>
-    <row r="1422" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1422" s="17"/>
-      <c r="B1422" s="8"/>
-    </row>
-    <row r="1423" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1423" s="17"/>
-      <c r="B1423" s="8"/>
-    </row>
-    <row r="1424" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1424" s="17"/>
-      <c r="B1424" s="8"/>
-    </row>
-    <row r="1425" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1425" s="17"/>
-      <c r="B1425" s="8"/>
-    </row>
-    <row r="1426" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1426" s="17"/>
-      <c r="B1426" s="8"/>
-    </row>
-    <row r="1427" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1427" s="17"/>
-      <c r="B1427" s="8"/>
-    </row>
-    <row r="1428" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1428" s="17"/>
-      <c r="B1428" s="8"/>
-    </row>
-    <row r="1429" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1429" s="17"/>
-      <c r="B1429" s="8"/>
-    </row>
-    <row r="1430" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1430" s="17"/>
-      <c r="B1430" s="8"/>
-    </row>
-    <row r="1431" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1431" s="17"/>
-      <c r="B1431" s="8"/>
-    </row>
-    <row r="1432" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1432" s="17"/>
-      <c r="B1432" s="8"/>
-    </row>
-    <row r="1433" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1433" s="17"/>
-      <c r="B1433" s="8"/>
-    </row>
-    <row r="1434" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1434" s="17"/>
-      <c r="B1434" s="8"/>
-    </row>
-    <row r="1435" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1435" s="17"/>
-      <c r="B1435" s="8"/>
-    </row>
-    <row r="1436" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1436" s="17"/>
-      <c r="B1436" s="8"/>
-    </row>
-    <row r="1437" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1437" s="17"/>
-      <c r="B1437" s="8"/>
-    </row>
-    <row r="1438" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1438" s="17"/>
-      <c r="B1438" s="8"/>
-    </row>
-    <row r="1439" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1439" s="17"/>
-      <c r="B1439" s="8"/>
-    </row>
-    <row r="1440" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1440" s="17"/>
-      <c r="B1440" s="8"/>
-    </row>
-    <row r="1441" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1441" s="17"/>
-      <c r="B1441" s="8"/>
-    </row>
-    <row r="1442" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1442" s="17"/>
-      <c r="B1442" s="8"/>
-    </row>
-    <row r="1443" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1443" s="17"/>
-      <c r="B1443" s="8"/>
-    </row>
-    <row r="1444" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1444" s="17"/>
-      <c r="B1444" s="8"/>
-    </row>
-    <row r="1445" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1445" s="17"/>
-      <c r="B1445" s="8"/>
-    </row>
-    <row r="1446" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1446" s="17"/>
-      <c r="B1446" s="8"/>
-    </row>
-    <row r="1447" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1447" s="17"/>
-      <c r="B1447" s="8"/>
-    </row>
-    <row r="1448" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1448" s="17"/>
-      <c r="B1448" s="8"/>
-    </row>
-    <row r="1449" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1449" s="17"/>
-      <c r="B1449" s="8"/>
-    </row>
-    <row r="1450" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1450" s="17"/>
-      <c r="B1450" s="8"/>
-    </row>
-    <row r="1451" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1451" s="17"/>
-      <c r="B1451" s="8"/>
-    </row>
-    <row r="1452" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1452" s="17"/>
-      <c r="B1452" s="8"/>
-    </row>
-    <row r="1453" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1453" s="17"/>
-      <c r="B1453" s="8"/>
-    </row>
-    <row r="1454" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1454" s="17"/>
-      <c r="B1454" s="8"/>
-    </row>
-    <row r="1455" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1455" s="17"/>
-      <c r="B1455" s="8"/>
-    </row>
-    <row r="1456" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1456" s="17"/>
-      <c r="B1456" s="8"/>
-    </row>
-    <row r="1457" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1457" s="17"/>
-      <c r="B1457" s="8"/>
-    </row>
-    <row r="1458" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1458" s="17"/>
-      <c r="B1458" s="8"/>
-    </row>
-    <row r="1459" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1459" s="17"/>
-      <c r="B1459" s="8"/>
-    </row>
-    <row r="1460" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1460" s="17"/>
-      <c r="B1460" s="8"/>
-    </row>
-    <row r="1461" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1461" s="17"/>
-      <c r="B1461" s="8"/>
-    </row>
-    <row r="1462" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1462" s="17"/>
-      <c r="B1462" s="8"/>
-    </row>
-    <row r="1463" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1463" s="17"/>
-      <c r="B1463" s="8"/>
-    </row>
-    <row r="1464" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1464" s="17"/>
-      <c r="B1464" s="8"/>
-    </row>
-    <row r="1465" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1465" s="8"/>
-      <c r="B1465" s="8"/>
-    </row>
-    <row r="1466" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1466" s="8"/>
-      <c r="B1466" s="8"/>
-    </row>
-    <row r="1467" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1467" s="8"/>
-      <c r="B1467" s="8"/>
-    </row>
-    <row r="1468" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1468" s="8"/>
-      <c r="B1468" s="8"/>
-    </row>
-    <row r="1469" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1469" s="8"/>
-      <c r="B1469" s="8"/>
-    </row>
-    <row r="1470" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1470" s="8"/>
-      <c r="B1470" s="8"/>
-    </row>
-    <row r="1471" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1471" s="8"/>
-      <c r="B1471" s="8"/>
-    </row>
-    <row r="1472" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1472" s="8"/>
-      <c r="B1472" s="8"/>
-    </row>
-    <row r="1473" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1473" s="8"/>
-      <c r="B1473" s="8"/>
-    </row>
-    <row r="1474" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1474" s="8"/>
-      <c r="B1474" s="8"/>
-    </row>
-    <row r="1475" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1475" s="8"/>
-      <c r="B1475" s="8"/>
-    </row>
-    <row r="1476" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1476" s="8"/>
-      <c r="B1476" s="8"/>
-    </row>
-    <row r="1477" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1477" s="8"/>
-      <c r="B1477" s="8"/>
-    </row>
-    <row r="1478" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1478" s="8"/>
-      <c r="B1478" s="8"/>
-    </row>
-    <row r="1479" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1479" s="8"/>
-      <c r="B1479" s="8"/>
-    </row>
-    <row r="1480" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1480" s="8"/>
-      <c r="B1480" s="8"/>
-    </row>
-    <row r="1481" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1481" s="8"/>
-      <c r="B1481" s="8"/>
-    </row>
-    <row r="1482" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1482" s="8"/>
-      <c r="B1482" s="8"/>
-    </row>
-    <row r="1483" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1483" s="8"/>
-      <c r="B1483" s="8"/>
-    </row>
-    <row r="1484" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1484" s="8"/>
-      <c r="B1484" s="8"/>
-    </row>
-    <row r="1485" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1485" s="8"/>
-      <c r="B1485" s="8"/>
-    </row>
-    <row r="1486" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1486" s="8"/>
-      <c r="B1486" s="8"/>
-    </row>
-    <row r="1487" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1487" s="8"/>
-      <c r="B1487" s="8"/>
-    </row>
-    <row r="1488" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1488" s="8"/>
-      <c r="B1488" s="8"/>
-    </row>
-    <row r="1489" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1489" s="8"/>
-      <c r="B1489" s="8"/>
-    </row>
-    <row r="1490" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1490" s="8"/>
-      <c r="B1490" s="8"/>
-    </row>
-    <row r="1491" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1491" s="8"/>
-      <c r="B1491" s="8"/>
-    </row>
-    <row r="1492" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1492" s="8"/>
-      <c r="B1492" s="8"/>
-    </row>
-    <row r="1493" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1493" s="8"/>
-      <c r="B1493" s="8"/>
-    </row>
-    <row r="1494" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1494" s="8"/>
-      <c r="B1494" s="8"/>
-    </row>
-    <row r="1495" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1495" s="8"/>
-      <c r="B1495" s="8"/>
-    </row>
-    <row r="1496" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1496" s="8"/>
-      <c r="B1496" s="8"/>
-    </row>
-    <row r="1497" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1497" s="8"/>
-      <c r="B1497" s="8"/>
-    </row>
-    <row r="1498" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1498" s="8"/>
-      <c r="B1498" s="8"/>
-    </row>
-    <row r="1499" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1499" s="8"/>
-      <c r="B1499" s="8"/>
-    </row>
-    <row r="1500" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1500" s="8"/>
-      <c r="B1500" s="8"/>
-    </row>
-    <row r="1501" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1501" s="8"/>
-      <c r="B1501" s="8"/>
-    </row>
-    <row r="1502" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1502" s="8"/>
-      <c r="B1502" s="8"/>
-    </row>
-    <row r="1503" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1503" s="8"/>
-      <c r="B1503" s="8"/>
-    </row>
-    <row r="1504" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1504" s="8"/>
-      <c r="B1504" s="8"/>
-    </row>
-    <row r="1505" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1505" s="8"/>
-      <c r="B1505" s="8"/>
-    </row>
-    <row r="1506" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1506" s="8"/>
-      <c r="B1506" s="8"/>
-    </row>
-    <row r="1507" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1507" s="8"/>
-      <c r="B1507" s="8"/>
-    </row>
-    <row r="1508" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1508" s="8"/>
-      <c r="B1508" s="8"/>
-    </row>
-    <row r="1509" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1509" s="8"/>
-      <c r="B1509" s="8"/>
-    </row>
-    <row r="1510" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1510" s="8"/>
-      <c r="B1510" s="8"/>
-    </row>
-    <row r="1511" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1511" s="8"/>
-      <c r="B1511" s="8"/>
-    </row>
-    <row r="1512" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1512" s="8"/>
-      <c r="B1512" s="8"/>
-    </row>
-    <row r="1513" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1513" s="8"/>
-      <c r="B1513" s="8"/>
-    </row>
-    <row r="1514" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1514" s="8"/>
-      <c r="B1514" s="8"/>
-    </row>
-    <row r="1515" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1515" s="8"/>
-      <c r="B1515" s="8"/>
-    </row>
-    <row r="1516" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1516" s="8"/>
-      <c r="B1516" s="8"/>
-    </row>
-    <row r="1517" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1517" s="8"/>
-      <c r="B1517" s="8"/>
-    </row>
-    <row r="1518" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1518" s="8"/>
-      <c r="B1518" s="8"/>
-    </row>
-    <row r="1519" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1519" s="8"/>
-      <c r="B1519" s="8"/>
-    </row>
-    <row r="1520" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1520" s="8"/>
-      <c r="B1520" s="8"/>
-    </row>
-    <row r="1521" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1521" s="8"/>
-      <c r="B1521" s="8"/>
-    </row>
-    <row r="1522" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1522" s="8"/>
-      <c r="B1522" s="8"/>
-    </row>
-    <row r="1523" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1523" s="8"/>
-      <c r="B1523" s="8"/>
-    </row>
-    <row r="1524" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1524" s="8"/>
-      <c r="B1524" s="8"/>
-    </row>
-    <row r="1525" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1525" s="8"/>
-      <c r="B1525" s="8"/>
-    </row>
-    <row r="1526" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1526" s="8"/>
-      <c r="B1526" s="8"/>
-    </row>
-    <row r="1527" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1527" s="8"/>
-      <c r="B1527" s="8"/>
-    </row>
-    <row r="1528" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1528" s="8"/>
-      <c r="B1528" s="8"/>
-    </row>
-    <row r="1529" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1529" s="8"/>
-      <c r="B1529" s="8"/>
-    </row>
-    <row r="1530" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1530" s="8"/>
-      <c r="B1530" s="8"/>
-    </row>
-    <row r="1531" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1531" s="8"/>
-      <c r="B1531" s="8"/>
-    </row>
-    <row r="1532" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1532" s="8"/>
-      <c r="B1532" s="8"/>
-    </row>
-    <row r="1533" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1533" s="8"/>
-      <c r="B1533" s="8"/>
-    </row>
-    <row r="1534" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1534" s="8"/>
-      <c r="B1534" s="8"/>
-    </row>
-    <row r="1535" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1535" s="8"/>
-      <c r="B1535" s="8"/>
-    </row>
-    <row r="1536" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1536" s="8"/>
-      <c r="B1536" s="8"/>
-    </row>
-    <row r="1537" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1537" s="8"/>
-      <c r="B1537" s="8"/>
-    </row>
-    <row r="1538" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1538" s="8"/>
-      <c r="B1538" s="8"/>
-    </row>
-    <row r="1539" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1539" s="8"/>
-      <c r="B1539" s="8"/>
-    </row>
-    <row r="1540" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1540" s="8"/>
-      <c r="B1540" s="8"/>
-    </row>
-    <row r="1541" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1541" s="8"/>
-      <c r="B1541" s="8"/>
-    </row>
-    <row r="1542" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1542" s="8"/>
-      <c r="B1542" s="8"/>
-    </row>
-    <row r="1543" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1543" s="8"/>
-      <c r="B1543" s="8"/>
-    </row>
-    <row r="1544" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1544" s="8"/>
-      <c r="B1544" s="8"/>
-    </row>
-    <row r="1545" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1545" s="8"/>
-      <c r="B1545" s="8"/>
-    </row>
-    <row r="1546" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1546" s="8"/>
-      <c r="B1546" s="8"/>
-    </row>
-    <row r="1547" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1547" s="8"/>
-      <c r="B1547" s="8"/>
-    </row>
-    <row r="1548" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1548" s="8"/>
-      <c r="B1548" s="8"/>
-    </row>
-    <row r="1549" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1549" s="8"/>
-      <c r="B1549" s="8"/>
-    </row>
-    <row r="1550" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1550" s="8"/>
-      <c r="B1550" s="8"/>
-    </row>
-    <row r="1551" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1551" s="8"/>
-      <c r="B1551" s="8"/>
-    </row>
-    <row r="1552" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1552" s="8"/>
-      <c r="B1552" s="8"/>
-    </row>
-    <row r="1553" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1553" s="8"/>
-      <c r="B1553" s="8"/>
-    </row>
-    <row r="1554" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1554" s="8"/>
-      <c r="B1554" s="8"/>
-    </row>
-    <row r="1555" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1555" s="8"/>
-      <c r="B1555" s="8"/>
-    </row>
-    <row r="1556" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1556" s="8"/>
-      <c r="B1556" s="8"/>
-    </row>
-    <row r="1557" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1557" s="8"/>
-      <c r="B1557" s="8"/>
-    </row>
-    <row r="1558" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1558" s="8"/>
-      <c r="B1558" s="8"/>
-    </row>
-    <row r="1559" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1559" s="8"/>
-      <c r="B1559" s="8"/>
-    </row>
-    <row r="1560" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1560" s="8"/>
-      <c r="B1560" s="8"/>
-    </row>
-    <row r="1561" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1561" s="8"/>
-      <c r="B1561" s="8"/>
-    </row>
-    <row r="1562" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1562" s="8"/>
-      <c r="B1562" s="8"/>
-    </row>
-    <row r="1563" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1563" s="8"/>
-      <c r="B1563" s="8"/>
-    </row>
-    <row r="1564" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1564" s="8"/>
-      <c r="B1564" s="8"/>
-    </row>
-    <row r="1565" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1565" s="8"/>
-      <c r="B1565" s="8"/>
-    </row>
-    <row r="1566" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1566" s="8"/>
-      <c r="B1566" s="8"/>
-    </row>
-    <row r="1567" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1567" s="8"/>
-      <c r="B1567" s="8"/>
-    </row>
-    <row r="1568" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1568" s="8"/>
-      <c r="B1568" s="8"/>
-    </row>
-    <row r="1569" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1569" s="8"/>
-      <c r="B1569" s="8"/>
-    </row>
-    <row r="1570" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1570" s="8"/>
-      <c r="B1570" s="8"/>
-    </row>
-    <row r="1571" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1571" s="8"/>
-      <c r="B1571" s="8"/>
-    </row>
-    <row r="1572" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1572" s="8"/>
-      <c r="B1572" s="8"/>
-    </row>
-    <row r="1573" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1573" s="8"/>
-      <c r="B1573" s="8"/>
-    </row>
-    <row r="1574" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1574" s="8"/>
-      <c r="B1574" s="8"/>
-    </row>
-    <row r="1575" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1575" s="8"/>
-      <c r="B1575" s="8"/>
-    </row>
-    <row r="1576" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1576" s="8"/>
-      <c r="B1576" s="8"/>
-    </row>
-    <row r="1577" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1577" s="8"/>
-      <c r="B1577" s="8"/>
-    </row>
-    <row r="1578" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1578" s="8"/>
-      <c r="B1578" s="8"/>
-    </row>
-    <row r="1579" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1579" s="8"/>
-      <c r="B1579" s="8"/>
-    </row>
-    <row r="1580" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1580" s="8"/>
-      <c r="B1580" s="8"/>
-    </row>
-    <row r="1581" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1581" s="8"/>
-      <c r="B1581" s="8"/>
-    </row>
-    <row r="1582" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1582" s="8"/>
-      <c r="B1582" s="8"/>
-    </row>
-    <row r="1583" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1583" s="8"/>
-      <c r="B1583" s="8"/>
-    </row>
-    <row r="1584" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1584" s="8"/>
-      <c r="B1584" s="8"/>
-    </row>
-    <row r="1585" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1585" s="8"/>
-      <c r="B1585" s="8"/>
-    </row>
-    <row r="1586" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1586" s="8"/>
-      <c r="B1586" s="8"/>
-    </row>
-    <row r="1587" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1587" s="8"/>
-      <c r="B1587" s="8"/>
-    </row>
-    <row r="1588" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1588" s="8"/>
-      <c r="B1588" s="8"/>
-    </row>
-    <row r="1589" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1589" s="8"/>
-      <c r="B1589" s="8"/>
-    </row>
-    <row r="1590" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1590" s="8"/>
-      <c r="B1590" s="8"/>
-    </row>
-    <row r="1591" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1591" s="8"/>
-      <c r="B1591" s="8"/>
-    </row>
-    <row r="1592" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1592" s="8"/>
-      <c r="B1592" s="8"/>
-    </row>
-    <row r="1593" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1593" s="8"/>
-      <c r="B1593" s="8"/>
-    </row>
-    <row r="1594" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1594" s="8"/>
-      <c r="B1594" s="8"/>
-    </row>
-    <row r="1595" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1595" s="8"/>
-      <c r="B1595" s="8"/>
-    </row>
-    <row r="1596" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1596" s="8"/>
-      <c r="B1596" s="8"/>
-    </row>
-    <row r="1597" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1597" s="8"/>
-      <c r="B1597" s="8"/>
-    </row>
-    <row r="1598" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1598" s="8"/>
-      <c r="B1598" s="8"/>
-    </row>
-    <row r="1599" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1599" s="8"/>
-      <c r="B1599" s="8"/>
-    </row>
-    <row r="1600" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1600" s="8"/>
-      <c r="B1600" s="8"/>
-    </row>
-    <row r="1601" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1601" s="8"/>
-      <c r="B1601" s="8"/>
-    </row>
-    <row r="1602" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1602" s="8"/>
-      <c r="B1602" s="8"/>
-    </row>
-    <row r="1603" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1603" s="8"/>
-      <c r="B1603" s="8"/>
-    </row>
-    <row r="1604" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1604" s="8"/>
-      <c r="B1604" s="8"/>
-    </row>
-    <row r="1605" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1605" s="8"/>
-      <c r="B1605" s="8"/>
-    </row>
-    <row r="1606" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1606" s="8"/>
-      <c r="B1606" s="8"/>
-    </row>
-    <row r="1607" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1607" s="8"/>
-      <c r="B1607" s="8"/>
-    </row>
-    <row r="1608" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1608" s="8"/>
-      <c r="B1608" s="8"/>
-    </row>
-    <row r="1609" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1609" s="8"/>
-      <c r="B1609" s="8"/>
-    </row>
-    <row r="1610" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1610" s="8"/>
-      <c r="B1610" s="8"/>
-    </row>
-    <row r="1611" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1611" s="8"/>
-      <c r="B1611" s="8"/>
-    </row>
-    <row r="1612" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1612" s="8"/>
-      <c r="B1612" s="8"/>
-    </row>
-    <row r="1613" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1613" s="8"/>
-      <c r="B1613" s="8"/>
-    </row>
-    <row r="1614" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1614" s="8"/>
-      <c r="B1614" s="8"/>
-    </row>
-    <row r="1615" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1615" s="8"/>
-      <c r="B1615" s="8"/>
-    </row>
-    <row r="1616" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1616" s="8"/>
-      <c r="B1616" s="8"/>
-    </row>
-    <row r="1617" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1617" s="8"/>
-      <c r="B1617" s="8"/>
-    </row>
-    <row r="1618" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1618" s="8"/>
-      <c r="B1618" s="8"/>
-    </row>
-    <row r="1619" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1619" s="8"/>
-      <c r="B1619" s="8"/>
-    </row>
-    <row r="1620" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1620" s="8"/>
-      <c r="B1620" s="8"/>
-    </row>
-    <row r="1621" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1621" s="8"/>
-      <c r="B1621" s="8"/>
-    </row>
-    <row r="1622" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1622" s="8"/>
-      <c r="B1622" s="8"/>
-    </row>
-    <row r="1623" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1623" s="8"/>
-      <c r="B1623" s="8"/>
-    </row>
-    <row r="1624" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1624" s="8"/>
-      <c r="B1624" s="8"/>
-    </row>
-    <row r="1625" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1625" s="8"/>
-      <c r="B1625" s="8"/>
-    </row>
-    <row r="1626" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1626" s="8"/>
-      <c r="B1626" s="8"/>
-    </row>
-    <row r="1627" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1627" s="8"/>
-      <c r="B1627" s="8"/>
-    </row>
-    <row r="1628" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1628" s="8"/>
-      <c r="B1628" s="8"/>
-    </row>
-    <row r="1629" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1629" s="8"/>
-      <c r="B1629" s="8"/>
-    </row>
-    <row r="1630" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1630" s="8"/>
-      <c r="B1630" s="8"/>
-    </row>
-    <row r="1631" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1631" s="8"/>
-      <c r="B1631" s="8"/>
-    </row>
-    <row r="1632" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1632" s="8"/>
-      <c r="B1632" s="8"/>
-    </row>
-    <row r="1633" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1633" s="8"/>
-      <c r="B1633" s="8"/>
-    </row>
-    <row r="1634" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1634" s="8"/>
-      <c r="B1634" s="8"/>
-    </row>
-    <row r="1635" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1635" s="8"/>
-      <c r="B1635" s="8"/>
-    </row>
-    <row r="1636" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1636" s="8"/>
-      <c r="B1636" s="8"/>
-    </row>
-    <row r="1637" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1637" s="8"/>
-      <c r="B1637" s="8"/>
-    </row>
-    <row r="1638" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1638" s="8"/>
-      <c r="B1638" s="8"/>
-    </row>
-    <row r="1639" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1639" s="8"/>
-      <c r="B1639" s="8"/>
-    </row>
-    <row r="1640" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1640" s="8"/>
-      <c r="B1640" s="8"/>
-    </row>
-    <row r="1641" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1641" s="8"/>
-      <c r="B1641" s="8"/>
-    </row>
-    <row r="1642" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1642" s="8"/>
-      <c r="B1642" s="8"/>
-    </row>
-    <row r="1643" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1643" s="8"/>
-      <c r="B1643" s="8"/>
-    </row>
-    <row r="1644" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1644" s="8"/>
-      <c r="B1644" s="8"/>
-    </row>
-    <row r="1645" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1645" s="8"/>
-      <c r="B1645" s="8"/>
-    </row>
-    <row r="1646" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1646" s="8"/>
-      <c r="B1646" s="8"/>
-    </row>
-    <row r="1647" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1647" s="8"/>
-      <c r="B1647" s="8"/>
-    </row>
-    <row r="1648" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1648" s="8"/>
-      <c r="B1648" s="8"/>
-    </row>
-    <row r="1649" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1649" s="8"/>
-      <c r="B1649" s="8"/>
-    </row>
-    <row r="1650" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1650" s="8"/>
-      <c r="B1650" s="8"/>
-    </row>
-    <row r="1651" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1651" s="8"/>
-      <c r="B1651" s="8"/>
-    </row>
-    <row r="1652" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1652" s="8"/>
-      <c r="B1652" s="8"/>
-    </row>
-    <row r="1653" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1653" s="8"/>
-      <c r="B1653" s="8"/>
-    </row>
-    <row r="1654" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1654" s="8"/>
-      <c r="B1654" s="8"/>
-    </row>
-    <row r="1655" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1655" s="8"/>
-      <c r="B1655" s="8"/>
-    </row>
-    <row r="1656" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1656" s="8"/>
-      <c r="B1656" s="8"/>
-    </row>
-    <row r="1657" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1657" s="8"/>
-      <c r="B1657" s="8"/>
-    </row>
-    <row r="1658" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1658" s="8"/>
-      <c r="B1658" s="8"/>
-    </row>
-    <row r="1659" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1659" s="8"/>
-      <c r="B1659" s="8"/>
+      <c r="A1195" s="8"/>
+      <c r="B1195" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dados/nomes_usuais.xlsx
+++ b/dados/nomes_usuais.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/catalogoPecas/dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://amaggicombr-my.sharepoint.com/personal/hiago_andre_amaggi_com_br/Documents/Área de Trabalho/codigos/catalogoPecas/dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B30F988B-CCBF-49C7-815A-6CB3693691D9}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_AD4D361C20488DEA4E38A03414D973025ADEDD81" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79F08109-DC03-4FB8-B58C-EA198379DF0C}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -1317,12 +1317,6 @@
     <t>Mecânica</t>
   </si>
   <si>
-    <t>CONECTOR MACHO 16X16MM (NÃO LANÇAR P/ ROTA)</t>
-  </si>
-  <si>
-    <t>TRAVA ELASTICA (não lançar)</t>
-  </si>
-  <si>
     <t>Elétrica</t>
   </si>
   <si>
@@ -1354,6 +1348,12 @@
   </si>
   <si>
     <t>categoria</t>
+  </si>
+  <si>
+    <t>CONECTOR MACHO 16X16MM</t>
+  </si>
+  <si>
+    <t>TRAVA ELASTICA</t>
   </si>
 </sst>
 </file>
@@ -1536,6 +1536,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1817,7 +1821,7 @@
         <v>425</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
@@ -2629,7 +2633,7 @@
         <v>341430</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>429</v>
@@ -5575,7 +5579,7 @@
         <v>1010024086</v>
       </c>
       <c r="B343" s="11" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="C343" s="6" t="s">
         <v>429</v>
@@ -5831,7 +5835,7 @@
         <v>361</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5842,7 +5846,7 @@
         <v>362</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5853,7 +5857,7 @@
         <v>363</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="369" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5864,7 +5868,7 @@
         <v>364</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="370" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5875,7 +5879,7 @@
         <v>365</v>
       </c>
       <c r="C370" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="371" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5886,7 +5890,7 @@
         <v>366</v>
       </c>
       <c r="C371" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="372" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5897,7 +5901,7 @@
         <v>367</v>
       </c>
       <c r="C372" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="373" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5908,7 +5912,7 @@
         <v>368</v>
       </c>
       <c r="C373" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="374" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5919,7 +5923,7 @@
         <v>369</v>
       </c>
       <c r="C374" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="375" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5930,7 +5934,7 @@
         <v>370</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="376" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5941,7 +5945,7 @@
         <v>371</v>
       </c>
       <c r="C376" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="377" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5952,7 +5956,7 @@
         <v>372</v>
       </c>
       <c r="C377" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="378" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5963,7 +5967,7 @@
         <v>373</v>
       </c>
       <c r="C378" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="379" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5974,7 +5978,7 @@
         <v>374</v>
       </c>
       <c r="C379" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="380" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5985,7 +5989,7 @@
         <v>375</v>
       </c>
       <c r="C380" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="381" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -5996,7 +6000,7 @@
         <v>376</v>
       </c>
       <c r="C381" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="382" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6007,7 +6011,7 @@
         <v>377</v>
       </c>
       <c r="C382" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="383" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6018,7 +6022,7 @@
         <v>378</v>
       </c>
       <c r="C383" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="384" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6029,7 +6033,7 @@
         <v>379</v>
       </c>
       <c r="C384" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="385" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6040,7 +6044,7 @@
         <v>380</v>
       </c>
       <c r="C385" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="386" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6051,7 +6055,7 @@
         <v>381</v>
       </c>
       <c r="C386" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="387" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6062,7 +6066,7 @@
         <v>382</v>
       </c>
       <c r="C387" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="388" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6073,7 +6077,7 @@
         <v>383</v>
       </c>
       <c r="C388" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="389" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6084,7 +6088,7 @@
         <v>384</v>
       </c>
       <c r="C389" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="390" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6095,7 +6099,7 @@
         <v>385</v>
       </c>
       <c r="C390" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="391" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6106,7 +6110,7 @@
         <v>386</v>
       </c>
       <c r="C391" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="392" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6117,7 +6121,7 @@
         <v>387</v>
       </c>
       <c r="C392" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="393" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6128,7 +6132,7 @@
         <v>388</v>
       </c>
       <c r="C393" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="394" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6139,7 +6143,7 @@
         <v>389</v>
       </c>
       <c r="C394" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="395" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6150,7 +6154,7 @@
         <v>390</v>
       </c>
       <c r="C395" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="396" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6161,7 +6165,7 @@
         <v>391</v>
       </c>
       <c r="C396" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="397" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6172,7 +6176,7 @@
         <v>392</v>
       </c>
       <c r="C397" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="398" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6183,7 +6187,7 @@
         <v>393</v>
       </c>
       <c r="C398" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="399" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6194,7 +6198,7 @@
         <v>394</v>
       </c>
       <c r="C399" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="400" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6205,7 +6209,7 @@
         <v>395</v>
       </c>
       <c r="C400" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="401" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6216,7 +6220,7 @@
         <v>396</v>
       </c>
       <c r="C401" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="402" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6227,7 +6231,7 @@
         <v>397</v>
       </c>
       <c r="C402" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="403" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6238,7 +6242,7 @@
         <v>398</v>
       </c>
       <c r="C403" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="404" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6249,7 +6253,7 @@
         <v>399</v>
       </c>
       <c r="C404" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="405" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6260,7 +6264,7 @@
         <v>400</v>
       </c>
       <c r="C405" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="406" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6271,7 +6275,7 @@
         <v>401</v>
       </c>
       <c r="C406" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="407" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6282,7 +6286,7 @@
         <v>402</v>
       </c>
       <c r="C407" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="408" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6293,7 +6297,7 @@
         <v>403</v>
       </c>
       <c r="C408" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="409" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6304,7 +6308,7 @@
         <v>404</v>
       </c>
       <c r="C409" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="410" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6315,7 +6319,7 @@
         <v>405</v>
       </c>
       <c r="C410" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="411" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6326,7 +6330,7 @@
         <v>406</v>
       </c>
       <c r="C411" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="412" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6337,7 +6341,7 @@
         <v>407</v>
       </c>
       <c r="C412" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="413" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6348,7 +6352,7 @@
         <v>408</v>
       </c>
       <c r="C413" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="414" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6359,7 +6363,7 @@
         <v>409</v>
       </c>
       <c r="C414" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="415" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6370,7 +6374,7 @@
         <v>410</v>
       </c>
       <c r="C415" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="416" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6381,7 +6385,7 @@
         <v>411</v>
       </c>
       <c r="C416" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6392,7 +6396,7 @@
         <v>412</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6403,7 +6407,7 @@
         <v>413</v>
       </c>
       <c r="C418" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6414,7 +6418,7 @@
         <v>414</v>
       </c>
       <c r="C419" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6425,7 +6429,7 @@
         <v>415</v>
       </c>
       <c r="C420" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6436,7 +6440,7 @@
         <v>416</v>
       </c>
       <c r="C421" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6447,7 +6451,7 @@
         <v>417</v>
       </c>
       <c r="C422" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6458,7 +6462,7 @@
         <v>418</v>
       </c>
       <c r="C423" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6469,7 +6473,7 @@
         <v>419</v>
       </c>
       <c r="C424" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6480,7 +6484,7 @@
         <v>420</v>
       </c>
       <c r="C425" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6491,7 +6495,7 @@
         <v>421</v>
       </c>
       <c r="C426" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6502,7 +6506,7 @@
         <v>422</v>
       </c>
       <c r="C427" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6513,7 +6517,7 @@
         <v>423</v>
       </c>
       <c r="C428" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6524,7 +6528,7 @@
         <v>424</v>
       </c>
       <c r="C429" s="6" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6532,10 +6536,10 @@
         <v>1010028657</v>
       </c>
       <c r="B430" s="8" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C430" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6543,10 +6547,10 @@
         <v>1010028655</v>
       </c>
       <c r="B431" s="8" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C431" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -6554,10 +6558,10 @@
         <v>1010084195</v>
       </c>
       <c r="B432" s="8" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C432" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="433" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -6565,10 +6569,10 @@
         <v>1010001400</v>
       </c>
       <c r="B433" s="8" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C433" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="434" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -6576,10 +6580,10 @@
         <v>1010008416</v>
       </c>
       <c r="B434" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C434" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="435" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -6587,10 +6591,10 @@
         <v>1010000896</v>
       </c>
       <c r="B435" s="8" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C435" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="436" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -6598,10 +6602,10 @@
         <v>1010084308</v>
       </c>
       <c r="B436" s="8" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C436" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="437" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
@@ -6609,10 +6613,10 @@
         <v>1010084035</v>
       </c>
       <c r="B437" s="8" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C437" s="6" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E437" s="17"/>
     </row>
